--- a/c.xlsx
+++ b/c.xlsx
@@ -1005,10 +1005,14 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr"/>
+          <t>943609</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>30 kg</t>
+        </is>
+      </c>
       <c r="I13" s="11" t="n">
         <v>460</v>
       </c>
@@ -1486,10 +1490,14 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr"/>
+          <t>943610</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>40 kg</t>
+        </is>
+      </c>
       <c r="F24" s="11" t="n">
         <v>444</v>
       </c>
@@ -1619,10 +1627,14 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q25" s="13" t="inlineStr"/>
+          <t>32732</t>
+        </is>
+      </c>
+      <c r="Q25" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
       <c r="R25" s="11" t="n">
         <v>124</v>
       </c>
@@ -1648,10 +1660,14 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr"/>
+          <t>943612</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>36 kg</t>
+        </is>
+      </c>
       <c r="F26" s="11" t="n">
         <v>368</v>
       </c>
@@ -1729,10 +1745,14 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr"/>
+          <t>943611</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>43 kg</t>
+        </is>
+      </c>
       <c r="F27" s="11" t="n">
         <v>288</v>
       </c>
@@ -3284,10 +3304,14 @@
       </c>
       <c r="S60" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T60" s="13" t="inlineStr"/>
+          <t>943614</t>
+        </is>
+      </c>
+      <c r="T60" s="13" t="inlineStr">
+        <is>
+          <t>38 kg</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="17" customHeight="1">
       <c r="B61" s="9" t="inlineStr">
@@ -5934,12 +5958,12 @@
       </c>
       <c r="M132" s="12" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="N132" s="13" t="inlineStr">
         <is>
-          <t>42 kg</t>
+          <t>34 kg</t>
         </is>
       </c>
       <c r="O132" s="11" t="n">
@@ -5980,10 +6004,14 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H133" s="13" t="inlineStr"/>
+          <t>943615</t>
+        </is>
+      </c>
+      <c r="H133" s="13" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
       <c r="I133" s="11" t="n">
         <v>505</v>
       </c>
@@ -6120,7 +6148,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>32277</t>
         </is>
       </c>
       <c r="H135" s="13" t="inlineStr">
@@ -6507,7 +6535,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
@@ -6677,10 +6705,14 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E147" s="13" t="inlineStr"/>
+          <t>34328</t>
+        </is>
+      </c>
+      <c r="E147" s="13" t="inlineStr">
+        <is>
+          <t>50 kg</t>
+        </is>
+      </c>
       <c r="F147" s="11" t="n">
         <v>545</v>
       </c>
@@ -7151,12 +7183,12 @@
       </c>
       <c r="S157" s="12" t="inlineStr">
         <is>
-          <t>30328</t>
+          <t>33744</t>
         </is>
       </c>
       <c r="T157" s="13" t="inlineStr">
         <is>
-          <t>39 kg</t>
+          <t>40 kg</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7683,7 @@
       </c>
       <c r="S168" s="12" t="inlineStr">
         <is>
-          <t>31736</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="T168" s="13" t="inlineStr">
@@ -7671,7 +7703,7 @@
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33815</t>
         </is>
       </c>
       <c r="E169" s="13" t="inlineStr">
@@ -7697,7 +7729,7 @@
       </c>
       <c r="J169" s="12" t="inlineStr">
         <is>
-          <t>30326</t>
+          <t>33419</t>
         </is>
       </c>
       <c r="K169" s="13" t="inlineStr">
@@ -7769,10 +7801,14 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H170" s="13" t="inlineStr"/>
+          <t>942822</t>
+        </is>
+      </c>
+      <c r="H170" s="13" t="inlineStr">
+        <is>
+          <t>39 kg</t>
+        </is>
+      </c>
       <c r="I170" s="11" t="n">
         <v>49</v>
       </c>
@@ -8191,10 +8227,14 @@
       </c>
       <c r="J180" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K180" s="13" t="inlineStr"/>
+          <t>33464</t>
+        </is>
+      </c>
+      <c r="K180" s="13" t="inlineStr">
+        <is>
+          <t>30 kg</t>
+        </is>
+      </c>
       <c r="L180" s="11" t="n">
         <v>564</v>
       </c>
@@ -8285,10 +8325,14 @@
       </c>
       <c r="M181" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N181" s="13" t="inlineStr"/>
+          <t>33837</t>
+        </is>
+      </c>
+      <c r="N181" s="13" t="inlineStr">
+        <is>
+          <t>44 kg</t>
+        </is>
+      </c>
       <c r="O181" s="11" t="n">
         <v>220</v>
       </c>
@@ -8327,12 +8371,12 @@
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>50 kg</t>
+          <t>35 kg</t>
         </is>
       </c>
       <c r="F182" s="11" t="n">
@@ -8479,10 +8523,14 @@
       </c>
       <c r="S183" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T183" s="13" t="inlineStr"/>
+          <t>943613</t>
+        </is>
+      </c>
+      <c r="T183" s="13" t="inlineStr">
+        <is>
+          <t>45 kg</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="5" customHeight="1"/>
     <row r="186" ht="20" customHeight="1">
@@ -8803,10 +8851,14 @@
       </c>
       <c r="S192" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T192" s="13" t="inlineStr"/>
+          <t>942824</t>
+        </is>
+      </c>
+      <c r="T192" s="13" t="inlineStr">
+        <is>
+          <t>47 kg</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="17" customHeight="1">
       <c r="B193" s="9" t="inlineStr">
@@ -8819,7 +8871,7 @@
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34330</t>
         </is>
       </c>
       <c r="E193" s="13" t="inlineStr">
@@ -12301,10 +12353,14 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr"/>
+          <t>943609</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>30 kg</t>
+        </is>
+      </c>
       <c r="G9" s="18" t="n">
         <v>460</v>
       </c>
@@ -12584,10 +12640,14 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr"/>
+          <t>943610</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>40 kg</t>
+        </is>
+      </c>
       <c r="D15" s="18" t="n">
         <v>444</v>
       </c>
@@ -12715,10 +12775,14 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O16" s="13" t="inlineStr"/>
+          <t>32732</t>
+        </is>
+      </c>
+      <c r="O16" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
       <c r="P16" s="18" t="n">
         <v>124</v>
       </c>
@@ -12739,10 +12803,14 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr"/>
+          <t>943612</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>36 kg</t>
+        </is>
+      </c>
       <c r="D17" s="18" t="n">
         <v>368</v>
       </c>
@@ -12815,10 +12883,14 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr"/>
+          <t>943611</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>43 kg</t>
+        </is>
+      </c>
       <c r="D18" s="18" t="n">
         <v>288</v>
       </c>
@@ -13782,10 +13854,14 @@
       </c>
       <c r="Q36" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R36" s="13" t="inlineStr"/>
+          <t>943614</t>
+        </is>
+      </c>
+      <c r="R36" s="13" t="inlineStr">
+        <is>
+          <t>38 kg</t>
+        </is>
+      </c>
       <c r="T36" s="20" t="n">
         <v>5</v>
       </c>
@@ -15482,12 +15558,12 @@
       </c>
       <c r="K78" s="19" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="L78" s="13" t="inlineStr">
         <is>
-          <t>42 kg</t>
+          <t>34 kg</t>
         </is>
       </c>
       <c r="M78" s="18" t="n">
@@ -15526,10 +15602,14 @@
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="13" t="inlineStr"/>
+          <t>943615</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
       <c r="G79" s="18" t="n">
         <v>505</v>
       </c>
@@ -15656,7 +15736,7 @@
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>32277</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
@@ -15853,7 +15933,7 @@
       </c>
       <c r="B86" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
@@ -16013,10 +16093,14 @@
       </c>
       <c r="B88" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C88" s="13" t="inlineStr"/>
+          <t>34328</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>50 kg</t>
+        </is>
+      </c>
       <c r="D88" s="18" t="n">
         <v>545</v>
       </c>
@@ -16297,12 +16381,12 @@
       </c>
       <c r="Q93" s="19" t="inlineStr">
         <is>
-          <t>30328</t>
+          <t>33744</t>
         </is>
       </c>
       <c r="R93" s="13" t="inlineStr">
         <is>
-          <t>39 kg</t>
+          <t>40 kg</t>
         </is>
       </c>
     </row>
@@ -16599,7 +16683,7 @@
       </c>
       <c r="Q99" s="19" t="inlineStr">
         <is>
-          <t>31736</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="R99" s="13" t="inlineStr">
@@ -16617,7 +16701,7 @@
       </c>
       <c r="B100" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33815</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
@@ -16643,7 +16727,7 @@
       </c>
       <c r="H100" s="19" t="inlineStr">
         <is>
-          <t>30326</t>
+          <t>33419</t>
         </is>
       </c>
       <c r="I100" s="13" t="inlineStr">
@@ -16710,10 +16794,14 @@
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F101" s="13" t="inlineStr"/>
+          <t>942822</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="inlineStr">
+        <is>
+          <t>39 kg</t>
+        </is>
+      </c>
       <c r="G101" s="18" t="n">
         <v>49</v>
       </c>
@@ -16939,10 +17027,14 @@
       </c>
       <c r="H106" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I106" s="13" t="inlineStr"/>
+          <t>33464</t>
+        </is>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>30 kg</t>
+        </is>
+      </c>
       <c r="J106" s="18" t="n">
         <v>564</v>
       </c>
@@ -17031,10 +17123,14 @@
       </c>
       <c r="K107" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L107" s="13" t="inlineStr"/>
+          <t>33837</t>
+        </is>
+      </c>
+      <c r="L107" s="13" t="inlineStr">
+        <is>
+          <t>44 kg</t>
+        </is>
+      </c>
       <c r="M107" s="18" t="n">
         <v>220</v>
       </c>
@@ -17068,12 +17164,12 @@
       </c>
       <c r="B108" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>50 kg</t>
+          <t>35 kg</t>
         </is>
       </c>
       <c r="D108" s="18" t="n">
@@ -17215,10 +17311,14 @@
       </c>
       <c r="Q109" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R109" s="13" t="inlineStr"/>
+          <t>943613</t>
+        </is>
+      </c>
+      <c r="R109" s="13" t="inlineStr">
+        <is>
+          <t>45 kg</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="17" t="n"/>
@@ -17351,10 +17451,14 @@
       </c>
       <c r="Q113" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R113" s="13" t="inlineStr"/>
+          <t>942824</t>
+        </is>
+      </c>
+      <c r="R113" s="13" t="inlineStr">
+        <is>
+          <t>47 kg</t>
+        </is>
+      </c>
       <c r="T113" s="20" t="n">
         <v>16</v>
       </c>
@@ -17365,7 +17469,7 @@
       </c>
       <c r="B114" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34330</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr">
@@ -17729,7 +17833,7 @@
         <v>18</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>836</v>
+        <v>866</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -17759,7 +17863,7 @@
         <v>18</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>666</v>
+        <v>822</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -17849,7 +17953,7 @@
         <v>18</v>
       </c>
       <c r="I12" s="23" t="n">
-        <v>903</v>
+        <v>941</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -18029,7 +18133,7 @@
         <v>16</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>753</v>
+        <v>780</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -18059,7 +18163,7 @@
         <v>18</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>909</v>
+        <v>959</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -18089,7 +18193,7 @@
         <v>18</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -18119,7 +18223,7 @@
         <v>18</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>906</v>
+        <v>945</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -18149,7 +18253,7 @@
         <v>18</v>
       </c>
       <c r="I22" s="23" t="n">
-        <v>828</v>
+        <v>932</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -18179,7 +18283,7 @@
         <v>18</v>
       </c>
       <c r="I23" s="25" t="n">
-        <v>918</v>
+        <v>965</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -18575,7 +18679,7 @@
       </c>
       <c r="D36" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>943609</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
@@ -18583,7 +18687,11 @@
           <t>65</t>
         </is>
       </c>
-      <c r="F36" s="33" t="inlineStr"/>
+      <c r="F36" s="33" t="inlineStr">
+        <is>
+          <t>30 kg</t>
+        </is>
+      </c>
       <c r="G36" s="30" t="inlineStr">
         <is>
           <t>BLOK 01</t>
@@ -18601,7 +18709,7 @@
       </c>
       <c r="J36" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -19302,7 +19410,7 @@
       </c>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>943610</t>
         </is>
       </c>
       <c r="E53" s="28" t="inlineStr">
@@ -19310,7 +19418,11 @@
           <t>68</t>
         </is>
       </c>
-      <c r="F53" s="29" t="inlineStr"/>
+      <c r="F53" s="29" t="inlineStr">
+        <is>
+          <t>40 kg</t>
+        </is>
+      </c>
       <c r="G53" s="28" t="inlineStr">
         <is>
           <t>BLOK 02</t>
@@ -19328,7 +19440,7 @@
       </c>
       <c r="J53" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -19728,7 +19840,7 @@
       </c>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="E63" s="28" t="inlineStr">
@@ -19736,7 +19848,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="F63" s="29" t="inlineStr"/>
+      <c r="F63" s="29" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
       <c r="G63" s="28" t="inlineStr">
         <is>
           <t>BLOK 02</t>
@@ -19754,7 +19870,7 @@
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -19810,7 +19926,7 @@
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>943612</t>
         </is>
       </c>
       <c r="E65" s="28" t="inlineStr">
@@ -19818,7 +19934,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="F65" s="29" t="inlineStr"/>
+      <c r="F65" s="29" t="inlineStr">
+        <is>
+          <t>36 kg</t>
+        </is>
+      </c>
       <c r="G65" s="28" t="inlineStr">
         <is>
           <t>BLOK 02</t>
@@ -19836,7 +19956,7 @@
       </c>
       <c r="J65" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -20064,7 +20184,7 @@
       </c>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>943611</t>
         </is>
       </c>
       <c r="E71" s="28" t="inlineStr">
@@ -20072,7 +20192,11 @@
           <t>68</t>
         </is>
       </c>
-      <c r="F71" s="29" t="inlineStr"/>
+      <c r="F71" s="29" t="inlineStr">
+        <is>
+          <t>43 kg</t>
+        </is>
+      </c>
       <c r="G71" s="28" t="inlineStr">
         <is>
           <t>BLOK 02</t>
@@ -20090,7 +20214,7 @@
       </c>
       <c r="J71" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -22597,7 +22721,7 @@
       </c>
       <c r="D130" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>943614</t>
         </is>
       </c>
       <c r="E130" s="30" t="inlineStr">
@@ -22605,7 +22729,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="F130" s="33" t="inlineStr"/>
+      <c r="F130" s="33" t="inlineStr">
+        <is>
+          <t>38 kg</t>
+        </is>
+      </c>
       <c r="G130" s="30" t="inlineStr">
         <is>
           <t>BLOK 05</t>
@@ -22623,7 +22751,7 @@
       </c>
       <c r="J130" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -24601,7 +24729,7 @@
       </c>
       <c r="J176" s="30" t="inlineStr">
         <is>
-          <t>BELUM DITEMPEL</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -27108,17 +27236,17 @@
       </c>
       <c r="D235" s="19" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="E235" s="28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F235" s="29" t="inlineStr">
         <is>
-          <t>42 kg</t>
+          <t>34 kg</t>
         </is>
       </c>
       <c r="G235" s="28" t="inlineStr">
@@ -27224,7 +27352,7 @@
       </c>
       <c r="J237" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -27237,7 +27365,7 @@
       </c>
       <c r="D238" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>943615</t>
         </is>
       </c>
       <c r="E238" s="30" t="inlineStr">
@@ -27245,7 +27373,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="F238" s="33" t="inlineStr"/>
+      <c r="F238" s="33" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
       <c r="G238" s="30" t="inlineStr">
         <is>
           <t>BLOK 11</t>
@@ -27263,7 +27395,7 @@
       </c>
       <c r="J238" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -27435,7 +27567,7 @@
       </c>
       <c r="J242" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -27663,12 +27795,12 @@
       </c>
       <c r="D248" s="32" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>32277</t>
         </is>
       </c>
       <c r="E248" s="30" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F248" s="33" t="inlineStr">
@@ -28093,12 +28225,12 @@
       </c>
       <c r="D258" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="E258" s="30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F258" s="33" t="inlineStr">
@@ -28123,7 +28255,7 @@
       </c>
       <c r="J258" s="30" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -28609,15 +28741,19 @@
       </c>
       <c r="D270" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="E270" s="30" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="F270" s="33" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F270" s="33" t="inlineStr">
+        <is>
+          <t>50 kg</t>
+        </is>
+      </c>
       <c r="G270" s="30" t="inlineStr">
         <is>
           <t>BLOK 12</t>
@@ -28635,7 +28771,7 @@
       </c>
       <c r="J270" s="30" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -28678,7 +28814,7 @@
       </c>
       <c r="J271" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -29336,17 +29472,17 @@
       </c>
       <c r="D287" s="19" t="inlineStr">
         <is>
-          <t>30328</t>
+          <t>33744</t>
         </is>
       </c>
       <c r="E287" s="28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F287" s="29" t="inlineStr">
         <is>
-          <t>39 kg</t>
+          <t>40 kg</t>
         </is>
       </c>
       <c r="G287" s="28" t="inlineStr">
@@ -29712,7 +29848,7 @@
       </c>
       <c r="J295" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -29970,7 +30106,7 @@
       </c>
       <c r="J301" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -30112,12 +30248,12 @@
       </c>
       <c r="D305" s="19" t="inlineStr">
         <is>
-          <t>31736</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="E305" s="28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F305" s="29" t="inlineStr">
@@ -30155,12 +30291,12 @@
       </c>
       <c r="D306" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33815</t>
         </is>
       </c>
       <c r="E306" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F306" s="33" t="inlineStr">
@@ -30185,7 +30321,7 @@
       </c>
       <c r="J306" s="30" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -30241,12 +30377,12 @@
       </c>
       <c r="D308" s="32" t="inlineStr">
         <is>
-          <t>30326</t>
+          <t>33419</t>
         </is>
       </c>
       <c r="E308" s="30" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F308" s="33" t="inlineStr">
@@ -30456,15 +30592,19 @@
       </c>
       <c r="D313" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>942822</t>
         </is>
       </c>
       <c r="E313" s="28" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="F313" s="29" t="inlineStr"/>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F313" s="29" t="inlineStr">
+        <is>
+          <t>39 kg</t>
+        </is>
+      </c>
       <c r="G313" s="28" t="inlineStr">
         <is>
           <t>BLOK 14</t>
@@ -30482,7 +30622,7 @@
       </c>
       <c r="J313" s="28" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -30740,7 +30880,7 @@
       </c>
       <c r="J319" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -30998,7 +31138,7 @@
       </c>
       <c r="J325" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31011,15 +31151,19 @@
       </c>
       <c r="D326" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="E326" s="30" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F326" s="33" t="inlineStr"/>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F326" s="33" t="inlineStr">
+        <is>
+          <t>30 kg</t>
+        </is>
+      </c>
       <c r="G326" s="30" t="inlineStr">
         <is>
           <t>BLOK 15</t>
@@ -31037,7 +31181,7 @@
       </c>
       <c r="J326" s="30" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31080,7 +31224,7 @@
       </c>
       <c r="J327" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31252,7 +31396,7 @@
       </c>
       <c r="J331" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31295,7 +31439,7 @@
       </c>
       <c r="J332" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31308,15 +31452,19 @@
       </c>
       <c r="D333" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="E333" s="28" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F333" s="29" t="inlineStr"/>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F333" s="29" t="inlineStr">
+        <is>
+          <t>44 kg</t>
+        </is>
+      </c>
       <c r="G333" s="28" t="inlineStr">
         <is>
           <t>BLOK 15</t>
@@ -31334,7 +31482,7 @@
       </c>
       <c r="J333" s="28" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31433,17 +31581,17 @@
       </c>
       <c r="D336" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="E336" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F336" s="33" t="inlineStr">
         <is>
-          <t>50 kg</t>
+          <t>35 kg</t>
         </is>
       </c>
       <c r="G336" s="30" t="inlineStr">
@@ -31463,7 +31611,7 @@
       </c>
       <c r="J336" s="30" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31506,7 +31654,7 @@
       </c>
       <c r="J337" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31549,7 +31697,7 @@
       </c>
       <c r="J338" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31592,7 +31740,7 @@
       </c>
       <c r="J339" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31766,7 +31914,7 @@
       </c>
       <c r="J343" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31809,7 +31957,7 @@
       </c>
       <c r="J344" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31852,7 +32000,7 @@
       </c>
       <c r="J345" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -31908,7 +32056,7 @@
       </c>
       <c r="D347" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>943613</t>
         </is>
       </c>
       <c r="E347" s="28" t="inlineStr">
@@ -31916,7 +32064,11 @@
           <t>53</t>
         </is>
       </c>
-      <c r="F347" s="29" t="inlineStr"/>
+      <c r="F347" s="29" t="inlineStr">
+        <is>
+          <t>45 kg</t>
+        </is>
+      </c>
       <c r="G347" s="28" t="inlineStr">
         <is>
           <t>BLOK 15</t>
@@ -31934,7 +32086,7 @@
       </c>
       <c r="J347" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32020,7 +32172,7 @@
       </c>
       <c r="J349" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32063,7 +32215,7 @@
       </c>
       <c r="J350" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32106,7 +32258,7 @@
       </c>
       <c r="J351" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32149,7 +32301,7 @@
       </c>
       <c r="J352" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32162,15 +32314,19 @@
       </c>
       <c r="D353" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>942824</t>
         </is>
       </c>
       <c r="E353" s="28" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="F353" s="29" t="inlineStr"/>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F353" s="29" t="inlineStr">
+        <is>
+          <t>47 kg</t>
+        </is>
+      </c>
       <c r="G353" s="28" t="inlineStr">
         <is>
           <t>BLOK 16</t>
@@ -32188,7 +32344,7 @@
       </c>
       <c r="J353" s="28" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32201,12 +32357,12 @@
       </c>
       <c r="D354" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34330</t>
         </is>
       </c>
       <c r="E354" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F354" s="33" t="inlineStr">
@@ -32231,7 +32387,7 @@
       </c>
       <c r="J354" s="30" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32274,7 +32430,7 @@
       </c>
       <c r="J355" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32317,7 +32473,7 @@
       </c>
       <c r="J356" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32360,7 +32516,7 @@
       </c>
       <c r="J357" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32403,7 +32559,7 @@
       </c>
       <c r="J358" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32446,7 +32602,7 @@
       </c>
       <c r="J359" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32532,7 +32688,7 @@
       </c>
       <c r="J361" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32575,7 +32731,7 @@
       </c>
       <c r="J362" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32618,7 +32774,7 @@
       </c>
       <c r="J363" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32661,7 +32817,7 @@
       </c>
       <c r="J364" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32704,7 +32860,7 @@
       </c>
       <c r="J365" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32790,7 +32946,7 @@
       </c>
       <c r="J367" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32833,7 +32989,7 @@
       </c>
       <c r="J368" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32876,7 +33032,7 @@
       </c>
       <c r="J369" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32919,7 +33075,7 @@
       </c>
       <c r="J370" s="30" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -32962,7 +33118,7 @@
       </c>
       <c r="J371" s="28" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>

--- a/c.xlsx
+++ b/c.xlsx
@@ -3998,16 +3998,16 @@
         </is>
       </c>
       <c r="R73" s="11" t="n">
-        <v>103</v>
+        <v>515</v>
       </c>
       <c r="S73" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32957</t>
         </is>
       </c>
       <c r="T73" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36.0 kg</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>45 kg</t>
+          <t>45.0 kg</t>
         </is>
       </c>
       <c r="F87" s="11" t="n">
@@ -11281,7 +11281,7 @@
         <v>387</v>
       </c>
       <c r="H61" s="14" t="n">
-        <v>103</v>
+        <v>515</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -15470,16 +15470,16 @@
         </is>
       </c>
       <c r="P44" s="18" t="n">
-        <v>103</v>
+        <v>515</v>
       </c>
       <c r="Q44" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32957</t>
         </is>
       </c>
       <c r="R44" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36.0 kg</t>
         </is>
       </c>
     </row>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>45 kg</t>
+          <t>45.0 kg</t>
         </is>
       </c>
       <c r="D53" s="18" t="n">
@@ -19753,7 +19753,7 @@
         <v>18</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>830</v>
+        <v>866</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -25906,21 +25906,21 @@
         <v>135</v>
       </c>
       <c r="C163" s="18" t="n">
-        <v>103</v>
+        <v>515</v>
       </c>
       <c r="D163" s="19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32957</t>
         </is>
       </c>
       <c r="E163" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F163" s="29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G163" s="28" t="inlineStr">
@@ -25940,7 +25940,7 @@
       </c>
       <c r="J163" s="28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>
@@ -27253,7 +27253,7 @@
       </c>
       <c r="F194" s="33" t="inlineStr">
         <is>
-          <t>45 kg</t>
+          <t>45.0 kg</t>
         </is>
       </c>
       <c r="G194" s="30" t="inlineStr">

--- a/c.xlsx
+++ b/c.xlsx
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="L11" s="11" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>35663</t>
         </is>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>45 kg</t>
+          <t>44 kg</t>
         </is>
       </c>
       <c r="O11" s="11" t="n">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>34 kg</t>
+          <t>45 kg</t>
         </is>
       </c>
       <c r="F22" s="11" t="n">
@@ -10713,7 +10713,7 @@
         <v>132</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>636</v>
@@ -10893,7 +10893,7 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>631</v>
@@ -13960,16 +13960,16 @@
         </is>
       </c>
       <c r="J7" s="18" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K7" s="19" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>35663</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>45 kg</t>
+          <t>44 kg</t>
         </is>
       </c>
       <c r="M7" s="18" t="n">
@@ -14344,16 +14344,16 @@
     </row>
     <row r="13">
       <c r="A13" s="18" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>34 kg</t>
+          <t>45 kg</t>
         </is>
       </c>
       <c r="D13" s="18" t="n">
@@ -20527,7 +20527,7 @@
         <v>6</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -20557,7 +20557,7 @@
         <v>6</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>1448</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -21455,21 +21455,21 @@
         <v>10</v>
       </c>
       <c r="C38" s="31" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D38" s="32" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>35663</t>
         </is>
       </c>
       <c r="E38" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F38" s="33" t="inlineStr">
         <is>
-          <t>45 kg</t>
+          <t>44 kg</t>
         </is>
       </c>
       <c r="G38" s="30" t="inlineStr">
@@ -22616,11 +22616,11 @@
         <v>37</v>
       </c>
       <c r="C65" s="18" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="E65" s="28" t="inlineStr">
@@ -22630,7 +22630,7 @@
       </c>
       <c r="F65" s="29" t="inlineStr">
         <is>
-          <t>34 kg</t>
+          <t>45 kg</t>
         </is>
       </c>
       <c r="G65" s="28" t="inlineStr">

--- a/c.xlsx
+++ b/c.xlsx
@@ -7268,9 +7268,13 @@
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>118</v>
-      </c>
-      <c r="D133" s="12" t="inlineStr"/>
+        <v>513</v>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>34240</t>
+        </is>
+      </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
           <t>50.0 kg</t>
@@ -12720,7 +12724,7 @@
         </is>
       </c>
       <c r="C111" s="14" t="n">
-        <v>118</v>
+        <v>513</v>
       </c>
       <c r="D111" s="14" t="n">
         <v>565</v>
@@ -18244,9 +18248,13 @@
     </row>
     <row r="79">
       <c r="A79" s="18" t="n">
-        <v>118</v>
-      </c>
-      <c r="B79" s="19" t="inlineStr"/>
+        <v>513</v>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>34240</t>
+        </is>
+      </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
           <t>50.0 kg</t>
@@ -33581,12 +33589,16 @@
         <v>292</v>
       </c>
       <c r="C320" s="31" t="n">
-        <v>118</v>
-      </c>
-      <c r="D320" s="32" t="inlineStr"/>
+        <v>513</v>
+      </c>
+      <c r="D320" s="32" t="inlineStr">
+        <is>
+          <t>34240</t>
+        </is>
+      </c>
       <c r="E320" s="30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F320" s="33" t="inlineStr">
@@ -33611,7 +33623,7 @@
       </c>
       <c r="J320" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SELESAI</t>
         </is>
       </c>
     </row>

--- a/c.xlsx
+++ b/c.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Rekapitulasi &amp; Cari Bal" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rekapitulasi &amp; Cari Bal'!$B$28:$J$537</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rekapitulasi &amp; Cari Bal'!$B$28:$J$562</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7901,15 +7901,45 @@
           <t>34 kg</t>
         </is>
       </c>
-      <c r="L130" s="11" t="inlineStr"/>
-      <c r="M130" s="12" t="inlineStr"/>
-      <c r="N130" s="13" t="inlineStr"/>
-      <c r="O130" s="11" t="inlineStr"/>
-      <c r="P130" s="12" t="inlineStr"/>
-      <c r="Q130" s="13" t="inlineStr"/>
-      <c r="R130" s="11" t="inlineStr"/>
-      <c r="S130" s="12" t="inlineStr"/>
-      <c r="T130" s="13" t="inlineStr"/>
+      <c r="L130" s="11" t="n">
+        <v>768</v>
+      </c>
+      <c r="M130" s="12" t="inlineStr">
+        <is>
+          <t>123144</t>
+        </is>
+      </c>
+      <c r="N130" s="13" t="inlineStr">
+        <is>
+          <t>39 kg</t>
+        </is>
+      </c>
+      <c r="O130" s="11" t="n">
+        <v>769</v>
+      </c>
+      <c r="P130" s="12" t="inlineStr">
+        <is>
+          <t>123305</t>
+        </is>
+      </c>
+      <c r="Q130" s="13" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
+      <c r="R130" s="11" t="n">
+        <v>767</v>
+      </c>
+      <c r="S130" s="12" t="inlineStr">
+        <is>
+          <t>940843</t>
+        </is>
+      </c>
+      <c r="T130" s="13" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="17" customHeight="1">
       <c r="B131" s="9" t="inlineStr">
@@ -7969,12 +7999,32 @@
           <t>35 kg</t>
         </is>
       </c>
-      <c r="O131" s="11" t="inlineStr"/>
-      <c r="P131" s="12" t="inlineStr"/>
-      <c r="Q131" s="13" t="inlineStr"/>
-      <c r="R131" s="11" t="inlineStr"/>
-      <c r="S131" s="12" t="inlineStr"/>
-      <c r="T131" s="13" t="inlineStr"/>
+      <c r="O131" s="11" t="n">
+        <v>770</v>
+      </c>
+      <c r="P131" s="12" t="inlineStr">
+        <is>
+          <t>940844</t>
+        </is>
+      </c>
+      <c r="Q131" s="13" t="inlineStr">
+        <is>
+          <t>44 kg</t>
+        </is>
+      </c>
+      <c r="R131" s="11" t="n">
+        <v>764</v>
+      </c>
+      <c r="S131" s="12" t="inlineStr">
+        <is>
+          <t>123304</t>
+        </is>
+      </c>
+      <c r="T131" s="13" t="inlineStr">
+        <is>
+          <t>44 kg</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="17" customHeight="1">
       <c r="B132" s="9" t="inlineStr">
@@ -8515,24 +8565,84 @@
           <t>T6</t>
         </is>
       </c>
-      <c r="C142" s="10" t="inlineStr"/>
-      <c r="D142" s="10" t="inlineStr"/>
-      <c r="E142" s="10" t="inlineStr"/>
-      <c r="F142" s="10" t="inlineStr"/>
-      <c r="G142" s="10" t="inlineStr"/>
-      <c r="H142" s="10" t="inlineStr"/>
-      <c r="I142" s="10" t="inlineStr"/>
-      <c r="J142" s="10" t="inlineStr"/>
-      <c r="K142" s="10" t="inlineStr"/>
-      <c r="L142" s="10" t="inlineStr"/>
-      <c r="M142" s="10" t="inlineStr"/>
-      <c r="N142" s="10" t="inlineStr"/>
-      <c r="O142" s="10" t="inlineStr"/>
-      <c r="P142" s="10" t="inlineStr"/>
-      <c r="Q142" s="10" t="inlineStr"/>
-      <c r="R142" s="10" t="inlineStr"/>
-      <c r="S142" s="10" t="inlineStr"/>
-      <c r="T142" s="10" t="inlineStr"/>
+      <c r="C142" s="11" t="n">
+        <v>747</v>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>123139</t>
+        </is>
+      </c>
+      <c r="E142" s="13" t="inlineStr">
+        <is>
+          <t>45 kg</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>787</v>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>940846</t>
+        </is>
+      </c>
+      <c r="H142" s="13" t="inlineStr">
+        <is>
+          <t>30 kg</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="n">
+        <v>748</v>
+      </c>
+      <c r="J142" s="12" t="inlineStr">
+        <is>
+          <t>123140</t>
+        </is>
+      </c>
+      <c r="K142" s="13" t="inlineStr">
+        <is>
+          <t>34 kg</t>
+        </is>
+      </c>
+      <c r="L142" s="11" t="n">
+        <v>788</v>
+      </c>
+      <c r="M142" s="12" t="inlineStr">
+        <is>
+          <t>123306</t>
+        </is>
+      </c>
+      <c r="N142" s="13" t="inlineStr">
+        <is>
+          <t>34 kg</t>
+        </is>
+      </c>
+      <c r="O142" s="11" t="n">
+        <v>762</v>
+      </c>
+      <c r="P142" s="12" t="inlineStr">
+        <is>
+          <t>123143</t>
+        </is>
+      </c>
+      <c r="Q142" s="13" t="inlineStr">
+        <is>
+          <t>42 kg</t>
+        </is>
+      </c>
+      <c r="R142" s="11" t="n">
+        <v>765</v>
+      </c>
+      <c r="S142" s="12" t="inlineStr">
+        <is>
+          <t>940842</t>
+        </is>
+      </c>
+      <c r="T142" s="13" t="inlineStr">
+        <is>
+          <t>50 kg</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="17" customHeight="1">
       <c r="B143" s="9" t="inlineStr">
@@ -8540,24 +8650,84 @@
           <t>T5</t>
         </is>
       </c>
-      <c r="C143" s="10" t="inlineStr"/>
-      <c r="D143" s="10" t="inlineStr"/>
-      <c r="E143" s="10" t="inlineStr"/>
-      <c r="F143" s="10" t="inlineStr"/>
-      <c r="G143" s="10" t="inlineStr"/>
-      <c r="H143" s="10" t="inlineStr"/>
-      <c r="I143" s="10" t="inlineStr"/>
-      <c r="J143" s="10" t="inlineStr"/>
-      <c r="K143" s="10" t="inlineStr"/>
-      <c r="L143" s="10" t="inlineStr"/>
-      <c r="M143" s="10" t="inlineStr"/>
-      <c r="N143" s="10" t="inlineStr"/>
-      <c r="O143" s="10" t="inlineStr"/>
-      <c r="P143" s="10" t="inlineStr"/>
-      <c r="Q143" s="10" t="inlineStr"/>
-      <c r="R143" s="10" t="inlineStr"/>
-      <c r="S143" s="10" t="inlineStr"/>
-      <c r="T143" s="10" t="inlineStr"/>
+      <c r="C143" s="11" t="n">
+        <v>715</v>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>940845</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="inlineStr">
+        <is>
+          <t>46 kg</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>786</v>
+      </c>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>123307</t>
+        </is>
+      </c>
+      <c r="H143" s="13" t="inlineStr">
+        <is>
+          <t>36 kg</t>
+        </is>
+      </c>
+      <c r="I143" s="11" t="n">
+        <v>789</v>
+      </c>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>123145</t>
+        </is>
+      </c>
+      <c r="K143" s="13" t="inlineStr">
+        <is>
+          <t>34 kg</t>
+        </is>
+      </c>
+      <c r="L143" s="11" t="n">
+        <v>763</v>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>123142</t>
+        </is>
+      </c>
+      <c r="N143" s="13" t="inlineStr">
+        <is>
+          <t>42 kg</t>
+        </is>
+      </c>
+      <c r="O143" s="11" t="n">
+        <v>761</v>
+      </c>
+      <c r="P143" s="12" t="inlineStr">
+        <is>
+          <t>123141</t>
+        </is>
+      </c>
+      <c r="Q143" s="13" t="inlineStr">
+        <is>
+          <t>44 kg</t>
+        </is>
+      </c>
+      <c r="R143" s="11" t="n">
+        <v>766</v>
+      </c>
+      <c r="S143" s="12" t="inlineStr">
+        <is>
+          <t>940847</t>
+        </is>
+      </c>
+      <c r="T143" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="17" customHeight="1">
       <c r="B144" s="9" t="inlineStr">
@@ -9098,24 +9268,64 @@
           <t>T6</t>
         </is>
       </c>
-      <c r="C154" s="10" t="inlineStr"/>
-      <c r="D154" s="10" t="inlineStr"/>
-      <c r="E154" s="10" t="inlineStr"/>
-      <c r="F154" s="10" t="inlineStr"/>
-      <c r="G154" s="10" t="inlineStr"/>
-      <c r="H154" s="10" t="inlineStr"/>
-      <c r="I154" s="10" t="inlineStr"/>
-      <c r="J154" s="10" t="inlineStr"/>
-      <c r="K154" s="10" t="inlineStr"/>
-      <c r="L154" s="10" t="inlineStr"/>
-      <c r="M154" s="10" t="inlineStr"/>
-      <c r="N154" s="10" t="inlineStr"/>
-      <c r="O154" s="10" t="inlineStr"/>
-      <c r="P154" s="10" t="inlineStr"/>
-      <c r="Q154" s="10" t="inlineStr"/>
-      <c r="R154" s="10" t="inlineStr"/>
-      <c r="S154" s="10" t="inlineStr"/>
-      <c r="T154" s="10" t="inlineStr"/>
+      <c r="C154" s="11" t="n">
+        <v>752</v>
+      </c>
+      <c r="D154" s="12" t="inlineStr">
+        <is>
+          <t>39325</t>
+        </is>
+      </c>
+      <c r="E154" s="13" t="inlineStr">
+        <is>
+          <t>42 kg</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>751</v>
+      </c>
+      <c r="G154" s="12" t="inlineStr">
+        <is>
+          <t>39200</t>
+        </is>
+      </c>
+      <c r="H154" s="13" t="inlineStr">
+        <is>
+          <t>41 kg</t>
+        </is>
+      </c>
+      <c r="I154" s="11" t="n">
+        <v>771</v>
+      </c>
+      <c r="J154" s="12" t="inlineStr">
+        <is>
+          <t>940848</t>
+        </is>
+      </c>
+      <c r="K154" s="13" t="inlineStr">
+        <is>
+          <t>30 kg</t>
+        </is>
+      </c>
+      <c r="L154" s="11" t="n">
+        <v>772</v>
+      </c>
+      <c r="M154" s="12" t="inlineStr">
+        <is>
+          <t>940840</t>
+        </is>
+      </c>
+      <c r="N154" s="13" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
+      <c r="O154" s="11" t="inlineStr"/>
+      <c r="P154" s="12" t="inlineStr"/>
+      <c r="Q154" s="13" t="inlineStr"/>
+      <c r="R154" s="11" t="inlineStr"/>
+      <c r="S154" s="12" t="inlineStr"/>
+      <c r="T154" s="13" t="inlineStr"/>
     </row>
     <row r="155" ht="17" customHeight="1">
       <c r="B155" s="9" t="inlineStr">
@@ -9123,24 +9333,64 @@
           <t>T5</t>
         </is>
       </c>
-      <c r="C155" s="10" t="inlineStr"/>
-      <c r="D155" s="10" t="inlineStr"/>
-      <c r="E155" s="10" t="inlineStr"/>
-      <c r="F155" s="10" t="inlineStr"/>
-      <c r="G155" s="10" t="inlineStr"/>
-      <c r="H155" s="10" t="inlineStr"/>
-      <c r="I155" s="10" t="inlineStr"/>
-      <c r="J155" s="10" t="inlineStr"/>
-      <c r="K155" s="10" t="inlineStr"/>
-      <c r="L155" s="10" t="inlineStr"/>
-      <c r="M155" s="10" t="inlineStr"/>
-      <c r="N155" s="10" t="inlineStr"/>
-      <c r="O155" s="10" t="inlineStr"/>
-      <c r="P155" s="10" t="inlineStr"/>
-      <c r="Q155" s="10" t="inlineStr"/>
-      <c r="R155" s="10" t="inlineStr"/>
-      <c r="S155" s="10" t="inlineStr"/>
-      <c r="T155" s="10" t="inlineStr"/>
+      <c r="C155" s="11" t="n">
+        <v>773</v>
+      </c>
+      <c r="D155" s="12" t="inlineStr">
+        <is>
+          <t>940841</t>
+        </is>
+      </c>
+      <c r="E155" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>755</v>
+      </c>
+      <c r="G155" s="12" t="inlineStr">
+        <is>
+          <t>123303</t>
+        </is>
+      </c>
+      <c r="H155" s="13" t="inlineStr">
+        <is>
+          <t>48 kg</t>
+        </is>
+      </c>
+      <c r="I155" s="11" t="n">
+        <v>753</v>
+      </c>
+      <c r="J155" s="12" t="inlineStr">
+        <is>
+          <t>123302</t>
+        </is>
+      </c>
+      <c r="K155" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
+      <c r="L155" s="11" t="n">
+        <v>749</v>
+      </c>
+      <c r="M155" s="12" t="inlineStr">
+        <is>
+          <t>123301</t>
+        </is>
+      </c>
+      <c r="N155" s="13" t="inlineStr">
+        <is>
+          <t>40 kg</t>
+        </is>
+      </c>
+      <c r="O155" s="11" t="inlineStr"/>
+      <c r="P155" s="12" t="inlineStr"/>
+      <c r="Q155" s="13" t="inlineStr"/>
+      <c r="R155" s="11" t="inlineStr"/>
+      <c r="S155" s="12" t="inlineStr"/>
+      <c r="T155" s="13" t="inlineStr"/>
     </row>
     <row r="156" ht="17" customHeight="1">
       <c r="B156" s="9" t="inlineStr">
@@ -13627,9 +13877,15 @@
       <c r="E108" s="14" t="n">
         <v>743</v>
       </c>
-      <c r="F108" s="14" t="inlineStr"/>
-      <c r="G108" s="14" t="inlineStr"/>
-      <c r="H108" s="14" t="inlineStr"/>
+      <c r="F108" s="14" t="n">
+        <v>768</v>
+      </c>
+      <c r="G108" s="14" t="n">
+        <v>769</v>
+      </c>
+      <c r="H108" s="14" t="n">
+        <v>767</v>
+      </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="B109" s="9" t="inlineStr">
@@ -13649,8 +13905,12 @@
       <c r="F109" s="14" t="n">
         <v>737</v>
       </c>
-      <c r="G109" s="14" t="inlineStr"/>
-      <c r="H109" s="14" t="inlineStr"/>
+      <c r="G109" s="14" t="n">
+        <v>770</v>
+      </c>
+      <c r="H109" s="14" t="n">
+        <v>764</v>
+      </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="B110" s="9" t="inlineStr">
@@ -13822,12 +14082,24 @@
           <t>T6</t>
         </is>
       </c>
-      <c r="C118" s="10" t="inlineStr"/>
-      <c r="D118" s="10" t="inlineStr"/>
-      <c r="E118" s="10" t="inlineStr"/>
-      <c r="F118" s="10" t="inlineStr"/>
-      <c r="G118" s="10" t="inlineStr"/>
-      <c r="H118" s="10" t="inlineStr"/>
+      <c r="C118" s="14" t="n">
+        <v>747</v>
+      </c>
+      <c r="D118" s="14" t="n">
+        <v>787</v>
+      </c>
+      <c r="E118" s="14" t="n">
+        <v>748</v>
+      </c>
+      <c r="F118" s="14" t="n">
+        <v>788</v>
+      </c>
+      <c r="G118" s="14" t="n">
+        <v>762</v>
+      </c>
+      <c r="H118" s="14" t="n">
+        <v>765</v>
+      </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="B119" s="9" t="inlineStr">
@@ -13835,12 +14107,24 @@
           <t>T5</t>
         </is>
       </c>
-      <c r="C119" s="10" t="inlineStr"/>
-      <c r="D119" s="10" t="inlineStr"/>
-      <c r="E119" s="10" t="inlineStr"/>
-      <c r="F119" s="10" t="inlineStr"/>
-      <c r="G119" s="10" t="inlineStr"/>
-      <c r="H119" s="10" t="inlineStr"/>
+      <c r="C119" s="14" t="n">
+        <v>715</v>
+      </c>
+      <c r="D119" s="14" t="n">
+        <v>786</v>
+      </c>
+      <c r="E119" s="14" t="n">
+        <v>789</v>
+      </c>
+      <c r="F119" s="14" t="n">
+        <v>763</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>761</v>
+      </c>
+      <c r="H119" s="14" t="n">
+        <v>766</v>
+      </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="B120" s="9" t="inlineStr">
@@ -14012,12 +14296,20 @@
           <t>T6</t>
         </is>
       </c>
-      <c r="C128" s="10" t="inlineStr"/>
-      <c r="D128" s="10" t="inlineStr"/>
-      <c r="E128" s="10" t="inlineStr"/>
-      <c r="F128" s="10" t="inlineStr"/>
-      <c r="G128" s="10" t="inlineStr"/>
-      <c r="H128" s="10" t="inlineStr"/>
+      <c r="C128" s="14" t="n">
+        <v>752</v>
+      </c>
+      <c r="D128" s="14" t="n">
+        <v>751</v>
+      </c>
+      <c r="E128" s="14" t="n">
+        <v>771</v>
+      </c>
+      <c r="F128" s="14" t="n">
+        <v>772</v>
+      </c>
+      <c r="G128" s="14" t="inlineStr"/>
+      <c r="H128" s="14" t="inlineStr"/>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="B129" s="9" t="inlineStr">
@@ -14025,12 +14317,20 @@
           <t>T5</t>
         </is>
       </c>
-      <c r="C129" s="10" t="inlineStr"/>
-      <c r="D129" s="10" t="inlineStr"/>
-      <c r="E129" s="10" t="inlineStr"/>
-      <c r="F129" s="10" t="inlineStr"/>
-      <c r="G129" s="10" t="inlineStr"/>
-      <c r="H129" s="10" t="inlineStr"/>
+      <c r="C129" s="14" t="n">
+        <v>773</v>
+      </c>
+      <c r="D129" s="14" t="n">
+        <v>755</v>
+      </c>
+      <c r="E129" s="14" t="n">
+        <v>753</v>
+      </c>
+      <c r="F129" s="14" t="n">
+        <v>749</v>
+      </c>
+      <c r="G129" s="14" t="inlineStr"/>
+      <c r="H129" s="14" t="inlineStr"/>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="B130" s="9" t="inlineStr">
@@ -19853,15 +20153,45 @@
           <t>34 kg</t>
         </is>
       </c>
-      <c r="J76" s="18" t="inlineStr"/>
-      <c r="K76" s="19" t="inlineStr"/>
-      <c r="L76" s="13" t="inlineStr"/>
-      <c r="M76" s="18" t="inlineStr"/>
-      <c r="N76" s="19" t="inlineStr"/>
-      <c r="O76" s="13" t="inlineStr"/>
-      <c r="P76" s="18" t="inlineStr"/>
-      <c r="Q76" s="19" t="inlineStr"/>
-      <c r="R76" s="13" t="inlineStr"/>
+      <c r="J76" s="18" t="n">
+        <v>768</v>
+      </c>
+      <c r="K76" s="19" t="inlineStr">
+        <is>
+          <t>123144</t>
+        </is>
+      </c>
+      <c r="L76" s="13" t="inlineStr">
+        <is>
+          <t>39 kg</t>
+        </is>
+      </c>
+      <c r="M76" s="18" t="n">
+        <v>769</v>
+      </c>
+      <c r="N76" s="19" t="inlineStr">
+        <is>
+          <t>123305</t>
+        </is>
+      </c>
+      <c r="O76" s="13" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
+      <c r="P76" s="18" t="n">
+        <v>767</v>
+      </c>
+      <c r="Q76" s="19" t="inlineStr">
+        <is>
+          <t>940843</t>
+        </is>
+      </c>
+      <c r="R76" s="13" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="18" t="n">
@@ -19916,12 +20246,32 @@
           <t>35 kg</t>
         </is>
       </c>
-      <c r="M77" s="18" t="inlineStr"/>
-      <c r="N77" s="19" t="inlineStr"/>
-      <c r="O77" s="13" t="inlineStr"/>
-      <c r="P77" s="18" t="inlineStr"/>
-      <c r="Q77" s="19" t="inlineStr"/>
-      <c r="R77" s="13" t="inlineStr"/>
+      <c r="M77" s="18" t="n">
+        <v>770</v>
+      </c>
+      <c r="N77" s="19" t="inlineStr">
+        <is>
+          <t>940844</t>
+        </is>
+      </c>
+      <c r="O77" s="13" t="inlineStr">
+        <is>
+          <t>44 kg</t>
+        </is>
+      </c>
+      <c r="P77" s="18" t="n">
+        <v>764</v>
+      </c>
+      <c r="Q77" s="19" t="inlineStr">
+        <is>
+          <t>123304</t>
+        </is>
+      </c>
+      <c r="R77" s="13" t="inlineStr">
+        <is>
+          <t>44 kg</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="18" t="n">
@@ -20267,44 +20617,164 @@
       <c r="R82" s="17" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="17" t="n"/>
-      <c r="B83" s="17" t="n"/>
-      <c r="C83" s="17" t="n"/>
-      <c r="D83" s="17" t="n"/>
-      <c r="E83" s="17" t="n"/>
-      <c r="F83" s="17" t="n"/>
-      <c r="G83" s="17" t="n"/>
-      <c r="H83" s="17" t="n"/>
-      <c r="I83" s="17" t="n"/>
-      <c r="J83" s="17" t="n"/>
-      <c r="K83" s="17" t="n"/>
-      <c r="L83" s="17" t="n"/>
-      <c r="M83" s="17" t="n"/>
-      <c r="N83" s="17" t="n"/>
-      <c r="O83" s="17" t="n"/>
-      <c r="P83" s="17" t="n"/>
-      <c r="Q83" s="17" t="n"/>
-      <c r="R83" s="17" t="n"/>
+      <c r="A83" s="18" t="n">
+        <v>747</v>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
+        <is>
+          <t>123139</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>45 kg</t>
+        </is>
+      </c>
+      <c r="D83" s="18" t="n">
+        <v>787</v>
+      </c>
+      <c r="E83" s="19" t="inlineStr">
+        <is>
+          <t>940846</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="inlineStr">
+        <is>
+          <t>30 kg</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="n">
+        <v>748</v>
+      </c>
+      <c r="H83" s="19" t="inlineStr">
+        <is>
+          <t>123140</t>
+        </is>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>34 kg</t>
+        </is>
+      </c>
+      <c r="J83" s="18" t="n">
+        <v>788</v>
+      </c>
+      <c r="K83" s="19" t="inlineStr">
+        <is>
+          <t>123306</t>
+        </is>
+      </c>
+      <c r="L83" s="13" t="inlineStr">
+        <is>
+          <t>34 kg</t>
+        </is>
+      </c>
+      <c r="M83" s="18" t="n">
+        <v>762</v>
+      </c>
+      <c r="N83" s="19" t="inlineStr">
+        <is>
+          <t>123143</t>
+        </is>
+      </c>
+      <c r="O83" s="13" t="inlineStr">
+        <is>
+          <t>42 kg</t>
+        </is>
+      </c>
+      <c r="P83" s="18" t="n">
+        <v>765</v>
+      </c>
+      <c r="Q83" s="19" t="inlineStr">
+        <is>
+          <t>940842</t>
+        </is>
+      </c>
+      <c r="R83" s="13" t="inlineStr">
+        <is>
+          <t>50 kg</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="17" t="n"/>
-      <c r="B84" s="17" t="n"/>
-      <c r="C84" s="17" t="n"/>
-      <c r="D84" s="17" t="n"/>
-      <c r="E84" s="17" t="n"/>
-      <c r="F84" s="17" t="n"/>
-      <c r="G84" s="17" t="n"/>
-      <c r="H84" s="17" t="n"/>
-      <c r="I84" s="17" t="n"/>
-      <c r="J84" s="17" t="n"/>
-      <c r="K84" s="17" t="n"/>
-      <c r="L84" s="17" t="n"/>
-      <c r="M84" s="17" t="n"/>
-      <c r="N84" s="17" t="n"/>
-      <c r="O84" s="17" t="n"/>
-      <c r="P84" s="17" t="n"/>
-      <c r="Q84" s="17" t="n"/>
-      <c r="R84" s="17" t="n"/>
+      <c r="A84" s="18" t="n">
+        <v>715</v>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>940845</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>46 kg</t>
+        </is>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>786</v>
+      </c>
+      <c r="E84" s="19" t="inlineStr">
+        <is>
+          <t>123307</t>
+        </is>
+      </c>
+      <c r="F84" s="13" t="inlineStr">
+        <is>
+          <t>36 kg</t>
+        </is>
+      </c>
+      <c r="G84" s="18" t="n">
+        <v>789</v>
+      </c>
+      <c r="H84" s="19" t="inlineStr">
+        <is>
+          <t>123145</t>
+        </is>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>34 kg</t>
+        </is>
+      </c>
+      <c r="J84" s="18" t="n">
+        <v>763</v>
+      </c>
+      <c r="K84" s="19" t="inlineStr">
+        <is>
+          <t>123142</t>
+        </is>
+      </c>
+      <c r="L84" s="13" t="inlineStr">
+        <is>
+          <t>42 kg</t>
+        </is>
+      </c>
+      <c r="M84" s="18" t="n">
+        <v>761</v>
+      </c>
+      <c r="N84" s="19" t="inlineStr">
+        <is>
+          <t>123141</t>
+        </is>
+      </c>
+      <c r="O84" s="13" t="inlineStr">
+        <is>
+          <t>44 kg</t>
+        </is>
+      </c>
+      <c r="P84" s="18" t="n">
+        <v>766</v>
+      </c>
+      <c r="Q84" s="19" t="inlineStr">
+        <is>
+          <t>940847</t>
+        </is>
+      </c>
+      <c r="R84" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="18" t="n">
@@ -20650,44 +21120,124 @@
       <c r="R89" s="17" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="17" t="n"/>
-      <c r="B90" s="17" t="n"/>
-      <c r="C90" s="17" t="n"/>
-      <c r="D90" s="17" t="n"/>
-      <c r="E90" s="17" t="n"/>
-      <c r="F90" s="17" t="n"/>
-      <c r="G90" s="17" t="n"/>
-      <c r="H90" s="17" t="n"/>
-      <c r="I90" s="17" t="n"/>
-      <c r="J90" s="17" t="n"/>
-      <c r="K90" s="17" t="n"/>
-      <c r="L90" s="17" t="n"/>
-      <c r="M90" s="17" t="n"/>
-      <c r="N90" s="17" t="n"/>
-      <c r="O90" s="17" t="n"/>
-      <c r="P90" s="17" t="n"/>
-      <c r="Q90" s="17" t="n"/>
-      <c r="R90" s="17" t="n"/>
+      <c r="A90" s="18" t="n">
+        <v>752</v>
+      </c>
+      <c r="B90" s="19" t="inlineStr">
+        <is>
+          <t>39325</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>42 kg</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="n">
+        <v>751</v>
+      </c>
+      <c r="E90" s="19" t="inlineStr">
+        <is>
+          <t>39200</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="inlineStr">
+        <is>
+          <t>41 kg</t>
+        </is>
+      </c>
+      <c r="G90" s="18" t="n">
+        <v>771</v>
+      </c>
+      <c r="H90" s="19" t="inlineStr">
+        <is>
+          <t>940848</t>
+        </is>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>30 kg</t>
+        </is>
+      </c>
+      <c r="J90" s="18" t="n">
+        <v>772</v>
+      </c>
+      <c r="K90" s="19" t="inlineStr">
+        <is>
+          <t>940840</t>
+        </is>
+      </c>
+      <c r="L90" s="13" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
+      <c r="M90" s="18" t="inlineStr"/>
+      <c r="N90" s="19" t="inlineStr"/>
+      <c r="O90" s="13" t="inlineStr"/>
+      <c r="P90" s="18" t="inlineStr"/>
+      <c r="Q90" s="19" t="inlineStr"/>
+      <c r="R90" s="13" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="17" t="n"/>
-      <c r="B91" s="17" t="n"/>
-      <c r="C91" s="17" t="n"/>
-      <c r="D91" s="17" t="n"/>
-      <c r="E91" s="17" t="n"/>
-      <c r="F91" s="17" t="n"/>
-      <c r="G91" s="17" t="n"/>
-      <c r="H91" s="17" t="n"/>
-      <c r="I91" s="17" t="n"/>
-      <c r="J91" s="17" t="n"/>
-      <c r="K91" s="17" t="n"/>
-      <c r="L91" s="17" t="n"/>
-      <c r="M91" s="17" t="n"/>
-      <c r="N91" s="17" t="n"/>
-      <c r="O91" s="17" t="n"/>
-      <c r="P91" s="17" t="n"/>
-      <c r="Q91" s="17" t="n"/>
-      <c r="R91" s="17" t="n"/>
+      <c r="A91" s="18" t="n">
+        <v>773</v>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>940841</t>
+        </is>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
+      <c r="D91" s="18" t="n">
+        <v>755</v>
+      </c>
+      <c r="E91" s="19" t="inlineStr">
+        <is>
+          <t>123303</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="inlineStr">
+        <is>
+          <t>48 kg</t>
+        </is>
+      </c>
+      <c r="G91" s="18" t="n">
+        <v>753</v>
+      </c>
+      <c r="H91" s="19" t="inlineStr">
+        <is>
+          <t>123302</t>
+        </is>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
+      <c r="J91" s="18" t="n">
+        <v>749</v>
+      </c>
+      <c r="K91" s="19" t="inlineStr">
+        <is>
+          <t>123301</t>
+        </is>
+      </c>
+      <c r="L91" s="13" t="inlineStr">
+        <is>
+          <t>40 kg</t>
+        </is>
+      </c>
+      <c r="M91" s="18" t="inlineStr"/>
+      <c r="N91" s="19" t="inlineStr"/>
+      <c r="O91" s="13" t="inlineStr"/>
+      <c r="P91" s="18" t="inlineStr"/>
+      <c r="Q91" s="19" t="inlineStr"/>
+      <c r="R91" s="13" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="18" t="n">
@@ -22183,7 +22733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:J537"/>
+  <dimension ref="B2:J562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -22589,13 +23139,13 @@
         <v>42</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I18" s="23" t="n">
-        <v>1229</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -22619,13 +23169,13 @@
         <v>42</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I19" s="25" t="n">
-        <v>959</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -22649,13 +23199,13 @@
         <v>42</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>1005</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -38359,21 +38909,21 @@
         <v>362</v>
       </c>
       <c r="C390" s="31" t="n">
-        <v>738</v>
+        <v>768</v>
       </c>
       <c r="D390" s="32" t="inlineStr">
         <is>
-          <t>39166</t>
+          <t>123144</t>
         </is>
       </c>
       <c r="E390" s="30" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F390" s="33" t="inlineStr">
         <is>
-          <t>32 kg</t>
+          <t>39 kg</t>
         </is>
       </c>
       <c r="G390" s="30" t="inlineStr">
@@ -38383,12 +38933,12 @@
       </c>
       <c r="H390" s="30" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I390" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J390" s="30" t="inlineStr">
@@ -38402,16 +38952,16 @@
         <v>363</v>
       </c>
       <c r="C391" s="18" t="n">
-        <v>734</v>
+        <v>769</v>
       </c>
       <c r="D391" s="19" t="inlineStr">
         <is>
-          <t>39551</t>
+          <t>123305</t>
         </is>
       </c>
       <c r="E391" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F391" s="29" t="inlineStr">
@@ -38426,12 +38976,12 @@
       </c>
       <c r="H391" s="28" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I391" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J391" s="28" t="inlineStr">
@@ -38445,16 +38995,16 @@
         <v>364</v>
       </c>
       <c r="C392" s="31" t="n">
-        <v>735</v>
+        <v>767</v>
       </c>
       <c r="D392" s="32" t="inlineStr">
         <is>
-          <t>39549</t>
+          <t>940843</t>
         </is>
       </c>
       <c r="E392" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F392" s="33" t="inlineStr">
@@ -38469,12 +39019,12 @@
       </c>
       <c r="H392" s="30" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I392" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J392" s="30" t="inlineStr">
@@ -38488,21 +39038,21 @@
         <v>365</v>
       </c>
       <c r="C393" s="18" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D393" s="19" t="inlineStr">
         <is>
-          <t>39167</t>
+          <t>39166</t>
         </is>
       </c>
       <c r="E393" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F393" s="29" t="inlineStr">
         <is>
-          <t>35 kg</t>
+          <t>32 kg</t>
         </is>
       </c>
       <c r="G393" s="28" t="inlineStr">
@@ -38517,7 +39067,7 @@
       </c>
       <c r="I393" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J393" s="28" t="inlineStr">
@@ -38531,21 +39081,21 @@
         <v>366</v>
       </c>
       <c r="C394" s="31" t="n">
-        <v>611</v>
+        <v>734</v>
       </c>
       <c r="D394" s="32" t="inlineStr">
         <is>
-          <t>34394</t>
+          <t>39551</t>
         </is>
       </c>
       <c r="E394" s="30" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F394" s="33" t="inlineStr">
         <is>
-          <t>35.0 kg</t>
+          <t>35 kg</t>
         </is>
       </c>
       <c r="G394" s="30" t="inlineStr">
@@ -38555,12 +39105,12 @@
       </c>
       <c r="H394" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I394" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J394" s="30" t="inlineStr">
@@ -38574,21 +39124,21 @@
         <v>367</v>
       </c>
       <c r="C395" s="18" t="n">
-        <v>587</v>
+        <v>735</v>
       </c>
       <c r="D395" s="19" t="inlineStr">
         <is>
-          <t>34808</t>
+          <t>39549</t>
         </is>
       </c>
       <c r="E395" s="28" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F395" s="29" t="inlineStr">
         <is>
-          <t>47.0 kg</t>
+          <t>35 kg</t>
         </is>
       </c>
       <c r="G395" s="28" t="inlineStr">
@@ -38598,12 +39148,12 @@
       </c>
       <c r="H395" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I395" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J395" s="28" t="inlineStr">
@@ -38617,21 +39167,21 @@
         <v>368</v>
       </c>
       <c r="C396" s="31" t="n">
-        <v>247</v>
+        <v>737</v>
       </c>
       <c r="D396" s="32" t="inlineStr">
         <is>
-          <t>30689</t>
+          <t>39167</t>
         </is>
       </c>
       <c r="E396" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F396" s="33" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>35 kg</t>
         </is>
       </c>
       <c r="G396" s="30" t="inlineStr">
@@ -38641,12 +39191,12 @@
       </c>
       <c r="H396" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I396" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J396" s="30" t="inlineStr">
@@ -38660,21 +39210,21 @@
         <v>369</v>
       </c>
       <c r="C397" s="18" t="n">
-        <v>414</v>
+        <v>770</v>
       </c>
       <c r="D397" s="19" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>940844</t>
         </is>
       </c>
       <c r="E397" s="28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F397" s="29" t="inlineStr">
         <is>
-          <t>44.0 kg</t>
+          <t>44 kg</t>
         </is>
       </c>
       <c r="G397" s="28" t="inlineStr">
@@ -38684,12 +39234,12 @@
       </c>
       <c r="H397" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I397" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J397" s="28" t="inlineStr">
@@ -38703,21 +39253,21 @@
         <v>370</v>
       </c>
       <c r="C398" s="31" t="n">
-        <v>346</v>
+        <v>764</v>
       </c>
       <c r="D398" s="32" t="inlineStr">
         <is>
-          <t>30624</t>
+          <t>123304</t>
         </is>
       </c>
       <c r="E398" s="30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F398" s="33" t="inlineStr">
         <is>
-          <t>34 kg</t>
+          <t>44 kg</t>
         </is>
       </c>
       <c r="G398" s="30" t="inlineStr">
@@ -38727,12 +39277,12 @@
       </c>
       <c r="H398" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I398" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J398" s="30" t="inlineStr">
@@ -38746,21 +39296,21 @@
         <v>371</v>
       </c>
       <c r="C399" s="18" t="n">
-        <v>338</v>
+        <v>611</v>
       </c>
       <c r="D399" s="19" t="inlineStr">
         <is>
-          <t>30172</t>
+          <t>34394</t>
         </is>
       </c>
       <c r="E399" s="28" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F399" s="29" t="inlineStr">
         <is>
-          <t>31.0 kg</t>
+          <t>35.0 kg</t>
         </is>
       </c>
       <c r="G399" s="28" t="inlineStr">
@@ -38775,7 +39325,7 @@
       </c>
       <c r="I399" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J399" s="28" t="inlineStr">
@@ -38789,21 +39339,21 @@
         <v>372</v>
       </c>
       <c r="C400" s="31" t="n">
-        <v>513</v>
+        <v>587</v>
       </c>
       <c r="D400" s="32" t="inlineStr">
         <is>
-          <t>34240</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="E400" s="30" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F400" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>47.0 kg</t>
         </is>
       </c>
       <c r="G400" s="30" t="inlineStr">
@@ -38813,12 +39363,12 @@
       </c>
       <c r="H400" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I400" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J400" s="30" t="inlineStr">
@@ -38832,21 +39382,21 @@
         <v>373</v>
       </c>
       <c r="C401" s="18" t="n">
-        <v>565</v>
+        <v>247</v>
       </c>
       <c r="D401" s="19" t="inlineStr">
         <is>
-          <t>33463</t>
+          <t>30689</t>
         </is>
       </c>
       <c r="E401" s="28" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F401" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>34.0 kg</t>
         </is>
       </c>
       <c r="G401" s="28" t="inlineStr">
@@ -38856,12 +39406,12 @@
       </c>
       <c r="H401" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I401" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J401" s="28" t="inlineStr">
@@ -38875,21 +39425,21 @@
         <v>374</v>
       </c>
       <c r="C402" s="31" t="n">
-        <v>154</v>
+        <v>414</v>
       </c>
       <c r="D402" s="32" t="inlineStr">
         <is>
-          <t>943615</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="E402" s="30" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F402" s="33" t="inlineStr">
         <is>
-          <t>35.0 kg</t>
+          <t>44.0 kg</t>
         </is>
       </c>
       <c r="G402" s="30" t="inlineStr">
@@ -38899,12 +39449,12 @@
       </c>
       <c r="H402" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I402" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J402" s="30" t="inlineStr">
@@ -38918,21 +39468,21 @@
         <v>375</v>
       </c>
       <c r="C403" s="18" t="n">
-        <v>505</v>
+        <v>346</v>
       </c>
       <c r="D403" s="19" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="E403" s="28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F403" s="29" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
+          <t>34 kg</t>
         </is>
       </c>
       <c r="G403" s="28" t="inlineStr">
@@ -38942,12 +39492,12 @@
       </c>
       <c r="H403" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I403" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J403" s="28" t="inlineStr">
@@ -38961,21 +39511,21 @@
         <v>376</v>
       </c>
       <c r="C404" s="31" t="n">
-        <v>259</v>
+        <v>338</v>
       </c>
       <c r="D404" s="32" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>30172</t>
         </is>
       </c>
       <c r="E404" s="30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F404" s="33" t="inlineStr">
         <is>
-          <t>46.0 kg</t>
+          <t>31.0 kg</t>
         </is>
       </c>
       <c r="G404" s="30" t="inlineStr">
@@ -38985,12 +39535,12 @@
       </c>
       <c r="H404" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I404" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J404" s="30" t="inlineStr">
@@ -39004,21 +39554,21 @@
         <v>377</v>
       </c>
       <c r="C405" s="18" t="n">
-        <v>228</v>
+        <v>513</v>
       </c>
       <c r="D405" s="19" t="inlineStr">
         <is>
-          <t>30695</t>
+          <t>34240</t>
         </is>
       </c>
       <c r="E405" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F405" s="29" t="inlineStr">
         <is>
-          <t>40.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G405" s="28" t="inlineStr">
@@ -39033,7 +39583,7 @@
       </c>
       <c r="I405" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J405" s="28" t="inlineStr">
@@ -39047,21 +39597,21 @@
         <v>378</v>
       </c>
       <c r="C406" s="31" t="n">
-        <v>598</v>
+        <v>565</v>
       </c>
       <c r="D406" s="32" t="inlineStr">
         <is>
-          <t>34363</t>
+          <t>33463</t>
         </is>
       </c>
       <c r="E406" s="30" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F406" s="33" t="inlineStr">
         <is>
-          <t>47.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G406" s="30" t="inlineStr">
@@ -39071,12 +39621,12 @@
       </c>
       <c r="H406" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I406" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J406" s="30" t="inlineStr">
@@ -39090,21 +39640,21 @@
         <v>379</v>
       </c>
       <c r="C407" s="18" t="n">
-        <v>567</v>
+        <v>154</v>
       </c>
       <c r="D407" s="19" t="inlineStr">
         <is>
-          <t>34342</t>
+          <t>943615</t>
         </is>
       </c>
       <c r="E407" s="28" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F407" s="29" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>35.0 kg</t>
         </is>
       </c>
       <c r="G407" s="28" t="inlineStr">
@@ -39114,12 +39664,12 @@
       </c>
       <c r="H407" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I407" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J407" s="28" t="inlineStr">
@@ -39133,21 +39683,21 @@
         <v>380</v>
       </c>
       <c r="C408" s="31" t="n">
-        <v>422</v>
+        <v>505</v>
       </c>
       <c r="D408" s="32" t="inlineStr">
         <is>
-          <t>30455</t>
+          <t>34096</t>
         </is>
       </c>
       <c r="E408" s="30" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F408" s="33" t="inlineStr">
         <is>
-          <t>49.0 kg</t>
+          <t>39.0 kg</t>
         </is>
       </c>
       <c r="G408" s="30" t="inlineStr">
@@ -39157,12 +39707,12 @@
       </c>
       <c r="H408" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I408" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J408" s="30" t="inlineStr">
@@ -39176,21 +39726,21 @@
         <v>381</v>
       </c>
       <c r="C409" s="18" t="n">
-        <v>347</v>
+        <v>259</v>
       </c>
       <c r="D409" s="19" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>30164</t>
         </is>
       </c>
       <c r="E409" s="28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F409" s="29" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="G409" s="28" t="inlineStr">
@@ -39200,12 +39750,12 @@
       </c>
       <c r="H409" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I409" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J409" s="28" t="inlineStr">
@@ -39219,21 +39769,21 @@
         <v>382</v>
       </c>
       <c r="C410" s="31" t="n">
-        <v>327</v>
+        <v>228</v>
       </c>
       <c r="D410" s="32" t="inlineStr">
         <is>
-          <t>30161</t>
+          <t>30695</t>
         </is>
       </c>
       <c r="E410" s="30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F410" s="33" t="inlineStr">
         <is>
-          <t>41.0 kg</t>
+          <t>40.0 kg</t>
         </is>
       </c>
       <c r="G410" s="30" t="inlineStr">
@@ -39243,12 +39793,12 @@
       </c>
       <c r="H410" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I410" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J410" s="30" t="inlineStr">
@@ -39262,21 +39812,21 @@
         <v>383</v>
       </c>
       <c r="C411" s="18" t="n">
-        <v>355</v>
+        <v>598</v>
       </c>
       <c r="D411" s="19" t="inlineStr">
         <is>
-          <t>30316</t>
+          <t>34363</t>
         </is>
       </c>
       <c r="E411" s="28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F411" s="29" t="inlineStr">
         <is>
-          <t>48.0 kg</t>
+          <t>47.0 kg</t>
         </is>
       </c>
       <c r="G411" s="28" t="inlineStr">
@@ -39291,7 +39841,7 @@
       </c>
       <c r="I411" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J411" s="28" t="inlineStr">
@@ -39305,21 +39855,21 @@
         <v>384</v>
       </c>
       <c r="C412" s="31" t="n">
-        <v>596</v>
+        <v>567</v>
       </c>
       <c r="D412" s="32" t="inlineStr">
         <is>
-          <t>34362</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="E412" s="30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F412" s="33" t="inlineStr">
         <is>
-          <t>45.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G412" s="30" t="inlineStr">
@@ -39329,12 +39879,12 @@
       </c>
       <c r="H412" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I412" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J412" s="30" t="inlineStr">
@@ -39348,21 +39898,21 @@
         <v>385</v>
       </c>
       <c r="C413" s="18" t="n">
-        <v>534</v>
+        <v>422</v>
       </c>
       <c r="D413" s="19" t="inlineStr">
         <is>
-          <t>34231</t>
+          <t>30455</t>
         </is>
       </c>
       <c r="E413" s="28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F413" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>49.0 kg</t>
         </is>
       </c>
       <c r="G413" s="28" t="inlineStr">
@@ -39372,12 +39922,12 @@
       </c>
       <c r="H413" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I413" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J413" s="28" t="inlineStr">
@@ -39391,21 +39941,21 @@
         <v>386</v>
       </c>
       <c r="C414" s="31" t="n">
-        <v>289</v>
+        <v>347</v>
       </c>
       <c r="D414" s="32" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>30622</t>
         </is>
       </c>
       <c r="E414" s="30" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F414" s="33" t="inlineStr">
         <is>
-          <t>47 kg</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G414" s="30" t="inlineStr">
@@ -39415,12 +39965,12 @@
       </c>
       <c r="H414" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I414" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J414" s="30" t="inlineStr">
@@ -39434,21 +39984,21 @@
         <v>387</v>
       </c>
       <c r="C415" s="18" t="n">
-        <v>410</v>
+        <v>327</v>
       </c>
       <c r="D415" s="19" t="inlineStr">
         <is>
-          <t>31625</t>
+          <t>30161</t>
         </is>
       </c>
       <c r="E415" s="28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F415" s="29" t="inlineStr">
         <is>
-          <t>29.0 kg</t>
+          <t>41.0 kg</t>
         </is>
       </c>
       <c r="G415" s="28" t="inlineStr">
@@ -39458,12 +40008,12 @@
       </c>
       <c r="H415" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I415" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J415" s="28" t="inlineStr">
@@ -39477,21 +40027,21 @@
         <v>388</v>
       </c>
       <c r="C416" s="31" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D416" s="32" t="inlineStr">
         <is>
-          <t>30181</t>
+          <t>30316</t>
         </is>
       </c>
       <c r="E416" s="30" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F416" s="33" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
+          <t>48.0 kg</t>
         </is>
       </c>
       <c r="G416" s="30" t="inlineStr">
@@ -39501,12 +40051,12 @@
       </c>
       <c r="H416" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I416" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J416" s="30" t="inlineStr">
@@ -39520,21 +40070,21 @@
         <v>389</v>
       </c>
       <c r="C417" s="18" t="n">
-        <v>404</v>
+        <v>596</v>
       </c>
       <c r="D417" s="19" t="inlineStr">
         <is>
-          <t>31632</t>
+          <t>34362</t>
         </is>
       </c>
       <c r="E417" s="28" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F417" s="29" t="inlineStr">
         <is>
-          <t>49.0 kg</t>
+          <t>45.0 kg</t>
         </is>
       </c>
       <c r="G417" s="28" t="inlineStr">
@@ -39549,7 +40099,7 @@
       </c>
       <c r="I417" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J417" s="28" t="inlineStr">
@@ -39563,36 +40113,36 @@
         <v>390</v>
       </c>
       <c r="C418" s="31" t="n">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="D418" s="32" t="inlineStr">
         <is>
-          <t>34207</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="E418" s="30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F418" s="33" t="inlineStr">
         <is>
-          <t>44.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G418" s="30" t="inlineStr">
         <is>
-          <t>BLOK 12</t>
+          <t>BLOK 11</t>
         </is>
       </c>
       <c r="H418" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I418" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J418" s="30" t="inlineStr">
@@ -39606,36 +40156,36 @@
         <v>391</v>
       </c>
       <c r="C419" s="18" t="n">
-        <v>208</v>
+        <v>289</v>
       </c>
       <c r="D419" s="19" t="inlineStr">
         <is>
-          <t>943648</t>
+          <t>31701</t>
         </is>
       </c>
       <c r="E419" s="28" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F419" s="29" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>47 kg</t>
         </is>
       </c>
       <c r="G419" s="28" t="inlineStr">
         <is>
-          <t>BLOK 12</t>
+          <t>BLOK 11</t>
         </is>
       </c>
       <c r="H419" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I419" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J419" s="28" t="inlineStr">
@@ -39649,36 +40199,36 @@
         <v>392</v>
       </c>
       <c r="C420" s="31" t="n">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="D420" s="32" t="inlineStr">
         <is>
-          <t>30634</t>
+          <t>31625</t>
         </is>
       </c>
       <c r="E420" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F420" s="33" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
+          <t>29.0 kg</t>
         </is>
       </c>
       <c r="G420" s="30" t="inlineStr">
         <is>
-          <t>BLOK 12</t>
+          <t>BLOK 11</t>
         </is>
       </c>
       <c r="H420" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I420" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J420" s="30" t="inlineStr">
@@ -39692,36 +40242,36 @@
         <v>393</v>
       </c>
       <c r="C421" s="18" t="n">
-        <v>169</v>
+        <v>357</v>
       </c>
       <c r="D421" s="19" t="inlineStr">
         <is>
-          <t>30327</t>
+          <t>30181</t>
         </is>
       </c>
       <c r="E421" s="28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F421" s="29" t="inlineStr">
         <is>
-          <t>35.0 kg</t>
+          <t>39.0 kg</t>
         </is>
       </c>
       <c r="G421" s="28" t="inlineStr">
         <is>
-          <t>BLOK 12</t>
+          <t>BLOK 11</t>
         </is>
       </c>
       <c r="H421" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I421" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J421" s="28" t="inlineStr">
@@ -39735,36 +40285,36 @@
         <v>394</v>
       </c>
       <c r="C422" s="31" t="n">
-        <v>216</v>
+        <v>404</v>
       </c>
       <c r="D422" s="32" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>31632</t>
         </is>
       </c>
       <c r="E422" s="30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F422" s="33" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
+          <t>49.0 kg</t>
         </is>
       </c>
       <c r="G422" s="30" t="inlineStr">
         <is>
-          <t>BLOK 12</t>
+          <t>BLOK 11</t>
         </is>
       </c>
       <c r="H422" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I422" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J422" s="30" t="inlineStr">
@@ -39778,21 +40328,21 @@
         <v>395</v>
       </c>
       <c r="C423" s="18" t="n">
-        <v>459</v>
+        <v>747</v>
       </c>
       <c r="D423" s="19" t="inlineStr">
         <is>
-          <t>34128</t>
+          <t>123139</t>
         </is>
       </c>
       <c r="E423" s="28" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F423" s="29" t="inlineStr">
         <is>
-          <t>42.0 kg</t>
+          <t>45 kg</t>
         </is>
       </c>
       <c r="G423" s="28" t="inlineStr">
@@ -39802,12 +40352,12 @@
       </c>
       <c r="H423" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I423" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J423" s="28" t="inlineStr">
@@ -39821,21 +40371,21 @@
         <v>396</v>
       </c>
       <c r="C424" s="31" t="n">
-        <v>519</v>
+        <v>787</v>
       </c>
       <c r="D424" s="32" t="inlineStr">
         <is>
-          <t>34229</t>
+          <t>940846</t>
         </is>
       </c>
       <c r="E424" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F424" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>30 kg</t>
         </is>
       </c>
       <c r="G424" s="30" t="inlineStr">
@@ -39845,12 +40395,12 @@
       </c>
       <c r="H424" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I424" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J424" s="30" t="inlineStr">
@@ -39864,21 +40414,21 @@
         <v>397</v>
       </c>
       <c r="C425" s="18" t="n">
-        <v>529</v>
+        <v>748</v>
       </c>
       <c r="D425" s="19" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>123140</t>
         </is>
       </c>
       <c r="E425" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F425" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>34 kg</t>
         </is>
       </c>
       <c r="G425" s="28" t="inlineStr">
@@ -39888,12 +40438,12 @@
       </c>
       <c r="H425" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I425" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J425" s="28" t="inlineStr">
@@ -39907,21 +40457,21 @@
         <v>398</v>
       </c>
       <c r="C426" s="31" t="n">
-        <v>445</v>
+        <v>788</v>
       </c>
       <c r="D426" s="32" t="inlineStr">
         <is>
-          <t>30751</t>
+          <t>123306</t>
         </is>
       </c>
       <c r="E426" s="30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F426" s="33" t="inlineStr">
         <is>
-          <t>31.0 kg</t>
+          <t>34 kg</t>
         </is>
       </c>
       <c r="G426" s="30" t="inlineStr">
@@ -39931,12 +40481,12 @@
       </c>
       <c r="H426" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I426" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J426" s="30" t="inlineStr">
@@ -39950,21 +40500,21 @@
         <v>399</v>
       </c>
       <c r="C427" s="18" t="n">
-        <v>403</v>
+        <v>762</v>
       </c>
       <c r="D427" s="19" t="inlineStr">
         <is>
-          <t>31626</t>
+          <t>123143</t>
         </is>
       </c>
       <c r="E427" s="28" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F427" s="29" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>42 kg</t>
         </is>
       </c>
       <c r="G427" s="28" t="inlineStr">
@@ -39974,12 +40524,12 @@
       </c>
       <c r="H427" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I427" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J427" s="28" t="inlineStr">
@@ -39993,21 +40543,21 @@
         <v>400</v>
       </c>
       <c r="C428" s="31" t="n">
-        <v>361</v>
+        <v>765</v>
       </c>
       <c r="D428" s="32" t="inlineStr">
         <is>
-          <t>30338</t>
+          <t>940842</t>
         </is>
       </c>
       <c r="E428" s="30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F428" s="33" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>50 kg</t>
         </is>
       </c>
       <c r="G428" s="30" t="inlineStr">
@@ -40017,12 +40567,12 @@
       </c>
       <c r="H428" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I428" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J428" s="30" t="inlineStr">
@@ -40036,21 +40586,21 @@
         <v>401</v>
       </c>
       <c r="C429" s="18" t="n">
-        <v>455</v>
+        <v>715</v>
       </c>
       <c r="D429" s="19" t="inlineStr">
         <is>
-          <t>30666</t>
+          <t>940845</t>
         </is>
       </c>
       <c r="E429" s="28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F429" s="29" t="inlineStr">
         <is>
-          <t>43.0 kg</t>
+          <t>46 kg</t>
         </is>
       </c>
       <c r="G429" s="28" t="inlineStr">
@@ -40060,12 +40610,12 @@
       </c>
       <c r="H429" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I429" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J429" s="28" t="inlineStr">
@@ -40079,11 +40629,11 @@
         <v>402</v>
       </c>
       <c r="C430" s="31" t="n">
-        <v>30</v>
+        <v>786</v>
       </c>
       <c r="D430" s="32" t="inlineStr">
         <is>
-          <t>943643</t>
+          <t>123307</t>
         </is>
       </c>
       <c r="E430" s="30" t="inlineStr">
@@ -40093,7 +40643,7 @@
       </c>
       <c r="F430" s="33" t="inlineStr">
         <is>
-          <t>45.0 kg</t>
+          <t>36 kg</t>
         </is>
       </c>
       <c r="G430" s="30" t="inlineStr">
@@ -40103,12 +40653,12 @@
       </c>
       <c r="H430" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I430" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J430" s="30" t="inlineStr">
@@ -40122,21 +40672,21 @@
         <v>403</v>
       </c>
       <c r="C431" s="18" t="n">
-        <v>528</v>
+        <v>789</v>
       </c>
       <c r="D431" s="19" t="inlineStr">
         <is>
-          <t>34417</t>
+          <t>123145</t>
         </is>
       </c>
       <c r="E431" s="28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F431" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>34 kg</t>
         </is>
       </c>
       <c r="G431" s="28" t="inlineStr">
@@ -40146,12 +40696,12 @@
       </c>
       <c r="H431" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I431" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J431" s="28" t="inlineStr">
@@ -40165,21 +40715,21 @@
         <v>404</v>
       </c>
       <c r="C432" s="31" t="n">
-        <v>312</v>
+        <v>763</v>
       </c>
       <c r="D432" s="32" t="inlineStr">
         <is>
-          <t>30626</t>
+          <t>123142</t>
         </is>
       </c>
       <c r="E432" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F432" s="33" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
+          <t>42 kg</t>
         </is>
       </c>
       <c r="G432" s="30" t="inlineStr">
@@ -40189,12 +40739,12 @@
       </c>
       <c r="H432" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I432" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J432" s="30" t="inlineStr">
@@ -40208,21 +40758,21 @@
         <v>405</v>
       </c>
       <c r="C433" s="18" t="n">
-        <v>316</v>
+        <v>761</v>
       </c>
       <c r="D433" s="19" t="inlineStr">
         <is>
-          <t>30449</t>
+          <t>123141</t>
         </is>
       </c>
       <c r="E433" s="28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F433" s="29" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>44 kg</t>
         </is>
       </c>
       <c r="G433" s="28" t="inlineStr">
@@ -40232,12 +40782,12 @@
       </c>
       <c r="H433" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I433" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J433" s="28" t="inlineStr">
@@ -40251,21 +40801,21 @@
         <v>406</v>
       </c>
       <c r="C434" s="31" t="n">
-        <v>407</v>
+        <v>766</v>
       </c>
       <c r="D434" s="32" t="inlineStr">
         <is>
-          <t>30443</t>
+          <t>940847</t>
         </is>
       </c>
       <c r="E434" s="30" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F434" s="33" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
+          <t>37 kg</t>
         </is>
       </c>
       <c r="G434" s="30" t="inlineStr">
@@ -40275,12 +40825,12 @@
       </c>
       <c r="H434" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I434" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J434" s="30" t="inlineStr">
@@ -40294,21 +40844,21 @@
         <v>407</v>
       </c>
       <c r="C435" s="18" t="n">
-        <v>231</v>
+        <v>517</v>
       </c>
       <c r="D435" s="19" t="inlineStr">
         <is>
-          <t>31732</t>
+          <t>34207</t>
         </is>
       </c>
       <c r="E435" s="28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F435" s="29" t="inlineStr">
         <is>
-          <t>41.0 kg</t>
+          <t>44.0 kg</t>
         </is>
       </c>
       <c r="G435" s="28" t="inlineStr">
@@ -40318,12 +40868,12 @@
       </c>
       <c r="H435" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I435" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J435" s="28" t="inlineStr">
@@ -40337,21 +40887,21 @@
         <v>408</v>
       </c>
       <c r="C436" s="31" t="n">
-        <v>512</v>
+        <v>208</v>
       </c>
       <c r="D436" s="32" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>943648</t>
         </is>
       </c>
       <c r="E436" s="30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F436" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G436" s="30" t="inlineStr">
@@ -40361,12 +40911,12 @@
       </c>
       <c r="H436" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I436" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J436" s="30" t="inlineStr">
@@ -40380,21 +40930,21 @@
         <v>409</v>
       </c>
       <c r="C437" s="18" t="n">
-        <v>545</v>
+        <v>342</v>
       </c>
       <c r="D437" s="19" t="inlineStr">
         <is>
-          <t>34250</t>
+          <t>30634</t>
         </is>
       </c>
       <c r="E437" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F437" s="29" t="inlineStr">
         <is>
-          <t>32.0 kg</t>
+          <t>39.0 kg</t>
         </is>
       </c>
       <c r="G437" s="28" t="inlineStr">
@@ -40404,12 +40954,12 @@
       </c>
       <c r="H437" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I437" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J437" s="28" t="inlineStr">
@@ -40423,21 +40973,21 @@
         <v>410</v>
       </c>
       <c r="C438" s="31" t="n">
-        <v>394</v>
+        <v>169</v>
       </c>
       <c r="D438" s="32" t="inlineStr">
         <is>
-          <t>30336</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="E438" s="30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F438" s="33" t="inlineStr">
         <is>
-          <t>31.0 kg</t>
+          <t>35.0 kg</t>
         </is>
       </c>
       <c r="G438" s="30" t="inlineStr">
@@ -40447,12 +40997,12 @@
       </c>
       <c r="H438" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I438" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J438" s="30" t="inlineStr">
@@ -40466,21 +41016,21 @@
         <v>411</v>
       </c>
       <c r="C439" s="18" t="n">
-        <v>322</v>
+        <v>216</v>
       </c>
       <c r="D439" s="19" t="inlineStr">
         <is>
-          <t>30159</t>
+          <t>32276</t>
         </is>
       </c>
       <c r="E439" s="28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F439" s="29" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>39.0 kg</t>
         </is>
       </c>
       <c r="G439" s="28" t="inlineStr">
@@ -40490,12 +41040,12 @@
       </c>
       <c r="H439" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I439" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J439" s="28" t="inlineStr">
@@ -40509,21 +41059,21 @@
         <v>412</v>
       </c>
       <c r="C440" s="31" t="n">
-        <v>335</v>
+        <v>459</v>
       </c>
       <c r="D440" s="32" t="inlineStr">
         <is>
-          <t>30144</t>
+          <t>34128</t>
         </is>
       </c>
       <c r="E440" s="30" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F440" s="33" t="inlineStr">
         <is>
-          <t>46.0 kg</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G440" s="30" t="inlineStr">
@@ -40533,12 +41083,12 @@
       </c>
       <c r="H440" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I440" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J440" s="30" t="inlineStr">
@@ -40552,21 +41102,21 @@
         <v>413</v>
       </c>
       <c r="C441" s="18" t="n">
-        <v>264</v>
+        <v>519</v>
       </c>
       <c r="D441" s="19" t="inlineStr">
         <is>
-          <t>30631</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="E441" s="28" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F441" s="29" t="inlineStr">
         <is>
-          <t>35.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G441" s="28" t="inlineStr">
@@ -40576,12 +41126,12 @@
       </c>
       <c r="H441" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I441" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J441" s="28" t="inlineStr">
@@ -40595,11 +41145,11 @@
         <v>414</v>
       </c>
       <c r="C442" s="31" t="n">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="D442" s="32" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>34236</t>
         </is>
       </c>
       <c r="E442" s="30" t="inlineStr">
@@ -40614,17 +41164,17 @@
       </c>
       <c r="G442" s="30" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H442" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I442" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J442" s="30" t="inlineStr">
@@ -40638,36 +41188,36 @@
         <v>415</v>
       </c>
       <c r="C443" s="18" t="n">
-        <v>531</v>
+        <v>445</v>
       </c>
       <c r="D443" s="19" t="inlineStr">
         <is>
-          <t>34235</t>
+          <t>30751</t>
         </is>
       </c>
       <c r="E443" s="28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F443" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>31.0 kg</t>
         </is>
       </c>
       <c r="G443" s="28" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H443" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I443" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J443" s="28" t="inlineStr">
@@ -40681,36 +41231,36 @@
         <v>416</v>
       </c>
       <c r="C444" s="31" t="n">
-        <v>63</v>
+        <v>403</v>
       </c>
       <c r="D444" s="32" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>31626</t>
         </is>
       </c>
       <c r="E444" s="30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F444" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>33.0 kg</t>
         </is>
       </c>
       <c r="G444" s="30" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H444" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I444" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J444" s="30" t="inlineStr">
@@ -40724,36 +41274,36 @@
         <v>417</v>
       </c>
       <c r="C445" s="18" t="n">
-        <v>168</v>
+        <v>361</v>
       </c>
       <c r="D445" s="19" t="inlineStr">
         <is>
-          <t>31738</t>
+          <t>30338</t>
         </is>
       </c>
       <c r="E445" s="28" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F445" s="29" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>34.0 kg</t>
         </is>
       </c>
       <c r="G445" s="28" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H445" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I445" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J445" s="28" t="inlineStr">
@@ -40767,36 +41317,36 @@
         <v>418</v>
       </c>
       <c r="C446" s="31" t="n">
-        <v>372</v>
+        <v>455</v>
       </c>
       <c r="D446" s="32" t="inlineStr">
         <is>
-          <t>30629</t>
+          <t>30666</t>
         </is>
       </c>
       <c r="E446" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F446" s="33" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>43.0 kg</t>
         </is>
       </c>
       <c r="G446" s="30" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H446" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I446" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J446" s="30" t="inlineStr">
@@ -40810,36 +41360,36 @@
         <v>419</v>
       </c>
       <c r="C447" s="18" t="n">
-        <v>402</v>
+        <v>30</v>
       </c>
       <c r="D447" s="19" t="inlineStr">
         <is>
-          <t>31628</t>
+          <t>943643</t>
         </is>
       </c>
       <c r="E447" s="28" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F447" s="29" t="inlineStr">
         <is>
-          <t>35.0 kg</t>
+          <t>45.0 kg</t>
         </is>
       </c>
       <c r="G447" s="28" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H447" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I447" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J447" s="28" t="inlineStr">
@@ -40853,36 +41403,36 @@
         <v>420</v>
       </c>
       <c r="C448" s="31" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D448" s="32" t="inlineStr">
         <is>
-          <t>34239</t>
+          <t>34417</t>
         </is>
       </c>
       <c r="E448" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F448" s="33" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G448" s="30" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H448" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I448" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J448" s="30" t="inlineStr">
@@ -40896,36 +41446,36 @@
         <v>421</v>
       </c>
       <c r="C449" s="18" t="n">
-        <v>533</v>
+        <v>312</v>
       </c>
       <c r="D449" s="19" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>30626</t>
         </is>
       </c>
       <c r="E449" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F449" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>39.0 kg</t>
         </is>
       </c>
       <c r="G449" s="28" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H449" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I449" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J449" s="28" t="inlineStr">
@@ -40939,36 +41489,36 @@
         <v>422</v>
       </c>
       <c r="C450" s="31" t="n">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="D450" s="32" t="inlineStr">
         <is>
-          <t>31735</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="E450" s="30" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F450" s="33" t="inlineStr">
         <is>
-          <t>46.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G450" s="30" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H450" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I450" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J450" s="30" t="inlineStr">
@@ -40982,36 +41532,36 @@
         <v>423</v>
       </c>
       <c r="C451" s="18" t="n">
-        <v>461</v>
+        <v>407</v>
       </c>
       <c r="D451" s="19" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>30443</t>
         </is>
       </c>
       <c r="E451" s="28" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F451" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>39.0 kg</t>
         </is>
       </c>
       <c r="G451" s="28" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H451" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I451" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J451" s="28" t="inlineStr">
@@ -41025,36 +41575,36 @@
         <v>424</v>
       </c>
       <c r="C452" s="31" t="n">
-        <v>446</v>
+        <v>231</v>
       </c>
       <c r="D452" s="32" t="inlineStr">
         <is>
-          <t>30754</t>
+          <t>31732</t>
         </is>
       </c>
       <c r="E452" s="30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F452" s="33" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>41.0 kg</t>
         </is>
       </c>
       <c r="G452" s="30" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H452" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I452" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J452" s="30" t="inlineStr">
@@ -41068,36 +41618,36 @@
         <v>425</v>
       </c>
       <c r="C453" s="18" t="n">
-        <v>132</v>
+        <v>512</v>
       </c>
       <c r="D453" s="19" t="inlineStr">
         <is>
-          <t>30328</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="E453" s="28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F453" s="29" t="inlineStr">
         <is>
-          <t>39 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G453" s="28" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H453" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I453" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J453" s="28" t="inlineStr">
@@ -41111,11 +41661,11 @@
         <v>426</v>
       </c>
       <c r="C454" s="31" t="n">
-        <v>126</v>
+        <v>545</v>
       </c>
       <c r="D454" s="32" t="inlineStr">
         <is>
-          <t>943641</t>
+          <t>34250</t>
         </is>
       </c>
       <c r="E454" s="30" t="inlineStr">
@@ -41125,22 +41675,22 @@
       </c>
       <c r="F454" s="33" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>32.0 kg</t>
         </is>
       </c>
       <c r="G454" s="30" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H454" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I454" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J454" s="30" t="inlineStr">
@@ -41154,36 +41704,36 @@
         <v>427</v>
       </c>
       <c r="C455" s="18" t="n">
-        <v>16</v>
+        <v>394</v>
       </c>
       <c r="D455" s="19" t="inlineStr">
         <is>
-          <t>943642</t>
+          <t>30336</t>
         </is>
       </c>
       <c r="E455" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F455" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>31.0 kg</t>
         </is>
       </c>
       <c r="G455" s="28" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H455" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I455" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J455" s="28" t="inlineStr">
@@ -41197,36 +41747,36 @@
         <v>428</v>
       </c>
       <c r="C456" s="31" t="n">
-        <v>140</v>
+        <v>322</v>
       </c>
       <c r="D456" s="32" t="inlineStr">
         <is>
-          <t>31737</t>
+          <t>30159</t>
         </is>
       </c>
       <c r="E456" s="30" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F456" s="33" t="inlineStr">
         <is>
-          <t>49.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G456" s="30" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H456" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I456" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J456" s="30" t="inlineStr">
@@ -41240,36 +41790,36 @@
         <v>429</v>
       </c>
       <c r="C457" s="18" t="n">
-        <v>141</v>
+        <v>335</v>
       </c>
       <c r="D457" s="19" t="inlineStr">
         <is>
-          <t>31739</t>
+          <t>30144</t>
         </is>
       </c>
       <c r="E457" s="28" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F457" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="G457" s="28" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H457" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I457" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J457" s="28" t="inlineStr">
@@ -41283,36 +41833,36 @@
         <v>430</v>
       </c>
       <c r="C458" s="31" t="n">
-        <v>178</v>
+        <v>264</v>
       </c>
       <c r="D458" s="32" t="inlineStr">
         <is>
-          <t>30359</t>
+          <t>30631</t>
         </is>
       </c>
       <c r="E458" s="30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F458" s="33" t="inlineStr">
         <is>
-          <t>44.0 kg</t>
+          <t>35.0 kg</t>
         </is>
       </c>
       <c r="G458" s="30" t="inlineStr">
         <is>
-          <t>BLOK 13</t>
+          <t>BLOK 12</t>
         </is>
       </c>
       <c r="H458" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I458" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J458" s="30" t="inlineStr">
@@ -41326,11 +41876,11 @@
         <v>431</v>
       </c>
       <c r="C459" s="18" t="n">
-        <v>401</v>
+        <v>752</v>
       </c>
       <c r="D459" s="19" t="inlineStr">
         <is>
-          <t>31633</t>
+          <t>39325</t>
         </is>
       </c>
       <c r="E459" s="28" t="inlineStr">
@@ -41340,7 +41890,7 @@
       </c>
       <c r="F459" s="29" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>42 kg</t>
         </is>
       </c>
       <c r="G459" s="28" t="inlineStr">
@@ -41350,12 +41900,12 @@
       </c>
       <c r="H459" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I459" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J459" s="28" t="inlineStr">
@@ -41368,24 +41918,22 @@
       <c r="B460" s="30" t="n">
         <v>432</v>
       </c>
-      <c r="C460" s="31" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="C460" s="31" t="n">
+        <v>751</v>
       </c>
       <c r="D460" s="32" t="inlineStr">
         <is>
-          <t>34233</t>
+          <t>39200</t>
         </is>
       </c>
       <c r="E460" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F460" s="33" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>41 kg</t>
         </is>
       </c>
       <c r="G460" s="30" t="inlineStr">
@@ -41395,12 +41943,12 @@
       </c>
       <c r="H460" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I460" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J460" s="30" t="inlineStr">
@@ -41414,21 +41962,21 @@
         <v>433</v>
       </c>
       <c r="C461" s="18" t="n">
-        <v>541</v>
+        <v>771</v>
       </c>
       <c r="D461" s="19" t="inlineStr">
         <is>
-          <t>34461</t>
+          <t>940848</t>
         </is>
       </c>
       <c r="E461" s="28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F461" s="29" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>30 kg</t>
         </is>
       </c>
       <c r="G461" s="28" t="inlineStr">
@@ -41438,12 +41986,12 @@
       </c>
       <c r="H461" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I461" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J461" s="28" t="inlineStr">
@@ -41457,21 +42005,21 @@
         <v>434</v>
       </c>
       <c r="C462" s="31" t="n">
-        <v>173</v>
+        <v>772</v>
       </c>
       <c r="D462" s="32" t="inlineStr">
         <is>
-          <t>31734</t>
+          <t>940840</t>
         </is>
       </c>
       <c r="E462" s="30" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F462" s="33" t="inlineStr">
         <is>
-          <t>43.0 kg</t>
+          <t>35 kg</t>
         </is>
       </c>
       <c r="G462" s="30" t="inlineStr">
@@ -41481,12 +42029,12 @@
       </c>
       <c r="H462" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I462" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J462" s="30" t="inlineStr">
@@ -41500,11 +42048,11 @@
         <v>435</v>
       </c>
       <c r="C463" s="18" t="n">
-        <v>409</v>
+        <v>773</v>
       </c>
       <c r="D463" s="19" t="inlineStr">
         <is>
-          <t>30445</t>
+          <t>940841</t>
         </is>
       </c>
       <c r="E463" s="28" t="inlineStr">
@@ -41514,7 +42062,7 @@
       </c>
       <c r="F463" s="29" t="inlineStr">
         <is>
-          <t>42.0 kg</t>
+          <t>37 kg</t>
         </is>
       </c>
       <c r="G463" s="28" t="inlineStr">
@@ -41524,12 +42072,12 @@
       </c>
       <c r="H463" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I463" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J463" s="28" t="inlineStr">
@@ -41543,21 +42091,21 @@
         <v>436</v>
       </c>
       <c r="C464" s="31" t="n">
-        <v>442</v>
+        <v>755</v>
       </c>
       <c r="D464" s="32" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>123303</t>
         </is>
       </c>
       <c r="E464" s="30" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F464" s="33" t="inlineStr">
         <is>
-          <t>42.0 kg</t>
+          <t>48 kg</t>
         </is>
       </c>
       <c r="G464" s="30" t="inlineStr">
@@ -41567,12 +42115,12 @@
       </c>
       <c r="H464" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I464" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J464" s="30" t="inlineStr">
@@ -41586,21 +42134,21 @@
         <v>437</v>
       </c>
       <c r="C465" s="18" t="n">
-        <v>429</v>
+        <v>753</v>
       </c>
       <c r="D465" s="19" t="inlineStr">
         <is>
-          <t>30317</t>
+          <t>123302</t>
         </is>
       </c>
       <c r="E465" s="28" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F465" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>37 kg</t>
         </is>
       </c>
       <c r="G465" s="28" t="inlineStr">
@@ -41610,12 +42158,12 @@
       </c>
       <c r="H465" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I465" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J465" s="28" t="inlineStr">
@@ -41629,36 +42177,36 @@
         <v>438</v>
       </c>
       <c r="C466" s="31" t="n">
-        <v>532</v>
+        <v>749</v>
       </c>
       <c r="D466" s="32" t="inlineStr">
         <is>
-          <t>34232</t>
+          <t>123301</t>
         </is>
       </c>
       <c r="E466" s="30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F466" s="33" t="inlineStr">
         <is>
-          <t>43.0 kg</t>
+          <t>40 kg</t>
         </is>
       </c>
       <c r="G466" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H466" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I466" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J466" s="30" t="inlineStr">
@@ -41672,26 +42220,26 @@
         <v>439</v>
       </c>
       <c r="C467" s="18" t="n">
-        <v>571</v>
+        <v>535</v>
       </c>
       <c r="D467" s="19" t="inlineStr">
         <is>
-          <t>34462</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="E467" s="28" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F467" s="29" t="inlineStr">
         <is>
-          <t>47.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G467" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H467" s="28" t="inlineStr">
@@ -41701,7 +42249,7 @@
       </c>
       <c r="I467" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J467" s="28" t="inlineStr">
@@ -41715,26 +42263,26 @@
         <v>440</v>
       </c>
       <c r="C468" s="31" t="n">
-        <v>273</v>
+        <v>531</v>
       </c>
       <c r="D468" s="32" t="inlineStr">
         <is>
-          <t>30141</t>
+          <t>34235</t>
         </is>
       </c>
       <c r="E468" s="30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F468" s="33" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G468" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H468" s="30" t="inlineStr">
@@ -41744,7 +42292,7 @@
       </c>
       <c r="I468" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J468" s="30" t="inlineStr">
@@ -41758,26 +42306,26 @@
         <v>441</v>
       </c>
       <c r="C469" s="18" t="n">
-        <v>449</v>
+        <v>63</v>
       </c>
       <c r="D469" s="19" t="inlineStr">
         <is>
-          <t>30660</t>
+          <t>30329</t>
         </is>
       </c>
       <c r="E469" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F469" s="29" t="inlineStr">
         <is>
-          <t>44.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G469" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H469" s="28" t="inlineStr">
@@ -41787,7 +42335,7 @@
       </c>
       <c r="I469" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J469" s="28" t="inlineStr">
@@ -41801,26 +42349,26 @@
         <v>442</v>
       </c>
       <c r="C470" s="31" t="n">
-        <v>441</v>
+        <v>168</v>
       </c>
       <c r="D470" s="32" t="inlineStr">
         <is>
-          <t>30752</t>
+          <t>31738</t>
         </is>
       </c>
       <c r="E470" s="30" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F470" s="33" t="inlineStr">
         <is>
-          <t>40.0 kg</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G470" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H470" s="30" t="inlineStr">
@@ -41830,7 +42378,7 @@
       </c>
       <c r="I470" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J470" s="30" t="inlineStr">
@@ -41844,26 +42392,26 @@
         <v>443</v>
       </c>
       <c r="C471" s="18" t="n">
-        <v>181</v>
+        <v>372</v>
       </c>
       <c r="D471" s="19" t="inlineStr">
         <is>
-          <t>32278</t>
+          <t>30629</t>
         </is>
       </c>
       <c r="E471" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F471" s="29" t="inlineStr">
         <is>
-          <t>33 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G471" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H471" s="28" t="inlineStr">
@@ -41873,7 +42421,7 @@
       </c>
       <c r="I471" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J471" s="28" t="inlineStr">
@@ -41887,36 +42435,36 @@
         <v>444</v>
       </c>
       <c r="C472" s="31" t="n">
-        <v>482</v>
+        <v>402</v>
       </c>
       <c r="D472" s="32" t="inlineStr">
         <is>
-          <t>33815</t>
+          <t>31628</t>
         </is>
       </c>
       <c r="E472" s="30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F472" s="33" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>35.0 kg</t>
         </is>
       </c>
       <c r="G472" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H472" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I472" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J472" s="30" t="inlineStr">
@@ -41930,26 +42478,26 @@
         <v>445</v>
       </c>
       <c r="C473" s="18" t="n">
-        <v>13</v>
+        <v>527</v>
       </c>
       <c r="D473" s="19" t="inlineStr">
         <is>
-          <t>943644</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="E473" s="28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F473" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G473" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H473" s="28" t="inlineStr">
@@ -41959,7 +42507,7 @@
       </c>
       <c r="I473" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J473" s="28" t="inlineStr">
@@ -41973,26 +42521,26 @@
         <v>446</v>
       </c>
       <c r="C474" s="31" t="n">
-        <v>219</v>
+        <v>533</v>
       </c>
       <c r="D474" s="32" t="inlineStr">
         <is>
-          <t>33419</t>
+          <t>34234</t>
         </is>
       </c>
       <c r="E474" s="30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F474" s="33" t="inlineStr">
         <is>
-          <t>46.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G474" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H474" s="30" t="inlineStr">
@@ -42002,7 +42550,7 @@
       </c>
       <c r="I474" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J474" s="30" t="inlineStr">
@@ -42016,26 +42564,26 @@
         <v>447</v>
       </c>
       <c r="C475" s="18" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D475" s="19" t="inlineStr">
         <is>
-          <t>31730</t>
+          <t>31735</t>
         </is>
       </c>
       <c r="E475" s="28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F475" s="29" t="inlineStr">
         <is>
-          <t>42.0 kg</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="G475" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H475" s="28" t="inlineStr">
@@ -42045,7 +42593,7 @@
       </c>
       <c r="I475" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J475" s="28" t="inlineStr">
@@ -42059,26 +42607,26 @@
         <v>448</v>
       </c>
       <c r="C476" s="31" t="n">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="D476" s="32" t="inlineStr">
         <is>
-          <t>30755</t>
+          <t>34129</t>
         </is>
       </c>
       <c r="E476" s="30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F476" s="33" t="inlineStr">
         <is>
-          <t>38.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G476" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H476" s="30" t="inlineStr">
@@ -42088,7 +42636,7 @@
       </c>
       <c r="I476" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J476" s="30" t="inlineStr">
@@ -42102,26 +42650,26 @@
         <v>449</v>
       </c>
       <c r="C477" s="18" t="n">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="D477" s="19" t="inlineStr">
         <is>
-          <t>30757</t>
+          <t>30754</t>
         </is>
       </c>
       <c r="E477" s="28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F477" s="29" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G477" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H477" s="28" t="inlineStr">
@@ -42131,7 +42679,7 @@
       </c>
       <c r="I477" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J477" s="28" t="inlineStr">
@@ -42145,36 +42693,36 @@
         <v>450</v>
       </c>
       <c r="C478" s="31" t="n">
-        <v>526</v>
+        <v>132</v>
       </c>
       <c r="D478" s="32" t="inlineStr">
         <is>
-          <t>34238</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="E478" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F478" s="33" t="inlineStr">
         <is>
-          <t>42.0 kg</t>
+          <t>39 kg</t>
         </is>
       </c>
       <c r="G478" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H478" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I478" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J478" s="30" t="inlineStr">
@@ -42188,26 +42736,26 @@
         <v>451</v>
       </c>
       <c r="C479" s="18" t="n">
-        <v>308</v>
+        <v>126</v>
       </c>
       <c r="D479" s="19" t="inlineStr">
         <is>
-          <t>942822</t>
+          <t>943641</t>
         </is>
       </c>
       <c r="E479" s="28" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F479" s="29" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G479" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H479" s="28" t="inlineStr">
@@ -42217,7 +42765,7 @@
       </c>
       <c r="I479" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J479" s="28" t="inlineStr">
@@ -42231,16 +42779,16 @@
         <v>452</v>
       </c>
       <c r="C480" s="31" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="D480" s="32" t="inlineStr">
         <is>
-          <t>30758</t>
+          <t>943642</t>
         </is>
       </c>
       <c r="E480" s="30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F480" s="33" t="inlineStr">
@@ -42250,7 +42798,7 @@
       </c>
       <c r="G480" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H480" s="30" t="inlineStr">
@@ -42260,7 +42808,7 @@
       </c>
       <c r="I480" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J480" s="30" t="inlineStr">
@@ -42274,26 +42822,26 @@
         <v>453</v>
       </c>
       <c r="C481" s="18" t="n">
-        <v>411</v>
+        <v>140</v>
       </c>
       <c r="D481" s="19" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>31737</t>
         </is>
       </c>
       <c r="E481" s="28" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F481" s="29" t="inlineStr">
         <is>
-          <t>29.0 kg</t>
+          <t>49.0 kg</t>
         </is>
       </c>
       <c r="G481" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H481" s="28" t="inlineStr">
@@ -42303,7 +42851,7 @@
       </c>
       <c r="I481" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J481" s="28" t="inlineStr">
@@ -42317,26 +42865,26 @@
         <v>454</v>
       </c>
       <c r="C482" s="31" t="n">
-        <v>319</v>
+        <v>141</v>
       </c>
       <c r="D482" s="32" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>31739</t>
         </is>
       </c>
       <c r="E482" s="30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F482" s="33" t="inlineStr">
         <is>
-          <t>28.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G482" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H482" s="30" t="inlineStr">
@@ -42346,7 +42894,7 @@
       </c>
       <c r="I482" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J482" s="30" t="inlineStr">
@@ -42360,26 +42908,26 @@
         <v>455</v>
       </c>
       <c r="C483" s="18" t="n">
-        <v>452</v>
+        <v>178</v>
       </c>
       <c r="D483" s="19" t="inlineStr">
         <is>
-          <t>30756</t>
+          <t>30359</t>
         </is>
       </c>
       <c r="E483" s="28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F483" s="29" t="inlineStr">
         <is>
-          <t>38.0 kg</t>
+          <t>44.0 kg</t>
         </is>
       </c>
       <c r="G483" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H483" s="28" t="inlineStr">
@@ -42389,7 +42937,7 @@
       </c>
       <c r="I483" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J483" s="28" t="inlineStr">
@@ -42403,36 +42951,36 @@
         <v>456</v>
       </c>
       <c r="C484" s="31" t="n">
-        <v>522</v>
+        <v>401</v>
       </c>
       <c r="D484" s="32" t="inlineStr">
         <is>
-          <t>33813</t>
+          <t>31633</t>
         </is>
       </c>
       <c r="E484" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F484" s="33" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>33.0 kg</t>
         </is>
       </c>
       <c r="G484" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H484" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I484" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J484" s="30" t="inlineStr">
@@ -42445,12 +42993,14 @@
       <c r="B485" s="28" t="n">
         <v>457</v>
       </c>
-      <c r="C485" s="18" t="n">
-        <v>543</v>
+      <c r="C485" s="18" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="D485" s="19" t="inlineStr">
         <is>
-          <t>34249</t>
+          <t>34233</t>
         </is>
       </c>
       <c r="E485" s="28" t="inlineStr">
@@ -42460,12 +43010,12 @@
       </c>
       <c r="F485" s="29" t="inlineStr">
         <is>
-          <t>32.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G485" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H485" s="28" t="inlineStr">
@@ -42475,7 +43025,7 @@
       </c>
       <c r="I485" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J485" s="28" t="inlineStr">
@@ -42489,26 +43039,26 @@
         <v>458</v>
       </c>
       <c r="C486" s="31" t="n">
-        <v>450</v>
+        <v>541</v>
       </c>
       <c r="D486" s="32" t="inlineStr">
         <is>
-          <t>30662</t>
+          <t>34461</t>
         </is>
       </c>
       <c r="E486" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F486" s="33" t="inlineStr">
         <is>
-          <t>46.0 kg</t>
+          <t>33.0 kg</t>
         </is>
       </c>
       <c r="G486" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H486" s="30" t="inlineStr">
@@ -42518,7 +43068,7 @@
       </c>
       <c r="I486" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J486" s="30" t="inlineStr">
@@ -42532,26 +43082,26 @@
         <v>459</v>
       </c>
       <c r="C487" s="18" t="n">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="D487" s="19" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>31734</t>
         </is>
       </c>
       <c r="E487" s="28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F487" s="29" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>43.0 kg</t>
         </is>
       </c>
       <c r="G487" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H487" s="28" t="inlineStr">
@@ -42561,7 +43111,7 @@
       </c>
       <c r="I487" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J487" s="28" t="inlineStr">
@@ -42575,26 +43125,26 @@
         <v>460</v>
       </c>
       <c r="C488" s="31" t="n">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="D488" s="32" t="inlineStr">
         <is>
-          <t>31156</t>
+          <t>30445</t>
         </is>
       </c>
       <c r="E488" s="30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F488" s="33" t="inlineStr">
         <is>
-          <t>47.0 kg</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G488" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H488" s="30" t="inlineStr">
@@ -42604,7 +43154,7 @@
       </c>
       <c r="I488" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J488" s="30" t="inlineStr">
@@ -42618,11 +43168,11 @@
         <v>461</v>
       </c>
       <c r="C489" s="18" t="n">
-        <v>175</v>
+        <v>442</v>
       </c>
       <c r="D489" s="19" t="inlineStr">
         <is>
-          <t>32202</t>
+          <t>30748</t>
         </is>
       </c>
       <c r="E489" s="28" t="inlineStr">
@@ -42632,12 +43182,12 @@
       </c>
       <c r="F489" s="29" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G489" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H489" s="28" t="inlineStr">
@@ -42647,7 +43197,7 @@
       </c>
       <c r="I489" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J489" s="28" t="inlineStr">
@@ -42661,16 +43211,16 @@
         <v>462</v>
       </c>
       <c r="C490" s="31" t="n">
-        <v>525</v>
+        <v>429</v>
       </c>
       <c r="D490" s="32" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>30317</t>
         </is>
       </c>
       <c r="E490" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F490" s="33" t="inlineStr">
@@ -42680,17 +43230,17 @@
       </c>
       <c r="G490" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H490" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I490" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J490" s="30" t="inlineStr">
@@ -42704,26 +43254,26 @@
         <v>463</v>
       </c>
       <c r="C491" s="18" t="n">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="D491" s="19" t="inlineStr">
         <is>
-          <t>34702</t>
+          <t>34232</t>
         </is>
       </c>
       <c r="E491" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F491" s="29" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>43.0 kg</t>
         </is>
       </c>
       <c r="G491" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H491" s="28" t="inlineStr">
@@ -42733,7 +43283,7 @@
       </c>
       <c r="I491" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J491" s="28" t="inlineStr">
@@ -42747,26 +43297,26 @@
         <v>464</v>
       </c>
       <c r="C492" s="31" t="n">
-        <v>276</v>
+        <v>571</v>
       </c>
       <c r="D492" s="32" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>34462</t>
         </is>
       </c>
       <c r="E492" s="30" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F492" s="33" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>47.0 kg</t>
         </is>
       </c>
       <c r="G492" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H492" s="30" t="inlineStr">
@@ -42776,7 +43326,7 @@
       </c>
       <c r="I492" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J492" s="30" t="inlineStr">
@@ -42790,26 +43340,26 @@
         <v>465</v>
       </c>
       <c r="C493" s="18" t="n">
-        <v>564</v>
+        <v>273</v>
       </c>
       <c r="D493" s="19" t="inlineStr">
         <is>
-          <t>34532</t>
+          <t>30141</t>
         </is>
       </c>
       <c r="E493" s="28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F493" s="29" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>34.0 kg</t>
         </is>
       </c>
       <c r="G493" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H493" s="28" t="inlineStr">
@@ -42819,7 +43369,7 @@
       </c>
       <c r="I493" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J493" s="28" t="inlineStr">
@@ -42833,26 +43383,26 @@
         <v>466</v>
       </c>
       <c r="C494" s="31" t="n">
-        <v>149</v>
+        <v>449</v>
       </c>
       <c r="D494" s="32" t="inlineStr">
         <is>
-          <t>31729</t>
+          <t>30660</t>
         </is>
       </c>
       <c r="E494" s="30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F494" s="33" t="inlineStr">
         <is>
-          <t>45.0 kg</t>
+          <t>44.0 kg</t>
         </is>
       </c>
       <c r="G494" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H494" s="30" t="inlineStr">
@@ -42862,7 +43412,7 @@
       </c>
       <c r="I494" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J494" s="30" t="inlineStr">
@@ -42876,11 +43426,11 @@
         <v>467</v>
       </c>
       <c r="C495" s="18" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D495" s="19" t="inlineStr">
         <is>
-          <t>30750</t>
+          <t>30752</t>
         </is>
       </c>
       <c r="E495" s="28" t="inlineStr">
@@ -42890,12 +43440,12 @@
       </c>
       <c r="F495" s="29" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>40.0 kg</t>
         </is>
       </c>
       <c r="G495" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H495" s="28" t="inlineStr">
@@ -42905,7 +43455,7 @@
       </c>
       <c r="I495" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J495" s="28" t="inlineStr">
@@ -42919,36 +43469,36 @@
         <v>468</v>
       </c>
       <c r="C496" s="31" t="n">
-        <v>521</v>
+        <v>181</v>
       </c>
       <c r="D496" s="32" t="inlineStr">
         <is>
-          <t>33812</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="E496" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F496" s="33" t="inlineStr">
         <is>
-          <t>47.0 kg</t>
+          <t>33 kg</t>
         </is>
       </c>
       <c r="G496" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H496" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I496" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J496" s="30" t="inlineStr">
@@ -42962,26 +43512,26 @@
         <v>469</v>
       </c>
       <c r="C497" s="18" t="n">
-        <v>536</v>
+        <v>482</v>
       </c>
       <c r="D497" s="19" t="inlineStr">
         <is>
-          <t>34701</t>
+          <t>33815</t>
         </is>
       </c>
       <c r="E497" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F497" s="29" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G497" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H497" s="28" t="inlineStr">
@@ -42991,7 +43541,7 @@
       </c>
       <c r="I497" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J497" s="28" t="inlineStr">
@@ -43005,26 +43555,26 @@
         <v>470</v>
       </c>
       <c r="C498" s="31" t="n">
-        <v>575</v>
+        <v>13</v>
       </c>
       <c r="D498" s="32" t="inlineStr">
         <is>
-          <t>34463</t>
+          <t>943644</t>
         </is>
       </c>
       <c r="E498" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F498" s="33" t="inlineStr">
         <is>
-          <t>38.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G498" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H498" s="30" t="inlineStr">
@@ -43034,7 +43584,7 @@
       </c>
       <c r="I498" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J498" s="30" t="inlineStr">
@@ -43048,26 +43598,26 @@
         <v>471</v>
       </c>
       <c r="C499" s="18" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D499" s="19" t="inlineStr">
         <is>
-          <t>33837</t>
+          <t>33419</t>
         </is>
       </c>
       <c r="E499" s="28" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F499" s="29" t="inlineStr">
         <is>
-          <t>44.0 kg</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="G499" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H499" s="28" t="inlineStr">
@@ -43077,7 +43627,7 @@
       </c>
       <c r="I499" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J499" s="28" t="inlineStr">
@@ -43091,26 +43641,26 @@
         <v>472</v>
       </c>
       <c r="C500" s="31" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="D500" s="32" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>31730</t>
         </is>
       </c>
       <c r="E500" s="30" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F500" s="33" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G500" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H500" s="30" t="inlineStr">
@@ -43120,7 +43670,7 @@
       </c>
       <c r="I500" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J500" s="30" t="inlineStr">
@@ -43134,26 +43684,26 @@
         <v>473</v>
       </c>
       <c r="C501" s="18" t="n">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="D501" s="19" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>30755</t>
         </is>
       </c>
       <c r="E501" s="28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F501" s="29" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>38.0 kg</t>
         </is>
       </c>
       <c r="G501" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H501" s="28" t="inlineStr">
@@ -43163,7 +43713,7 @@
       </c>
       <c r="I501" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J501" s="28" t="inlineStr">
@@ -43177,36 +43727,36 @@
         <v>474</v>
       </c>
       <c r="C502" s="31" t="n">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="D502" s="32" t="inlineStr">
         <is>
-          <t>34329</t>
+          <t>30757</t>
         </is>
       </c>
       <c r="E502" s="30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F502" s="33" t="inlineStr">
         <is>
-          <t>35.0 kg</t>
+          <t>34.0 kg</t>
         </is>
       </c>
       <c r="G502" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H502" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I502" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J502" s="30" t="inlineStr">
@@ -43220,26 +43770,26 @@
         <v>475</v>
       </c>
       <c r="C503" s="18" t="n">
-        <v>566</v>
+        <v>526</v>
       </c>
       <c r="D503" s="19" t="inlineStr">
         <is>
-          <t>34341</t>
+          <t>34238</t>
         </is>
       </c>
       <c r="E503" s="28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F503" s="29" t="inlineStr">
         <is>
-          <t>41.0 kg</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G503" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H503" s="28" t="inlineStr">
@@ -43249,7 +43799,7 @@
       </c>
       <c r="I503" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J503" s="28" t="inlineStr">
@@ -43263,26 +43813,26 @@
         <v>476</v>
       </c>
       <c r="C504" s="31" t="n">
-        <v>559</v>
+        <v>308</v>
       </c>
       <c r="D504" s="32" t="inlineStr">
         <is>
-          <t>34344</t>
+          <t>942822</t>
         </is>
       </c>
       <c r="E504" s="30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F504" s="33" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>39.0 kg</t>
         </is>
       </c>
       <c r="G504" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H504" s="30" t="inlineStr">
@@ -43292,7 +43842,7 @@
       </c>
       <c r="I504" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J504" s="30" t="inlineStr">
@@ -43306,26 +43856,26 @@
         <v>477</v>
       </c>
       <c r="C505" s="18" t="n">
-        <v>572</v>
+        <v>49</v>
       </c>
       <c r="D505" s="19" t="inlineStr">
         <is>
-          <t>33462</t>
+          <t>30758</t>
         </is>
       </c>
       <c r="E505" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F505" s="29" t="inlineStr">
         <is>
-          <t>38.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G505" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H505" s="28" t="inlineStr">
@@ -43335,7 +43885,7 @@
       </c>
       <c r="I505" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J505" s="28" t="inlineStr">
@@ -43349,26 +43899,26 @@
         <v>478</v>
       </c>
       <c r="C506" s="31" t="n">
-        <v>356</v>
+        <v>411</v>
       </c>
       <c r="D506" s="32" t="inlineStr">
         <is>
-          <t>30330</t>
+          <t>30451</t>
         </is>
       </c>
       <c r="E506" s="30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F506" s="33" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>29.0 kg</t>
         </is>
       </c>
       <c r="G506" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H506" s="30" t="inlineStr">
@@ -43378,7 +43928,7 @@
       </c>
       <c r="I506" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J506" s="30" t="inlineStr">
@@ -43392,26 +43942,26 @@
         <v>479</v>
       </c>
       <c r="C507" s="18" t="n">
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="D507" s="19" t="inlineStr">
         <is>
-          <t>33421</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="E507" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F507" s="29" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
+          <t>28.0 kg</t>
         </is>
       </c>
       <c r="G507" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H507" s="28" t="inlineStr">
@@ -43421,7 +43971,7 @@
       </c>
       <c r="I507" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J507" s="28" t="inlineStr">
@@ -43434,39 +43984,37 @@
       <c r="B508" s="30" t="n">
         <v>480</v>
       </c>
-      <c r="C508" s="31" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+      <c r="C508" s="31" t="n">
+        <v>452</v>
       </c>
       <c r="D508" s="32" t="inlineStr">
         <is>
-          <t>943646</t>
+          <t>30756</t>
         </is>
       </c>
       <c r="E508" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F508" s="33" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>38.0 kg</t>
         </is>
       </c>
       <c r="G508" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H508" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I508" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J508" s="30" t="inlineStr">
@@ -43480,11 +44028,11 @@
         <v>481</v>
       </c>
       <c r="C509" s="18" t="n">
-        <v>553</v>
+        <v>522</v>
       </c>
       <c r="D509" s="19" t="inlineStr">
         <is>
-          <t>33834</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="E509" s="28" t="inlineStr">
@@ -43494,12 +44042,12 @@
       </c>
       <c r="F509" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G509" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H509" s="28" t="inlineStr">
@@ -43509,7 +44057,7 @@
       </c>
       <c r="I509" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J509" s="28" t="inlineStr">
@@ -43523,26 +44071,26 @@
         <v>482</v>
       </c>
       <c r="C510" s="31" t="n">
-        <v>179</v>
+        <v>543</v>
       </c>
       <c r="D510" s="32" t="inlineStr">
         <is>
-          <t>942823</t>
+          <t>34249</t>
         </is>
       </c>
       <c r="E510" s="30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F510" s="33" t="inlineStr">
         <is>
-          <t>43.0 kg</t>
+          <t>32.0 kg</t>
         </is>
       </c>
       <c r="G510" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H510" s="30" t="inlineStr">
@@ -43552,7 +44100,7 @@
       </c>
       <c r="I510" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J510" s="30" t="inlineStr">
@@ -43566,11 +44114,11 @@
         <v>483</v>
       </c>
       <c r="C511" s="18" t="n">
-        <v>574</v>
+        <v>450</v>
       </c>
       <c r="D511" s="19" t="inlineStr">
         <is>
-          <t>33836</t>
+          <t>30662</t>
         </is>
       </c>
       <c r="E511" s="28" t="inlineStr">
@@ -43580,12 +44128,12 @@
       </c>
       <c r="F511" s="29" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="G511" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H511" s="28" t="inlineStr">
@@ -43595,7 +44143,7 @@
       </c>
       <c r="I511" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J511" s="28" t="inlineStr">
@@ -43609,26 +44157,26 @@
         <v>484</v>
       </c>
       <c r="C512" s="31" t="n">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="D512" s="32" t="inlineStr">
         <is>
-          <t>31733</t>
+          <t>31295</t>
         </is>
       </c>
       <c r="E512" s="30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F512" s="33" t="inlineStr">
         <is>
-          <t>41.0 kg</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G512" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H512" s="30" t="inlineStr">
@@ -43638,7 +44186,7 @@
       </c>
       <c r="I512" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J512" s="30" t="inlineStr">
@@ -43652,26 +44200,26 @@
         <v>485</v>
       </c>
       <c r="C513" s="18" t="n">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="D513" s="19" t="inlineStr">
         <is>
-          <t>943613</t>
+          <t>31156</t>
         </is>
       </c>
       <c r="E513" s="28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F513" s="29" t="inlineStr">
         <is>
-          <t>45.0 kg</t>
+          <t>47.0 kg</t>
         </is>
       </c>
       <c r="G513" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H513" s="28" t="inlineStr">
@@ -43681,7 +44229,7 @@
       </c>
       <c r="I513" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J513" s="28" t="inlineStr">
@@ -43695,36 +44243,36 @@
         <v>486</v>
       </c>
       <c r="C514" s="31" t="n">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="D514" s="32" t="inlineStr">
         <is>
-          <t>943645</t>
+          <t>32202</t>
         </is>
       </c>
       <c r="E514" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F514" s="33" t="inlineStr">
         <is>
-          <t>46.0 kg</t>
+          <t>34.0 kg</t>
         </is>
       </c>
       <c r="G514" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H514" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I514" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J514" s="30" t="inlineStr">
@@ -43738,16 +44286,16 @@
         <v>487</v>
       </c>
       <c r="C515" s="18" t="n">
-        <v>552</v>
+        <v>525</v>
       </c>
       <c r="D515" s="19" t="inlineStr">
         <is>
-          <t>33835</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="E515" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F515" s="29" t="inlineStr">
@@ -43757,7 +44305,7 @@
       </c>
       <c r="G515" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H515" s="28" t="inlineStr">
@@ -43767,7 +44315,7 @@
       </c>
       <c r="I515" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J515" s="28" t="inlineStr">
@@ -43781,26 +44329,26 @@
         <v>488</v>
       </c>
       <c r="C516" s="31" t="n">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="D516" s="32" t="inlineStr">
         <is>
-          <t>33461</t>
+          <t>34702</t>
         </is>
       </c>
       <c r="E516" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F516" s="33" t="inlineStr">
         <is>
-          <t>42.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G516" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H516" s="30" t="inlineStr">
@@ -43810,7 +44358,7 @@
       </c>
       <c r="I516" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J516" s="30" t="inlineStr">
@@ -43824,26 +44372,26 @@
         <v>489</v>
       </c>
       <c r="C517" s="18" t="n">
-        <v>558</v>
+        <v>276</v>
       </c>
       <c r="D517" s="19" t="inlineStr">
         <is>
-          <t>34459</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="E517" s="28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F517" s="29" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G517" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H517" s="28" t="inlineStr">
@@ -43853,7 +44401,7 @@
       </c>
       <c r="I517" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J517" s="28" t="inlineStr">
@@ -43867,26 +44415,26 @@
         <v>490</v>
       </c>
       <c r="C518" s="31" t="n">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="D518" s="32" t="inlineStr">
         <is>
-          <t>34340</t>
+          <t>34532</t>
         </is>
       </c>
       <c r="E518" s="30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F518" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G518" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H518" s="30" t="inlineStr">
@@ -43896,7 +44444,7 @@
       </c>
       <c r="I518" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J518" s="30" t="inlineStr">
@@ -43910,26 +44458,26 @@
         <v>491</v>
       </c>
       <c r="C519" s="18" t="n">
-        <v>307</v>
+        <v>149</v>
       </c>
       <c r="D519" s="19" t="inlineStr">
         <is>
-          <t>942824</t>
+          <t>31729</t>
         </is>
       </c>
       <c r="E519" s="28" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F519" s="29" t="inlineStr">
         <is>
-          <t>47.0 kg</t>
+          <t>45.0 kg</t>
         </is>
       </c>
       <c r="G519" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H519" s="28" t="inlineStr">
@@ -43939,7 +44487,7 @@
       </c>
       <c r="I519" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J519" s="28" t="inlineStr">
@@ -43953,36 +44501,36 @@
         <v>492</v>
       </c>
       <c r="C520" s="31" t="n">
-        <v>480</v>
+        <v>443</v>
       </c>
       <c r="D520" s="32" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>30750</t>
         </is>
       </c>
       <c r="E520" s="30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F520" s="33" t="inlineStr">
         <is>
-          <t>32.0 kg</t>
+          <t>34.0 kg</t>
         </is>
       </c>
       <c r="G520" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H520" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I520" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J520" s="30" t="inlineStr">
@@ -43996,26 +44544,26 @@
         <v>493</v>
       </c>
       <c r="C521" s="18" t="n">
-        <v>548</v>
+        <v>521</v>
       </c>
       <c r="D521" s="19" t="inlineStr">
         <is>
-          <t>33832</t>
+          <t>33812</t>
         </is>
       </c>
       <c r="E521" s="28" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F521" s="29" t="inlineStr">
         <is>
-          <t>49.0 kg</t>
+          <t>47.0 kg</t>
         </is>
       </c>
       <c r="G521" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H521" s="28" t="inlineStr">
@@ -44025,7 +44573,7 @@
       </c>
       <c r="I521" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J521" s="28" t="inlineStr">
@@ -44039,11 +44587,11 @@
         <v>494</v>
       </c>
       <c r="C522" s="31" t="n">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="D522" s="32" t="inlineStr">
         <is>
-          <t>34703</t>
+          <t>34701</t>
         </is>
       </c>
       <c r="E522" s="30" t="inlineStr">
@@ -44053,12 +44601,12 @@
       </c>
       <c r="F522" s="33" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>33.0 kg</t>
         </is>
       </c>
       <c r="G522" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H522" s="30" t="inlineStr">
@@ -44068,7 +44616,7 @@
       </c>
       <c r="I522" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J522" s="30" t="inlineStr">
@@ -44082,26 +44630,26 @@
         <v>495</v>
       </c>
       <c r="C523" s="18" t="n">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="D523" s="19" t="inlineStr">
         <is>
-          <t>34246</t>
+          <t>34463</t>
         </is>
       </c>
       <c r="E523" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F523" s="29" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>38.0 kg</t>
         </is>
       </c>
       <c r="G523" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H523" s="28" t="inlineStr">
@@ -44111,7 +44659,7 @@
       </c>
       <c r="I523" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J523" s="28" t="inlineStr">
@@ -44125,26 +44673,26 @@
         <v>496</v>
       </c>
       <c r="C524" s="31" t="n">
-        <v>544</v>
+        <v>223</v>
       </c>
       <c r="D524" s="32" t="inlineStr">
         <is>
-          <t>34460</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="E524" s="30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F524" s="33" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>44.0 kg</t>
         </is>
       </c>
       <c r="G524" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H524" s="30" t="inlineStr">
@@ -44154,7 +44702,7 @@
       </c>
       <c r="I524" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J524" s="30" t="inlineStr">
@@ -44168,26 +44716,26 @@
         <v>497</v>
       </c>
       <c r="C525" s="18" t="n">
-        <v>561</v>
+        <v>220</v>
       </c>
       <c r="D525" s="19" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>31731</t>
         </is>
       </c>
       <c r="E525" s="28" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F525" s="29" t="inlineStr">
         <is>
-          <t>40.0 kg</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G525" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H525" s="28" t="inlineStr">
@@ -44197,7 +44745,7 @@
       </c>
       <c r="I525" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J525" s="28" t="inlineStr">
@@ -44211,36 +44759,36 @@
         <v>498</v>
       </c>
       <c r="C526" s="31" t="n">
-        <v>523</v>
+        <v>435</v>
       </c>
       <c r="D526" s="32" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>32120</t>
         </is>
       </c>
       <c r="E526" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F526" s="33" t="inlineStr">
         <is>
-          <t>45.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G526" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H526" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I526" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J526" s="30" t="inlineStr">
@@ -44254,26 +44802,26 @@
         <v>499</v>
       </c>
       <c r="C527" s="18" t="n">
-        <v>539</v>
+        <v>481</v>
       </c>
       <c r="D527" s="19" t="inlineStr">
         <is>
-          <t>34247</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="E527" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F527" s="29" t="inlineStr">
         <is>
-          <t>49.0 kg</t>
+          <t>35.0 kg</t>
         </is>
       </c>
       <c r="G527" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H527" s="28" t="inlineStr">
@@ -44283,7 +44831,7 @@
       </c>
       <c r="I527" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J527" s="28" t="inlineStr">
@@ -44297,26 +44845,26 @@
         <v>500</v>
       </c>
       <c r="C528" s="31" t="n">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="D528" s="32" t="inlineStr">
         <is>
-          <t>34531</t>
+          <t>34341</t>
         </is>
       </c>
       <c r="E528" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F528" s="33" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>41.0 kg</t>
         </is>
       </c>
       <c r="G528" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H528" s="30" t="inlineStr">
@@ -44326,7 +44874,7 @@
       </c>
       <c r="I528" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J528" s="30" t="inlineStr">
@@ -44340,16 +44888,16 @@
         <v>501</v>
       </c>
       <c r="C529" s="18" t="n">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="D529" s="19" t="inlineStr">
         <is>
-          <t>33833</t>
+          <t>34344</t>
         </is>
       </c>
       <c r="E529" s="28" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F529" s="29" t="inlineStr">
@@ -44359,7 +44907,7 @@
       </c>
       <c r="G529" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H529" s="28" t="inlineStr">
@@ -44369,7 +44917,7 @@
       </c>
       <c r="I529" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J529" s="28" t="inlineStr">
@@ -44383,26 +44931,26 @@
         <v>502</v>
       </c>
       <c r="C530" s="31" t="n">
-        <v>540</v>
+        <v>572</v>
       </c>
       <c r="D530" s="32" t="inlineStr">
         <is>
-          <t>34248</t>
+          <t>33462</t>
         </is>
       </c>
       <c r="E530" s="30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F530" s="33" t="inlineStr">
         <is>
-          <t>41.0 kg</t>
+          <t>38.0 kg</t>
         </is>
       </c>
       <c r="G530" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H530" s="30" t="inlineStr">
@@ -44412,7 +44960,7 @@
       </c>
       <c r="I530" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J530" s="30" t="inlineStr">
@@ -44426,26 +44974,26 @@
         <v>503</v>
       </c>
       <c r="C531" s="18" t="n">
-        <v>538</v>
+        <v>356</v>
       </c>
       <c r="D531" s="19" t="inlineStr">
         <is>
-          <t>34458</t>
+          <t>30330</t>
         </is>
       </c>
       <c r="E531" s="28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F531" s="29" t="inlineStr">
         <is>
-          <t>40.0 kg</t>
+          <t>33.0 kg</t>
         </is>
       </c>
       <c r="G531" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H531" s="28" t="inlineStr">
@@ -44455,7 +45003,7 @@
       </c>
       <c r="I531" s="28" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J531" s="28" t="inlineStr">
@@ -44469,11 +45017,11 @@
         <v>504</v>
       </c>
       <c r="C532" s="31" t="n">
-        <v>524</v>
+        <v>285</v>
       </c>
       <c r="D532" s="32" t="inlineStr">
         <is>
-          <t>33445</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="E532" s="30" t="inlineStr">
@@ -44483,22 +45031,22 @@
       </c>
       <c r="F532" s="33" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>39.0 kg</t>
         </is>
       </c>
       <c r="G532" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H532" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I532" s="30" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J532" s="30" t="inlineStr">
@@ -44511,27 +45059,29 @@
       <c r="B533" s="28" t="n">
         <v>505</v>
       </c>
-      <c r="C533" s="18" t="n">
-        <v>551</v>
+      <c r="C533" s="18" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
       </c>
       <c r="D533" s="19" t="inlineStr">
         <is>
-          <t>33838</t>
+          <t>943646</t>
         </is>
       </c>
       <c r="E533" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F533" s="29" t="inlineStr">
         <is>
-          <t>46.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G533" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H533" s="28" t="inlineStr">
@@ -44541,7 +45091,7 @@
       </c>
       <c r="I533" s="28" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J533" s="28" t="inlineStr">
@@ -44555,11 +45105,11 @@
         <v>506</v>
       </c>
       <c r="C534" s="31" t="n">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="D534" s="32" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>33834</t>
         </is>
       </c>
       <c r="E534" s="30" t="inlineStr">
@@ -44569,12 +45119,12 @@
       </c>
       <c r="F534" s="33" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G534" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H534" s="30" t="inlineStr">
@@ -44584,7 +45134,7 @@
       </c>
       <c r="I534" s="30" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J534" s="30" t="inlineStr">
@@ -44598,26 +45148,26 @@
         <v>507</v>
       </c>
       <c r="C535" s="18" t="n">
-        <v>573</v>
+        <v>179</v>
       </c>
       <c r="D535" s="19" t="inlineStr">
         <is>
-          <t>34704</t>
+          <t>942823</t>
         </is>
       </c>
       <c r="E535" s="28" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F535" s="29" t="inlineStr">
         <is>
-          <t>40.0 kg</t>
+          <t>43.0 kg</t>
         </is>
       </c>
       <c r="G535" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H535" s="28" t="inlineStr">
@@ -44627,7 +45177,7 @@
       </c>
       <c r="I535" s="28" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J535" s="28" t="inlineStr">
@@ -44641,26 +45191,26 @@
         <v>508</v>
       </c>
       <c r="C536" s="31" t="n">
-        <v>64</v>
+        <v>574</v>
       </c>
       <c r="D536" s="32" t="inlineStr">
         <is>
-          <t>942825</t>
+          <t>33836</t>
         </is>
       </c>
       <c r="E536" s="30" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F536" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>33.0 kg</t>
         </is>
       </c>
       <c r="G536" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H536" s="30" t="inlineStr">
@@ -44670,7 +45220,7 @@
       </c>
       <c r="I536" s="30" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J536" s="30" t="inlineStr">
@@ -44684,46 +45234,1121 @@
         <v>509</v>
       </c>
       <c r="C537" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="D537" s="19" t="inlineStr">
+        <is>
+          <t>31733</t>
+        </is>
+      </c>
+      <c r="E537" s="28" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F537" s="29" t="inlineStr">
+        <is>
+          <t>41.0 kg</t>
+        </is>
+      </c>
+      <c r="G537" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 15</t>
+        </is>
+      </c>
+      <c r="H537" s="28" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="I537" s="28" t="inlineStr">
+        <is>
+          <t>Saf 5</t>
+        </is>
+      </c>
+      <c r="J537" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="538" ht="20" customHeight="1">
+      <c r="B538" s="30" t="n">
+        <v>510</v>
+      </c>
+      <c r="C538" s="31" t="n">
+        <v>343</v>
+      </c>
+      <c r="D538" s="32" t="inlineStr">
+        <is>
+          <t>943613</t>
+        </is>
+      </c>
+      <c r="E538" s="30" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F538" s="33" t="inlineStr">
+        <is>
+          <t>45.0 kg</t>
+        </is>
+      </c>
+      <c r="G538" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 15</t>
+        </is>
+      </c>
+      <c r="H538" s="30" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="I538" s="30" t="inlineStr">
+        <is>
+          <t>Saf 6</t>
+        </is>
+      </c>
+      <c r="J538" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="539" ht="20" customHeight="1">
+      <c r="B539" s="28" t="n">
+        <v>511</v>
+      </c>
+      <c r="C539" s="18" t="n">
+        <v>113</v>
+      </c>
+      <c r="D539" s="19" t="inlineStr">
+        <is>
+          <t>943645</t>
+        </is>
+      </c>
+      <c r="E539" s="28" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F539" s="29" t="inlineStr">
+        <is>
+          <t>46.0 kg</t>
+        </is>
+      </c>
+      <c r="G539" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H539" s="28" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="I539" s="28" t="inlineStr">
+        <is>
+          <t>Saf 1</t>
+        </is>
+      </c>
+      <c r="J539" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="540" ht="20" customHeight="1">
+      <c r="B540" s="30" t="n">
+        <v>512</v>
+      </c>
+      <c r="C540" s="31" t="n">
+        <v>552</v>
+      </c>
+      <c r="D540" s="32" t="inlineStr">
+        <is>
+          <t>33835</t>
+        </is>
+      </c>
+      <c r="E540" s="30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F540" s="33" t="inlineStr">
+        <is>
+          <t>50.0 kg</t>
+        </is>
+      </c>
+      <c r="G540" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H540" s="30" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="I540" s="30" t="inlineStr">
+        <is>
+          <t>Saf 2</t>
+        </is>
+      </c>
+      <c r="J540" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="541" ht="20" customHeight="1">
+      <c r="B541" s="28" t="n">
+        <v>513</v>
+      </c>
+      <c r="C541" s="18" t="n">
+        <v>555</v>
+      </c>
+      <c r="D541" s="19" t="inlineStr">
+        <is>
+          <t>33461</t>
+        </is>
+      </c>
+      <c r="E541" s="28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F541" s="29" t="inlineStr">
+        <is>
+          <t>42.0 kg</t>
+        </is>
+      </c>
+      <c r="G541" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H541" s="28" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="I541" s="28" t="inlineStr">
+        <is>
+          <t>Saf 3</t>
+        </is>
+      </c>
+      <c r="J541" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="542" ht="20" customHeight="1">
+      <c r="B542" s="30" t="n">
+        <v>514</v>
+      </c>
+      <c r="C542" s="31" t="n">
+        <v>558</v>
+      </c>
+      <c r="D542" s="32" t="inlineStr">
+        <is>
+          <t>34459</t>
+        </is>
+      </c>
+      <c r="E542" s="30" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F542" s="33" t="inlineStr">
+        <is>
+          <t>33.0 kg</t>
+        </is>
+      </c>
+      <c r="G542" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H542" s="30" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="I542" s="30" t="inlineStr">
+        <is>
+          <t>Saf 4</t>
+        </is>
+      </c>
+      <c r="J542" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="543" ht="20" customHeight="1">
+      <c r="B543" s="28" t="n">
+        <v>515</v>
+      </c>
+      <c r="C543" s="18" t="n">
+        <v>549</v>
+      </c>
+      <c r="D543" s="19" t="inlineStr">
+        <is>
+          <t>34340</t>
+        </is>
+      </c>
+      <c r="E543" s="28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F543" s="29" t="inlineStr">
+        <is>
+          <t>50.0 kg</t>
+        </is>
+      </c>
+      <c r="G543" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H543" s="28" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="I543" s="28" t="inlineStr">
+        <is>
+          <t>Saf 5</t>
+        </is>
+      </c>
+      <c r="J543" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="544" ht="20" customHeight="1">
+      <c r="B544" s="30" t="n">
+        <v>516</v>
+      </c>
+      <c r="C544" s="31" t="n">
+        <v>307</v>
+      </c>
+      <c r="D544" s="32" t="inlineStr">
+        <is>
+          <t>942824</t>
+        </is>
+      </c>
+      <c r="E544" s="30" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F544" s="33" t="inlineStr">
+        <is>
+          <t>47.0 kg</t>
+        </is>
+      </c>
+      <c r="G544" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H544" s="30" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="I544" s="30" t="inlineStr">
+        <is>
+          <t>Saf 6</t>
+        </is>
+      </c>
+      <c r="J544" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="545" ht="20" customHeight="1">
+      <c r="B545" s="28" t="n">
+        <v>517</v>
+      </c>
+      <c r="C545" s="18" t="n">
+        <v>480</v>
+      </c>
+      <c r="D545" s="19" t="inlineStr">
+        <is>
+          <t>34330</t>
+        </is>
+      </c>
+      <c r="E545" s="28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F545" s="29" t="inlineStr">
+        <is>
+          <t>32.0 kg</t>
+        </is>
+      </c>
+      <c r="G545" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H545" s="28" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="I545" s="28" t="inlineStr">
+        <is>
+          <t>Saf 1</t>
+        </is>
+      </c>
+      <c r="J545" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="546" ht="20" customHeight="1">
+      <c r="B546" s="30" t="n">
+        <v>518</v>
+      </c>
+      <c r="C546" s="31" t="n">
+        <v>548</v>
+      </c>
+      <c r="D546" s="32" t="inlineStr">
+        <is>
+          <t>33832</t>
+        </is>
+      </c>
+      <c r="E546" s="30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F546" s="33" t="inlineStr">
+        <is>
+          <t>49.0 kg</t>
+        </is>
+      </c>
+      <c r="G546" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H546" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="I546" s="30" t="inlineStr">
+        <is>
+          <t>Saf 2</t>
+        </is>
+      </c>
+      <c r="J546" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="547" ht="20" customHeight="1">
+      <c r="B547" s="28" t="n">
+        <v>519</v>
+      </c>
+      <c r="C547" s="18" t="n">
+        <v>542</v>
+      </c>
+      <c r="D547" s="19" t="inlineStr">
+        <is>
+          <t>34703</t>
+        </is>
+      </c>
+      <c r="E547" s="28" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F547" s="29" t="inlineStr">
+        <is>
+          <t>34.0 kg</t>
+        </is>
+      </c>
+      <c r="G547" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H547" s="28" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="I547" s="28" t="inlineStr">
+        <is>
+          <t>Saf 3</t>
+        </is>
+      </c>
+      <c r="J547" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="548" ht="20" customHeight="1">
+      <c r="B548" s="30" t="n">
+        <v>520</v>
+      </c>
+      <c r="C548" s="31" t="n">
+        <v>557</v>
+      </c>
+      <c r="D548" s="32" t="inlineStr">
+        <is>
+          <t>34246</t>
+        </is>
+      </c>
+      <c r="E548" s="30" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F548" s="33" t="inlineStr">
+        <is>
+          <t>33.0 kg</t>
+        </is>
+      </c>
+      <c r="G548" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H548" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="I548" s="30" t="inlineStr">
+        <is>
+          <t>Saf 4</t>
+        </is>
+      </c>
+      <c r="J548" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="549" ht="20" customHeight="1">
+      <c r="B549" s="28" t="n">
+        <v>521</v>
+      </c>
+      <c r="C549" s="18" t="n">
+        <v>544</v>
+      </c>
+      <c r="D549" s="19" t="inlineStr">
+        <is>
+          <t>34460</t>
+        </is>
+      </c>
+      <c r="E549" s="28" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F549" s="29" t="inlineStr">
+        <is>
+          <t>30.0 kg</t>
+        </is>
+      </c>
+      <c r="G549" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H549" s="28" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="I549" s="28" t="inlineStr">
+        <is>
+          <t>Saf 5</t>
+        </is>
+      </c>
+      <c r="J549" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="550" ht="20" customHeight="1">
+      <c r="B550" s="30" t="n">
+        <v>522</v>
+      </c>
+      <c r="C550" s="31" t="n">
+        <v>561</v>
+      </c>
+      <c r="D550" s="32" t="inlineStr">
+        <is>
+          <t>34343</t>
+        </is>
+      </c>
+      <c r="E550" s="30" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F550" s="33" t="inlineStr">
+        <is>
+          <t>40.0 kg</t>
+        </is>
+      </c>
+      <c r="G550" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H550" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="I550" s="30" t="inlineStr">
+        <is>
+          <t>Saf 6</t>
+        </is>
+      </c>
+      <c r="J550" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="551" ht="20" customHeight="1">
+      <c r="B551" s="28" t="n">
+        <v>523</v>
+      </c>
+      <c r="C551" s="18" t="n">
+        <v>523</v>
+      </c>
+      <c r="D551" s="19" t="inlineStr">
+        <is>
+          <t>33814</t>
+        </is>
+      </c>
+      <c r="E551" s="28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F551" s="29" t="inlineStr">
+        <is>
+          <t>45.0 kg</t>
+        </is>
+      </c>
+      <c r="G551" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H551" s="28" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="I551" s="28" t="inlineStr">
+        <is>
+          <t>Saf 1</t>
+        </is>
+      </c>
+      <c r="J551" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="552" ht="20" customHeight="1">
+      <c r="B552" s="30" t="n">
+        <v>524</v>
+      </c>
+      <c r="C552" s="31" t="n">
+        <v>539</v>
+      </c>
+      <c r="D552" s="32" t="inlineStr">
+        <is>
+          <t>34247</t>
+        </is>
+      </c>
+      <c r="E552" s="30" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F552" s="33" t="inlineStr">
+        <is>
+          <t>49.0 kg</t>
+        </is>
+      </c>
+      <c r="G552" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H552" s="30" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="I552" s="30" t="inlineStr">
+        <is>
+          <t>Saf 2</t>
+        </is>
+      </c>
+      <c r="J552" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="553" ht="20" customHeight="1">
+      <c r="B553" s="28" t="n">
+        <v>525</v>
+      </c>
+      <c r="C553" s="18" t="n">
+        <v>547</v>
+      </c>
+      <c r="D553" s="19" t="inlineStr">
+        <is>
+          <t>34531</t>
+        </is>
+      </c>
+      <c r="E553" s="28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F553" s="29" t="inlineStr">
+        <is>
+          <t>37.0 kg</t>
+        </is>
+      </c>
+      <c r="G553" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H553" s="28" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="I553" s="28" t="inlineStr">
+        <is>
+          <t>Saf 3</t>
+        </is>
+      </c>
+      <c r="J553" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="554" ht="20" customHeight="1">
+      <c r="B554" s="30" t="n">
+        <v>526</v>
+      </c>
+      <c r="C554" s="31" t="n">
+        <v>554</v>
+      </c>
+      <c r="D554" s="32" t="inlineStr">
+        <is>
+          <t>33833</t>
+        </is>
+      </c>
+      <c r="E554" s="30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F554" s="33" t="inlineStr">
+        <is>
+          <t>36.0 kg</t>
+        </is>
+      </c>
+      <c r="G554" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H554" s="30" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="I554" s="30" t="inlineStr">
+        <is>
+          <t>Saf 4</t>
+        </is>
+      </c>
+      <c r="J554" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="555" ht="20" customHeight="1">
+      <c r="B555" s="28" t="n">
+        <v>527</v>
+      </c>
+      <c r="C555" s="18" t="n">
+        <v>540</v>
+      </c>
+      <c r="D555" s="19" t="inlineStr">
+        <is>
+          <t>34248</t>
+        </is>
+      </c>
+      <c r="E555" s="28" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F555" s="29" t="inlineStr">
+        <is>
+          <t>41.0 kg</t>
+        </is>
+      </c>
+      <c r="G555" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H555" s="28" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="I555" s="28" t="inlineStr">
+        <is>
+          <t>Saf 5</t>
+        </is>
+      </c>
+      <c r="J555" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="556" ht="20" customHeight="1">
+      <c r="B556" s="30" t="n">
+        <v>528</v>
+      </c>
+      <c r="C556" s="31" t="n">
+        <v>538</v>
+      </c>
+      <c r="D556" s="32" t="inlineStr">
+        <is>
+          <t>34458</t>
+        </is>
+      </c>
+      <c r="E556" s="30" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F556" s="33" t="inlineStr">
+        <is>
+          <t>40.0 kg</t>
+        </is>
+      </c>
+      <c r="G556" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H556" s="30" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="I556" s="30" t="inlineStr">
+        <is>
+          <t>Saf 6</t>
+        </is>
+      </c>
+      <c r="J556" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="557" ht="20" customHeight="1">
+      <c r="B557" s="28" t="n">
+        <v>529</v>
+      </c>
+      <c r="C557" s="18" t="n">
+        <v>524</v>
+      </c>
+      <c r="D557" s="19" t="inlineStr">
+        <is>
+          <t>33445</t>
+        </is>
+      </c>
+      <c r="E557" s="28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F557" s="29" t="inlineStr">
+        <is>
+          <t>30.0 kg</t>
+        </is>
+      </c>
+      <c r="G557" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H557" s="28" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="I557" s="28" t="inlineStr">
+        <is>
+          <t>Saf 1</t>
+        </is>
+      </c>
+      <c r="J557" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="558" ht="20" customHeight="1">
+      <c r="B558" s="30" t="n">
+        <v>530</v>
+      </c>
+      <c r="C558" s="31" t="n">
+        <v>551</v>
+      </c>
+      <c r="D558" s="32" t="inlineStr">
+        <is>
+          <t>33838</t>
+        </is>
+      </c>
+      <c r="E558" s="30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F558" s="33" t="inlineStr">
+        <is>
+          <t>46.0 kg</t>
+        </is>
+      </c>
+      <c r="G558" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H558" s="30" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="I558" s="30" t="inlineStr">
+        <is>
+          <t>Saf 2</t>
+        </is>
+      </c>
+      <c r="J558" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="559" ht="20" customHeight="1">
+      <c r="B559" s="28" t="n">
+        <v>531</v>
+      </c>
+      <c r="C559" s="18" t="n">
+        <v>546</v>
+      </c>
+      <c r="D559" s="19" t="inlineStr">
+        <is>
+          <t>33831</t>
+        </is>
+      </c>
+      <c r="E559" s="28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F559" s="29" t="inlineStr">
+        <is>
+          <t>34.0 kg</t>
+        </is>
+      </c>
+      <c r="G559" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H559" s="28" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="I559" s="28" t="inlineStr">
+        <is>
+          <t>Saf 3</t>
+        </is>
+      </c>
+      <c r="J559" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="560" ht="20" customHeight="1">
+      <c r="B560" s="30" t="n">
+        <v>532</v>
+      </c>
+      <c r="C560" s="31" t="n">
+        <v>573</v>
+      </c>
+      <c r="D560" s="32" t="inlineStr">
+        <is>
+          <t>34704</t>
+        </is>
+      </c>
+      <c r="E560" s="30" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F560" s="33" t="inlineStr">
+        <is>
+          <t>40.0 kg</t>
+        </is>
+      </c>
+      <c r="G560" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H560" s="30" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="I560" s="30" t="inlineStr">
+        <is>
+          <t>Saf 4</t>
+        </is>
+      </c>
+      <c r="J560" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="561" ht="20" customHeight="1">
+      <c r="B561" s="28" t="n">
+        <v>533</v>
+      </c>
+      <c r="C561" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="D561" s="19" t="inlineStr">
+        <is>
+          <t>942825</t>
+        </is>
+      </c>
+      <c r="E561" s="28" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F561" s="29" t="inlineStr">
+        <is>
+          <t>50.0 kg</t>
+        </is>
+      </c>
+      <c r="G561" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H561" s="28" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="I561" s="28" t="inlineStr">
+        <is>
+          <t>Saf 5</t>
+        </is>
+      </c>
+      <c r="J561" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="562" ht="20" customHeight="1">
+      <c r="B562" s="30" t="n">
+        <v>534</v>
+      </c>
+      <c r="C562" s="31" t="n">
         <v>560</v>
       </c>
-      <c r="D537" s="19" t="inlineStr">
+      <c r="D562" s="32" t="inlineStr">
         <is>
           <t>34464</t>
         </is>
       </c>
-      <c r="E537" s="28" t="inlineStr">
+      <c r="E562" s="30" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="F537" s="29" t="inlineStr">
+      <c r="F562" s="33" t="inlineStr">
         <is>
           <t>31.0 kg</t>
         </is>
       </c>
-      <c r="G537" s="28" t="inlineStr">
+      <c r="G562" s="30" t="inlineStr">
         <is>
           <t>BLOK 16</t>
         </is>
       </c>
-      <c r="H537" s="28" t="inlineStr">
+      <c r="H562" s="30" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="I537" s="28" t="inlineStr">
+      <c r="I562" s="30" t="inlineStr">
         <is>
           <t>Saf 6</t>
         </is>
       </c>
-      <c r="J537" s="28" t="inlineStr">
+      <c r="J562" s="30" t="inlineStr">
         <is>
           <t>SELESAI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B28:J537"/>
+  <autoFilter ref="B28:J562"/>
   <mergeCells count="1">
     <mergeCell ref="B24:D24"/>
   </mergeCells>

--- a/c.xlsx
+++ b/c.xlsx
@@ -5159,16 +5159,16 @@
         </is>
       </c>
       <c r="F83" s="11" t="n">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>39096</t>
+          <t>39097</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t>44 kg</t>
+          <t>39 kg</t>
         </is>
       </c>
       <c r="I83" s="11" t="n">
@@ -13043,7 +13043,7 @@
         <v>680</v>
       </c>
       <c r="D69" s="14" t="n">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E69" s="14" t="n">
         <v>693</v>
@@ -18206,16 +18206,16 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>39096</t>
+          <t>39097</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>44 kg</t>
+          <t>39 kg</t>
         </is>
       </c>
       <c r="G49" s="18" t="n">
@@ -23025,7 +23025,7 @@
         <v>7</v>
       </c>
       <c r="I14" s="23" t="n">
-        <v>1401</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -32932,11 +32932,11 @@
         <v>223</v>
       </c>
       <c r="C251" s="18" t="n">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D251" s="19" t="inlineStr">
         <is>
-          <t>39096</t>
+          <t>39097</t>
         </is>
       </c>
       <c r="E251" s="28" t="inlineStr">
@@ -32946,7 +32946,7 @@
       </c>
       <c r="F251" s="29" t="inlineStr">
         <is>
-          <t>44 kg</t>
+          <t>39 kg</t>
         </is>
       </c>
       <c r="G251" s="28" t="inlineStr">

--- a/c.xlsx
+++ b/c.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Rekapitulasi &amp; Cari Bal" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rekapitulasi &amp; Cari Bal'!$B$28:$J$562</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rekapitulasi &amp; Cari Bal'!$B$28:$J$580</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9320,12 +9320,32 @@
           <t>35 kg</t>
         </is>
       </c>
-      <c r="O154" s="11" t="inlineStr"/>
-      <c r="P154" s="12" t="inlineStr"/>
-      <c r="Q154" s="13" t="inlineStr"/>
-      <c r="R154" s="11" t="inlineStr"/>
-      <c r="S154" s="12" t="inlineStr"/>
-      <c r="T154" s="13" t="inlineStr"/>
+      <c r="O154" s="11" t="n">
+        <v>757</v>
+      </c>
+      <c r="P154" s="12" t="inlineStr">
+        <is>
+          <t>123596</t>
+        </is>
+      </c>
+      <c r="Q154" s="13" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
+      <c r="R154" s="11" t="n">
+        <v>759</v>
+      </c>
+      <c r="S154" s="12" t="inlineStr">
+        <is>
+          <t>123593</t>
+        </is>
+      </c>
+      <c r="T154" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="17" customHeight="1">
       <c r="B155" s="9" t="inlineStr">
@@ -9385,12 +9405,32 @@
           <t>40 kg</t>
         </is>
       </c>
-      <c r="O155" s="11" t="inlineStr"/>
-      <c r="P155" s="12" t="inlineStr"/>
-      <c r="Q155" s="13" t="inlineStr"/>
-      <c r="R155" s="11" t="inlineStr"/>
-      <c r="S155" s="12" t="inlineStr"/>
-      <c r="T155" s="13" t="inlineStr"/>
+      <c r="O155" s="11" t="n">
+        <v>756</v>
+      </c>
+      <c r="P155" s="12" t="inlineStr">
+        <is>
+          <t>123592</t>
+        </is>
+      </c>
+      <c r="Q155" s="13" t="inlineStr">
+        <is>
+          <t>41 kg</t>
+        </is>
+      </c>
+      <c r="R155" s="11" t="n">
+        <v>758</v>
+      </c>
+      <c r="S155" s="12" t="inlineStr">
+        <is>
+          <t>123595</t>
+        </is>
+      </c>
+      <c r="T155" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="17" customHeight="1">
       <c r="B156" s="9" t="inlineStr">
@@ -9933,24 +9973,84 @@
           <t>T6</t>
         </is>
       </c>
-      <c r="C166" s="10" t="inlineStr"/>
-      <c r="D166" s="10" t="inlineStr"/>
-      <c r="E166" s="10" t="inlineStr"/>
-      <c r="F166" s="10" t="inlineStr"/>
-      <c r="G166" s="10" t="inlineStr"/>
-      <c r="H166" s="10" t="inlineStr"/>
-      <c r="I166" s="10" t="inlineStr"/>
-      <c r="J166" s="10" t="inlineStr"/>
-      <c r="K166" s="10" t="inlineStr"/>
-      <c r="L166" s="10" t="inlineStr"/>
-      <c r="M166" s="10" t="inlineStr"/>
-      <c r="N166" s="10" t="inlineStr"/>
-      <c r="O166" s="10" t="inlineStr"/>
-      <c r="P166" s="10" t="inlineStr"/>
-      <c r="Q166" s="10" t="inlineStr"/>
-      <c r="R166" s="10" t="inlineStr"/>
-      <c r="S166" s="10" t="inlineStr"/>
-      <c r="T166" s="10" t="inlineStr"/>
+      <c r="C166" s="11" t="n">
+        <v>796</v>
+      </c>
+      <c r="D166" s="12" t="inlineStr">
+        <is>
+          <t>123367</t>
+        </is>
+      </c>
+      <c r="E166" s="13" t="inlineStr">
+        <is>
+          <t>40 kg</t>
+        </is>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>792</v>
+      </c>
+      <c r="G166" s="12" t="inlineStr">
+        <is>
+          <t>123422</t>
+        </is>
+      </c>
+      <c r="H166" s="13" t="inlineStr">
+        <is>
+          <t>46 kg</t>
+        </is>
+      </c>
+      <c r="I166" s="11" t="n">
+        <v>797</v>
+      </c>
+      <c r="J166" s="12" t="inlineStr">
+        <is>
+          <t>123368</t>
+        </is>
+      </c>
+      <c r="K166" s="13" t="inlineStr">
+        <is>
+          <t>50 kg</t>
+        </is>
+      </c>
+      <c r="L166" s="11" t="n">
+        <v>807</v>
+      </c>
+      <c r="M166" s="12" t="inlineStr">
+        <is>
+          <t>123364</t>
+        </is>
+      </c>
+      <c r="N166" s="13" t="inlineStr">
+        <is>
+          <t>49 kg</t>
+        </is>
+      </c>
+      <c r="O166" s="11" t="n">
+        <v>798</v>
+      </c>
+      <c r="P166" s="12" t="inlineStr">
+        <is>
+          <t>123591</t>
+        </is>
+      </c>
+      <c r="Q166" s="13" t="inlineStr">
+        <is>
+          <t>32 kg</t>
+        </is>
+      </c>
+      <c r="R166" s="11" t="n">
+        <v>801</v>
+      </c>
+      <c r="S166" s="12" t="inlineStr">
+        <is>
+          <t>123366</t>
+        </is>
+      </c>
+      <c r="T166" s="13" t="inlineStr">
+        <is>
+          <t>32 kg</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="17" customHeight="1">
       <c r="B167" s="9" t="inlineStr">
@@ -9958,24 +10058,84 @@
           <t>T5</t>
         </is>
       </c>
-      <c r="C167" s="10" t="inlineStr"/>
-      <c r="D167" s="10" t="inlineStr"/>
-      <c r="E167" s="10" t="inlineStr"/>
-      <c r="F167" s="10" t="inlineStr"/>
-      <c r="G167" s="10" t="inlineStr"/>
-      <c r="H167" s="10" t="inlineStr"/>
-      <c r="I167" s="10" t="inlineStr"/>
-      <c r="J167" s="10" t="inlineStr"/>
-      <c r="K167" s="10" t="inlineStr"/>
-      <c r="L167" s="10" t="inlineStr"/>
-      <c r="M167" s="10" t="inlineStr"/>
-      <c r="N167" s="10" t="inlineStr"/>
-      <c r="O167" s="10" t="inlineStr"/>
-      <c r="P167" s="10" t="inlineStr"/>
-      <c r="Q167" s="10" t="inlineStr"/>
-      <c r="R167" s="10" t="inlineStr"/>
-      <c r="S167" s="10" t="inlineStr"/>
-      <c r="T167" s="10" t="inlineStr"/>
+      <c r="C167" s="11" t="n">
+        <v>791</v>
+      </c>
+      <c r="D167" s="12" t="inlineStr">
+        <is>
+          <t>123423</t>
+        </is>
+      </c>
+      <c r="E167" s="13" t="inlineStr">
+        <is>
+          <t>44 kg</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>795</v>
+      </c>
+      <c r="G167" s="12" t="inlineStr">
+        <is>
+          <t>39351</t>
+        </is>
+      </c>
+      <c r="H167" s="13" t="inlineStr">
+        <is>
+          <t>30 kg</t>
+        </is>
+      </c>
+      <c r="I167" s="11" t="n">
+        <v>790</v>
+      </c>
+      <c r="J167" s="12" t="inlineStr">
+        <is>
+          <t>123420</t>
+        </is>
+      </c>
+      <c r="K167" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
+      <c r="L167" s="11" t="n">
+        <v>802</v>
+      </c>
+      <c r="M167" s="12" t="inlineStr">
+        <is>
+          <t>123365</t>
+        </is>
+      </c>
+      <c r="N167" s="13" t="inlineStr">
+        <is>
+          <t>36 kg</t>
+        </is>
+      </c>
+      <c r="O167" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="P167" s="12" t="inlineStr">
+        <is>
+          <t>39350</t>
+        </is>
+      </c>
+      <c r="Q167" s="13" t="inlineStr">
+        <is>
+          <t>33 kg</t>
+        </is>
+      </c>
+      <c r="R167" s="11" t="n">
+        <v>760</v>
+      </c>
+      <c r="S167" s="12" t="inlineStr">
+        <is>
+          <t>123594</t>
+        </is>
+      </c>
+      <c r="T167" s="13" t="inlineStr">
+        <is>
+          <t>41 kg</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="17" customHeight="1">
       <c r="B168" s="9" t="inlineStr">
@@ -10516,24 +10676,34 @@
           <t>T6</t>
         </is>
       </c>
-      <c r="C178" s="10" t="inlineStr"/>
-      <c r="D178" s="10" t="inlineStr"/>
-      <c r="E178" s="10" t="inlineStr"/>
-      <c r="F178" s="10" t="inlineStr"/>
-      <c r="G178" s="10" t="inlineStr"/>
-      <c r="H178" s="10" t="inlineStr"/>
-      <c r="I178" s="10" t="inlineStr"/>
-      <c r="J178" s="10" t="inlineStr"/>
-      <c r="K178" s="10" t="inlineStr"/>
-      <c r="L178" s="10" t="inlineStr"/>
-      <c r="M178" s="10" t="inlineStr"/>
-      <c r="N178" s="10" t="inlineStr"/>
-      <c r="O178" s="10" t="inlineStr"/>
-      <c r="P178" s="10" t="inlineStr"/>
-      <c r="Q178" s="10" t="inlineStr"/>
-      <c r="R178" s="10" t="inlineStr"/>
-      <c r="S178" s="10" t="inlineStr"/>
-      <c r="T178" s="10" t="inlineStr"/>
+      <c r="C178" s="11" t="inlineStr"/>
+      <c r="D178" s="12" t="inlineStr"/>
+      <c r="E178" s="13" t="inlineStr"/>
+      <c r="F178" s="11" t="inlineStr"/>
+      <c r="G178" s="12" t="inlineStr"/>
+      <c r="H178" s="13" t="inlineStr"/>
+      <c r="I178" s="11" t="inlineStr"/>
+      <c r="J178" s="12" t="inlineStr"/>
+      <c r="K178" s="13" t="inlineStr"/>
+      <c r="L178" s="11" t="inlineStr"/>
+      <c r="M178" s="12" t="inlineStr"/>
+      <c r="N178" s="13" t="inlineStr"/>
+      <c r="O178" s="11" t="inlineStr"/>
+      <c r="P178" s="12" t="inlineStr"/>
+      <c r="Q178" s="13" t="inlineStr"/>
+      <c r="R178" s="11" t="n">
+        <v>793</v>
+      </c>
+      <c r="S178" s="12" t="inlineStr">
+        <is>
+          <t>123421</t>
+        </is>
+      </c>
+      <c r="T178" s="13" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="17" customHeight="1">
       <c r="B179" s="9" t="inlineStr">
@@ -10541,24 +10711,34 @@
           <t>T5</t>
         </is>
       </c>
-      <c r="C179" s="10" t="inlineStr"/>
-      <c r="D179" s="10" t="inlineStr"/>
-      <c r="E179" s="10" t="inlineStr"/>
-      <c r="F179" s="10" t="inlineStr"/>
-      <c r="G179" s="10" t="inlineStr"/>
-      <c r="H179" s="10" t="inlineStr"/>
-      <c r="I179" s="10" t="inlineStr"/>
-      <c r="J179" s="10" t="inlineStr"/>
-      <c r="K179" s="10" t="inlineStr"/>
-      <c r="L179" s="10" t="inlineStr"/>
-      <c r="M179" s="10" t="inlineStr"/>
-      <c r="N179" s="10" t="inlineStr"/>
-      <c r="O179" s="10" t="inlineStr"/>
-      <c r="P179" s="10" t="inlineStr"/>
-      <c r="Q179" s="10" t="inlineStr"/>
-      <c r="R179" s="10" t="inlineStr"/>
-      <c r="S179" s="10" t="inlineStr"/>
-      <c r="T179" s="10" t="inlineStr"/>
+      <c r="C179" s="11" t="inlineStr"/>
+      <c r="D179" s="12" t="inlineStr"/>
+      <c r="E179" s="13" t="inlineStr"/>
+      <c r="F179" s="11" t="inlineStr"/>
+      <c r="G179" s="12" t="inlineStr"/>
+      <c r="H179" s="13" t="inlineStr"/>
+      <c r="I179" s="11" t="inlineStr"/>
+      <c r="J179" s="12" t="inlineStr"/>
+      <c r="K179" s="13" t="inlineStr"/>
+      <c r="L179" s="11" t="inlineStr"/>
+      <c r="M179" s="12" t="inlineStr"/>
+      <c r="N179" s="13" t="inlineStr"/>
+      <c r="O179" s="11" t="inlineStr"/>
+      <c r="P179" s="12" t="inlineStr"/>
+      <c r="Q179" s="13" t="inlineStr"/>
+      <c r="R179" s="11" t="n">
+        <v>794</v>
+      </c>
+      <c r="S179" s="12" t="inlineStr">
+        <is>
+          <t>39352</t>
+        </is>
+      </c>
+      <c r="T179" s="13" t="inlineStr">
+        <is>
+          <t>50 kg</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="17" customHeight="1">
       <c r="B180" s="9" t="inlineStr">
@@ -14308,8 +14488,12 @@
       <c r="F128" s="14" t="n">
         <v>772</v>
       </c>
-      <c r="G128" s="14" t="inlineStr"/>
-      <c r="H128" s="14" t="inlineStr"/>
+      <c r="G128" s="14" t="n">
+        <v>757</v>
+      </c>
+      <c r="H128" s="14" t="n">
+        <v>759</v>
+      </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="B129" s="9" t="inlineStr">
@@ -14329,8 +14513,12 @@
       <c r="F129" s="14" t="n">
         <v>749</v>
       </c>
-      <c r="G129" s="14" t="inlineStr"/>
-      <c r="H129" s="14" t="inlineStr"/>
+      <c r="G129" s="14" t="n">
+        <v>756</v>
+      </c>
+      <c r="H129" s="14" t="n">
+        <v>758</v>
+      </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="B130" s="9" t="inlineStr">
@@ -14504,12 +14692,24 @@
           <t>T6</t>
         </is>
       </c>
-      <c r="C138" s="10" t="inlineStr"/>
-      <c r="D138" s="10" t="inlineStr"/>
-      <c r="E138" s="10" t="inlineStr"/>
-      <c r="F138" s="10" t="inlineStr"/>
-      <c r="G138" s="10" t="inlineStr"/>
-      <c r="H138" s="10" t="inlineStr"/>
+      <c r="C138" s="14" t="n">
+        <v>796</v>
+      </c>
+      <c r="D138" s="14" t="n">
+        <v>792</v>
+      </c>
+      <c r="E138" s="14" t="n">
+        <v>797</v>
+      </c>
+      <c r="F138" s="14" t="n">
+        <v>807</v>
+      </c>
+      <c r="G138" s="14" t="n">
+        <v>798</v>
+      </c>
+      <c r="H138" s="14" t="n">
+        <v>801</v>
+      </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="B139" s="9" t="inlineStr">
@@ -14517,12 +14717,24 @@
           <t>T5</t>
         </is>
       </c>
-      <c r="C139" s="10" t="inlineStr"/>
-      <c r="D139" s="10" t="inlineStr"/>
-      <c r="E139" s="10" t="inlineStr"/>
-      <c r="F139" s="10" t="inlineStr"/>
-      <c r="G139" s="10" t="inlineStr"/>
-      <c r="H139" s="10" t="inlineStr"/>
+      <c r="C139" s="14" t="n">
+        <v>791</v>
+      </c>
+      <c r="D139" s="14" t="n">
+        <v>795</v>
+      </c>
+      <c r="E139" s="14" t="n">
+        <v>790</v>
+      </c>
+      <c r="F139" s="14" t="n">
+        <v>802</v>
+      </c>
+      <c r="G139" s="14" t="n">
+        <v>800</v>
+      </c>
+      <c r="H139" s="14" t="n">
+        <v>760</v>
+      </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="B140" s="9" t="inlineStr">
@@ -14694,12 +14906,14 @@
           <t>T6</t>
         </is>
       </c>
-      <c r="C148" s="10" t="inlineStr"/>
-      <c r="D148" s="10" t="inlineStr"/>
-      <c r="E148" s="10" t="inlineStr"/>
-      <c r="F148" s="10" t="inlineStr"/>
-      <c r="G148" s="10" t="inlineStr"/>
-      <c r="H148" s="10" t="inlineStr"/>
+      <c r="C148" s="14" t="inlineStr"/>
+      <c r="D148" s="14" t="inlineStr"/>
+      <c r="E148" s="14" t="inlineStr"/>
+      <c r="F148" s="14" t="inlineStr"/>
+      <c r="G148" s="14" t="inlineStr"/>
+      <c r="H148" s="14" t="n">
+        <v>793</v>
+      </c>
     </row>
     <row r="149" ht="18" customHeight="1">
       <c r="B149" s="9" t="inlineStr">
@@ -14707,12 +14921,14 @@
           <t>T5</t>
         </is>
       </c>
-      <c r="C149" s="10" t="inlineStr"/>
-      <c r="D149" s="10" t="inlineStr"/>
-      <c r="E149" s="10" t="inlineStr"/>
-      <c r="F149" s="10" t="inlineStr"/>
-      <c r="G149" s="10" t="inlineStr"/>
-      <c r="H149" s="10" t="inlineStr"/>
+      <c r="C149" s="14" t="inlineStr"/>
+      <c r="D149" s="14" t="inlineStr"/>
+      <c r="E149" s="14" t="inlineStr"/>
+      <c r="F149" s="14" t="inlineStr"/>
+      <c r="G149" s="14" t="inlineStr"/>
+      <c r="H149" s="14" t="n">
+        <v>794</v>
+      </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="B150" s="9" t="inlineStr">
@@ -21172,12 +21388,32 @@
           <t>35 kg</t>
         </is>
       </c>
-      <c r="M90" s="18" t="inlineStr"/>
-      <c r="N90" s="19" t="inlineStr"/>
-      <c r="O90" s="13" t="inlineStr"/>
-      <c r="P90" s="18" t="inlineStr"/>
-      <c r="Q90" s="19" t="inlineStr"/>
-      <c r="R90" s="13" t="inlineStr"/>
+      <c r="M90" s="18" t="n">
+        <v>757</v>
+      </c>
+      <c r="N90" s="19" t="inlineStr">
+        <is>
+          <t>123596</t>
+        </is>
+      </c>
+      <c r="O90" s="13" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
+      <c r="P90" s="18" t="n">
+        <v>759</v>
+      </c>
+      <c r="Q90" s="19" t="inlineStr">
+        <is>
+          <t>123593</t>
+        </is>
+      </c>
+      <c r="R90" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="18" t="n">
@@ -21232,12 +21468,32 @@
           <t>40 kg</t>
         </is>
       </c>
-      <c r="M91" s="18" t="inlineStr"/>
-      <c r="N91" s="19" t="inlineStr"/>
-      <c r="O91" s="13" t="inlineStr"/>
-      <c r="P91" s="18" t="inlineStr"/>
-      <c r="Q91" s="19" t="inlineStr"/>
-      <c r="R91" s="13" t="inlineStr"/>
+      <c r="M91" s="18" t="n">
+        <v>756</v>
+      </c>
+      <c r="N91" s="19" t="inlineStr">
+        <is>
+          <t>123592</t>
+        </is>
+      </c>
+      <c r="O91" s="13" t="inlineStr">
+        <is>
+          <t>41 kg</t>
+        </is>
+      </c>
+      <c r="P91" s="18" t="n">
+        <v>758</v>
+      </c>
+      <c r="Q91" s="19" t="inlineStr">
+        <is>
+          <t>123595</t>
+        </is>
+      </c>
+      <c r="R91" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="18" t="n">
@@ -21585,44 +21841,164 @@
       <c r="R96" s="17" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="17" t="n"/>
-      <c r="B97" s="17" t="n"/>
-      <c r="C97" s="17" t="n"/>
-      <c r="D97" s="17" t="n"/>
-      <c r="E97" s="17" t="n"/>
-      <c r="F97" s="17" t="n"/>
-      <c r="G97" s="17" t="n"/>
-      <c r="H97" s="17" t="n"/>
-      <c r="I97" s="17" t="n"/>
-      <c r="J97" s="17" t="n"/>
-      <c r="K97" s="17" t="n"/>
-      <c r="L97" s="17" t="n"/>
-      <c r="M97" s="17" t="n"/>
-      <c r="N97" s="17" t="n"/>
-      <c r="O97" s="17" t="n"/>
-      <c r="P97" s="17" t="n"/>
-      <c r="Q97" s="17" t="n"/>
-      <c r="R97" s="17" t="n"/>
+      <c r="A97" s="18" t="n">
+        <v>796</v>
+      </c>
+      <c r="B97" s="19" t="inlineStr">
+        <is>
+          <t>123367</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>40 kg</t>
+        </is>
+      </c>
+      <c r="D97" s="18" t="n">
+        <v>792</v>
+      </c>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>123422</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="inlineStr">
+        <is>
+          <t>46 kg</t>
+        </is>
+      </c>
+      <c r="G97" s="18" t="n">
+        <v>797</v>
+      </c>
+      <c r="H97" s="19" t="inlineStr">
+        <is>
+          <t>123368</t>
+        </is>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>50 kg</t>
+        </is>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>807</v>
+      </c>
+      <c r="K97" s="19" t="inlineStr">
+        <is>
+          <t>123364</t>
+        </is>
+      </c>
+      <c r="L97" s="13" t="inlineStr">
+        <is>
+          <t>49 kg</t>
+        </is>
+      </c>
+      <c r="M97" s="18" t="n">
+        <v>798</v>
+      </c>
+      <c r="N97" s="19" t="inlineStr">
+        <is>
+          <t>123591</t>
+        </is>
+      </c>
+      <c r="O97" s="13" t="inlineStr">
+        <is>
+          <t>32 kg</t>
+        </is>
+      </c>
+      <c r="P97" s="18" t="n">
+        <v>801</v>
+      </c>
+      <c r="Q97" s="19" t="inlineStr">
+        <is>
+          <t>123366</t>
+        </is>
+      </c>
+      <c r="R97" s="13" t="inlineStr">
+        <is>
+          <t>32 kg</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="17" t="n"/>
-      <c r="B98" s="17" t="n"/>
-      <c r="C98" s="17" t="n"/>
-      <c r="D98" s="17" t="n"/>
-      <c r="E98" s="17" t="n"/>
-      <c r="F98" s="17" t="n"/>
-      <c r="G98" s="17" t="n"/>
-      <c r="H98" s="17" t="n"/>
-      <c r="I98" s="17" t="n"/>
-      <c r="J98" s="17" t="n"/>
-      <c r="K98" s="17" t="n"/>
-      <c r="L98" s="17" t="n"/>
-      <c r="M98" s="17" t="n"/>
-      <c r="N98" s="17" t="n"/>
-      <c r="O98" s="17" t="n"/>
-      <c r="P98" s="17" t="n"/>
-      <c r="Q98" s="17" t="n"/>
-      <c r="R98" s="17" t="n"/>
+      <c r="A98" s="18" t="n">
+        <v>791</v>
+      </c>
+      <c r="B98" s="19" t="inlineStr">
+        <is>
+          <t>123423</t>
+        </is>
+      </c>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>44 kg</t>
+        </is>
+      </c>
+      <c r="D98" s="18" t="n">
+        <v>795</v>
+      </c>
+      <c r="E98" s="19" t="inlineStr">
+        <is>
+          <t>39351</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="inlineStr">
+        <is>
+          <t>30 kg</t>
+        </is>
+      </c>
+      <c r="G98" s="18" t="n">
+        <v>790</v>
+      </c>
+      <c r="H98" s="19" t="inlineStr">
+        <is>
+          <t>123420</t>
+        </is>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>37 kg</t>
+        </is>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>802</v>
+      </c>
+      <c r="K98" s="19" t="inlineStr">
+        <is>
+          <t>123365</t>
+        </is>
+      </c>
+      <c r="L98" s="13" t="inlineStr">
+        <is>
+          <t>36 kg</t>
+        </is>
+      </c>
+      <c r="M98" s="18" t="n">
+        <v>800</v>
+      </c>
+      <c r="N98" s="19" t="inlineStr">
+        <is>
+          <t>39350</t>
+        </is>
+      </c>
+      <c r="O98" s="13" t="inlineStr">
+        <is>
+          <t>33 kg</t>
+        </is>
+      </c>
+      <c r="P98" s="18" t="n">
+        <v>760</v>
+      </c>
+      <c r="Q98" s="19" t="inlineStr">
+        <is>
+          <t>123594</t>
+        </is>
+      </c>
+      <c r="R98" s="13" t="inlineStr">
+        <is>
+          <t>41 kg</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="18" t="n">
@@ -21968,44 +22344,64 @@
       <c r="R103" s="17" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="17" t="n"/>
-      <c r="B104" s="17" t="n"/>
-      <c r="C104" s="17" t="n"/>
-      <c r="D104" s="17" t="n"/>
-      <c r="E104" s="17" t="n"/>
-      <c r="F104" s="17" t="n"/>
-      <c r="G104" s="17" t="n"/>
-      <c r="H104" s="17" t="n"/>
-      <c r="I104" s="17" t="n"/>
-      <c r="J104" s="17" t="n"/>
-      <c r="K104" s="17" t="n"/>
-      <c r="L104" s="17" t="n"/>
-      <c r="M104" s="17" t="n"/>
-      <c r="N104" s="17" t="n"/>
-      <c r="O104" s="17" t="n"/>
-      <c r="P104" s="17" t="n"/>
-      <c r="Q104" s="17" t="n"/>
-      <c r="R104" s="17" t="n"/>
+      <c r="A104" s="18" t="inlineStr"/>
+      <c r="B104" s="19" t="inlineStr"/>
+      <c r="C104" s="13" t="inlineStr"/>
+      <c r="D104" s="18" t="inlineStr"/>
+      <c r="E104" s="19" t="inlineStr"/>
+      <c r="F104" s="13" t="inlineStr"/>
+      <c r="G104" s="18" t="inlineStr"/>
+      <c r="H104" s="19" t="inlineStr"/>
+      <c r="I104" s="13" t="inlineStr"/>
+      <c r="J104" s="18" t="inlineStr"/>
+      <c r="K104" s="19" t="inlineStr"/>
+      <c r="L104" s="13" t="inlineStr"/>
+      <c r="M104" s="18" t="inlineStr"/>
+      <c r="N104" s="19" t="inlineStr"/>
+      <c r="O104" s="13" t="inlineStr"/>
+      <c r="P104" s="18" t="n">
+        <v>793</v>
+      </c>
+      <c r="Q104" s="19" t="inlineStr">
+        <is>
+          <t>123421</t>
+        </is>
+      </c>
+      <c r="R104" s="13" t="inlineStr">
+        <is>
+          <t>35 kg</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="17" t="n"/>
-      <c r="B105" s="17" t="n"/>
-      <c r="C105" s="17" t="n"/>
-      <c r="D105" s="17" t="n"/>
-      <c r="E105" s="17" t="n"/>
-      <c r="F105" s="17" t="n"/>
-      <c r="G105" s="17" t="n"/>
-      <c r="H105" s="17" t="n"/>
-      <c r="I105" s="17" t="n"/>
-      <c r="J105" s="17" t="n"/>
-      <c r="K105" s="17" t="n"/>
-      <c r="L105" s="17" t="n"/>
-      <c r="M105" s="17" t="n"/>
-      <c r="N105" s="17" t="n"/>
-      <c r="O105" s="17" t="n"/>
-      <c r="P105" s="17" t="n"/>
-      <c r="Q105" s="17" t="n"/>
-      <c r="R105" s="17" t="n"/>
+      <c r="A105" s="18" t="inlineStr"/>
+      <c r="B105" s="19" t="inlineStr"/>
+      <c r="C105" s="13" t="inlineStr"/>
+      <c r="D105" s="18" t="inlineStr"/>
+      <c r="E105" s="19" t="inlineStr"/>
+      <c r="F105" s="13" t="inlineStr"/>
+      <c r="G105" s="18" t="inlineStr"/>
+      <c r="H105" s="19" t="inlineStr"/>
+      <c r="I105" s="13" t="inlineStr"/>
+      <c r="J105" s="18" t="inlineStr"/>
+      <c r="K105" s="19" t="inlineStr"/>
+      <c r="L105" s="13" t="inlineStr"/>
+      <c r="M105" s="18" t="inlineStr"/>
+      <c r="N105" s="19" t="inlineStr"/>
+      <c r="O105" s="13" t="inlineStr"/>
+      <c r="P105" s="18" t="n">
+        <v>794</v>
+      </c>
+      <c r="Q105" s="19" t="inlineStr">
+        <is>
+          <t>39352</t>
+        </is>
+      </c>
+      <c r="R105" s="13" t="inlineStr">
+        <is>
+          <t>50 kg</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="18" t="n">
@@ -22733,7 +23129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:J562"/>
+  <dimension ref="B2:J580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -23199,13 +23595,13 @@
         <v>42</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I20" s="23" t="n">
-        <v>1315</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -23229,13 +23625,13 @@
         <v>42</v>
       </c>
       <c r="G21" s="25" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>945</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -23259,13 +23655,13 @@
         <v>42</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I22" s="23" t="n">
-        <v>932</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -42048,21 +42444,21 @@
         <v>435</v>
       </c>
       <c r="C463" s="18" t="n">
-        <v>773</v>
+        <v>757</v>
       </c>
       <c r="D463" s="19" t="inlineStr">
         <is>
-          <t>940841</t>
+          <t>123596</t>
         </is>
       </c>
       <c r="E463" s="28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F463" s="29" t="inlineStr">
         <is>
-          <t>37 kg</t>
+          <t>35 kg</t>
         </is>
       </c>
       <c r="G463" s="28" t="inlineStr">
@@ -42072,12 +42468,12 @@
       </c>
       <c r="H463" s="28" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I463" s="28" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J463" s="28" t="inlineStr">
@@ -42091,21 +42487,21 @@
         <v>436</v>
       </c>
       <c r="C464" s="31" t="n">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="D464" s="32" t="inlineStr">
         <is>
-          <t>123303</t>
+          <t>123593</t>
         </is>
       </c>
       <c r="E464" s="30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F464" s="33" t="inlineStr">
         <is>
-          <t>48 kg</t>
+          <t>37 kg</t>
         </is>
       </c>
       <c r="G464" s="30" t="inlineStr">
@@ -42115,12 +42511,12 @@
       </c>
       <c r="H464" s="30" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I464" s="30" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J464" s="30" t="inlineStr">
@@ -42134,16 +42530,16 @@
         <v>437</v>
       </c>
       <c r="C465" s="18" t="n">
-        <v>753</v>
+        <v>773</v>
       </c>
       <c r="D465" s="19" t="inlineStr">
         <is>
-          <t>123302</t>
+          <t>940841</t>
         </is>
       </c>
       <c r="E465" s="28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F465" s="29" t="inlineStr">
@@ -42163,7 +42559,7 @@
       </c>
       <c r="I465" s="28" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J465" s="28" t="inlineStr">
@@ -42177,21 +42573,21 @@
         <v>438</v>
       </c>
       <c r="C466" s="31" t="n">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="D466" s="32" t="inlineStr">
         <is>
-          <t>123301</t>
+          <t>123303</t>
         </is>
       </c>
       <c r="E466" s="30" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F466" s="33" t="inlineStr">
         <is>
-          <t>40 kg</t>
+          <t>48 kg</t>
         </is>
       </c>
       <c r="G466" s="30" t="inlineStr">
@@ -42206,7 +42602,7 @@
       </c>
       <c r="I466" s="30" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J466" s="30" t="inlineStr">
@@ -42220,21 +42616,21 @@
         <v>439</v>
       </c>
       <c r="C467" s="18" t="n">
-        <v>535</v>
+        <v>753</v>
       </c>
       <c r="D467" s="19" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>123302</t>
         </is>
       </c>
       <c r="E467" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F467" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>37 kg</t>
         </is>
       </c>
       <c r="G467" s="28" t="inlineStr">
@@ -42244,12 +42640,12 @@
       </c>
       <c r="H467" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I467" s="28" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J467" s="28" t="inlineStr">
@@ -42263,11 +42659,11 @@
         <v>440</v>
       </c>
       <c r="C468" s="31" t="n">
-        <v>531</v>
+        <v>749</v>
       </c>
       <c r="D468" s="32" t="inlineStr">
         <is>
-          <t>34235</t>
+          <t>123301</t>
         </is>
       </c>
       <c r="E468" s="30" t="inlineStr">
@@ -42277,7 +42673,7 @@
       </c>
       <c r="F468" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>40 kg</t>
         </is>
       </c>
       <c r="G468" s="30" t="inlineStr">
@@ -42287,12 +42683,12 @@
       </c>
       <c r="H468" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I468" s="30" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J468" s="30" t="inlineStr">
@@ -42306,21 +42702,21 @@
         <v>441</v>
       </c>
       <c r="C469" s="18" t="n">
-        <v>63</v>
+        <v>756</v>
       </c>
       <c r="D469" s="19" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>123592</t>
         </is>
       </c>
       <c r="E469" s="28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F469" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>41 kg</t>
         </is>
       </c>
       <c r="G469" s="28" t="inlineStr">
@@ -42330,12 +42726,12 @@
       </c>
       <c r="H469" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I469" s="28" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J469" s="28" t="inlineStr">
@@ -42349,21 +42745,21 @@
         <v>442</v>
       </c>
       <c r="C470" s="31" t="n">
-        <v>168</v>
+        <v>758</v>
       </c>
       <c r="D470" s="32" t="inlineStr">
         <is>
-          <t>31738</t>
+          <t>123595</t>
         </is>
       </c>
       <c r="E470" s="30" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F470" s="33" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>37 kg</t>
         </is>
       </c>
       <c r="G470" s="30" t="inlineStr">
@@ -42373,12 +42769,12 @@
       </c>
       <c r="H470" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I470" s="30" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J470" s="30" t="inlineStr">
@@ -42392,21 +42788,21 @@
         <v>443</v>
       </c>
       <c r="C471" s="18" t="n">
-        <v>372</v>
+        <v>535</v>
       </c>
       <c r="D471" s="19" t="inlineStr">
         <is>
-          <t>30629</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="E471" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F471" s="29" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G471" s="28" t="inlineStr">
@@ -42421,7 +42817,7 @@
       </c>
       <c r="I471" s="28" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J471" s="28" t="inlineStr">
@@ -42435,21 +42831,21 @@
         <v>444</v>
       </c>
       <c r="C472" s="31" t="n">
-        <v>402</v>
+        <v>531</v>
       </c>
       <c r="D472" s="32" t="inlineStr">
         <is>
-          <t>31628</t>
+          <t>34235</t>
         </is>
       </c>
       <c r="E472" s="30" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F472" s="33" t="inlineStr">
         <is>
-          <t>35.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G472" s="30" t="inlineStr">
@@ -42464,7 +42860,7 @@
       </c>
       <c r="I472" s="30" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J472" s="30" t="inlineStr">
@@ -42478,21 +42874,21 @@
         <v>445</v>
       </c>
       <c r="C473" s="18" t="n">
-        <v>527</v>
+        <v>63</v>
       </c>
       <c r="D473" s="19" t="inlineStr">
         <is>
-          <t>34239</t>
+          <t>30329</t>
         </is>
       </c>
       <c r="E473" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F473" s="29" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G473" s="28" t="inlineStr">
@@ -42502,12 +42898,12 @@
       </c>
       <c r="H473" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I473" s="28" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J473" s="28" t="inlineStr">
@@ -42521,21 +42917,21 @@
         <v>446</v>
       </c>
       <c r="C474" s="31" t="n">
-        <v>533</v>
+        <v>168</v>
       </c>
       <c r="D474" s="32" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>31738</t>
         </is>
       </c>
       <c r="E474" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F474" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G474" s="30" t="inlineStr">
@@ -42545,12 +42941,12 @@
       </c>
       <c r="H474" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I474" s="30" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J474" s="30" t="inlineStr">
@@ -42564,21 +42960,21 @@
         <v>447</v>
       </c>
       <c r="C475" s="18" t="n">
-        <v>233</v>
+        <v>372</v>
       </c>
       <c r="D475" s="19" t="inlineStr">
         <is>
-          <t>31735</t>
+          <t>30629</t>
         </is>
       </c>
       <c r="E475" s="28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F475" s="29" t="inlineStr">
         <is>
-          <t>46.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G475" s="28" t="inlineStr">
@@ -42588,12 +42984,12 @@
       </c>
       <c r="H475" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I475" s="28" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J475" s="28" t="inlineStr">
@@ -42607,21 +43003,21 @@
         <v>448</v>
       </c>
       <c r="C476" s="31" t="n">
-        <v>461</v>
+        <v>402</v>
       </c>
       <c r="D476" s="32" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>31628</t>
         </is>
       </c>
       <c r="E476" s="30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F476" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>35.0 kg</t>
         </is>
       </c>
       <c r="G476" s="30" t="inlineStr">
@@ -42631,12 +43027,12 @@
       </c>
       <c r="H476" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I476" s="30" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J476" s="30" t="inlineStr">
@@ -42650,21 +43046,21 @@
         <v>449</v>
       </c>
       <c r="C477" s="18" t="n">
-        <v>446</v>
+        <v>527</v>
       </c>
       <c r="D477" s="19" t="inlineStr">
         <is>
-          <t>30754</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="E477" s="28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F477" s="29" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G477" s="28" t="inlineStr">
@@ -42679,7 +43075,7 @@
       </c>
       <c r="I477" s="28" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J477" s="28" t="inlineStr">
@@ -42693,21 +43089,21 @@
         <v>450</v>
       </c>
       <c r="C478" s="31" t="n">
-        <v>132</v>
+        <v>533</v>
       </c>
       <c r="D478" s="32" t="inlineStr">
         <is>
-          <t>30328</t>
+          <t>34234</t>
         </is>
       </c>
       <c r="E478" s="30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F478" s="33" t="inlineStr">
         <is>
-          <t>39 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G478" s="30" t="inlineStr">
@@ -42722,7 +43118,7 @@
       </c>
       <c r="I478" s="30" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J478" s="30" t="inlineStr">
@@ -42736,21 +43132,21 @@
         <v>451</v>
       </c>
       <c r="C479" s="18" t="n">
-        <v>126</v>
+        <v>233</v>
       </c>
       <c r="D479" s="19" t="inlineStr">
         <is>
-          <t>943641</t>
+          <t>31735</t>
         </is>
       </c>
       <c r="E479" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F479" s="29" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="G479" s="28" t="inlineStr">
@@ -42760,12 +43156,12 @@
       </c>
       <c r="H479" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I479" s="28" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J479" s="28" t="inlineStr">
@@ -42779,16 +43175,16 @@
         <v>452</v>
       </c>
       <c r="C480" s="31" t="n">
-        <v>16</v>
+        <v>461</v>
       </c>
       <c r="D480" s="32" t="inlineStr">
         <is>
-          <t>943642</t>
+          <t>34129</t>
         </is>
       </c>
       <c r="E480" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F480" s="33" t="inlineStr">
@@ -42803,12 +43199,12 @@
       </c>
       <c r="H480" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I480" s="30" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J480" s="30" t="inlineStr">
@@ -42822,21 +43218,21 @@
         <v>453</v>
       </c>
       <c r="C481" s="18" t="n">
-        <v>140</v>
+        <v>446</v>
       </c>
       <c r="D481" s="19" t="inlineStr">
         <is>
-          <t>31737</t>
+          <t>30754</t>
         </is>
       </c>
       <c r="E481" s="28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F481" s="29" t="inlineStr">
         <is>
-          <t>49.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G481" s="28" t="inlineStr">
@@ -42846,12 +43242,12 @@
       </c>
       <c r="H481" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I481" s="28" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J481" s="28" t="inlineStr">
@@ -42865,21 +43261,21 @@
         <v>454</v>
       </c>
       <c r="C482" s="31" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D482" s="32" t="inlineStr">
         <is>
-          <t>31739</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="E482" s="30" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F482" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>39 kg</t>
         </is>
       </c>
       <c r="G482" s="30" t="inlineStr">
@@ -42889,12 +43285,12 @@
       </c>
       <c r="H482" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I482" s="30" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J482" s="30" t="inlineStr">
@@ -42908,21 +43304,21 @@
         <v>455</v>
       </c>
       <c r="C483" s="18" t="n">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="D483" s="19" t="inlineStr">
         <is>
-          <t>30359</t>
+          <t>943641</t>
         </is>
       </c>
       <c r="E483" s="28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F483" s="29" t="inlineStr">
         <is>
-          <t>44.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G483" s="28" t="inlineStr">
@@ -42937,7 +43333,7 @@
       </c>
       <c r="I483" s="28" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J483" s="28" t="inlineStr">
@@ -42951,21 +43347,21 @@
         <v>456</v>
       </c>
       <c r="C484" s="31" t="n">
-        <v>401</v>
+        <v>16</v>
       </c>
       <c r="D484" s="32" t="inlineStr">
         <is>
-          <t>31633</t>
+          <t>943642</t>
         </is>
       </c>
       <c r="E484" s="30" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F484" s="33" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G484" s="30" t="inlineStr">
@@ -42980,7 +43376,7 @@
       </c>
       <c r="I484" s="30" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J484" s="30" t="inlineStr">
@@ -42993,24 +43389,22 @@
       <c r="B485" s="28" t="n">
         <v>457</v>
       </c>
-      <c r="C485" s="18" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="C485" s="18" t="n">
+        <v>140</v>
       </c>
       <c r="D485" s="19" t="inlineStr">
         <is>
-          <t>34233</t>
+          <t>31737</t>
         </is>
       </c>
       <c r="E485" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F485" s="29" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>49.0 kg</t>
         </is>
       </c>
       <c r="G485" s="28" t="inlineStr">
@@ -43020,12 +43414,12 @@
       </c>
       <c r="H485" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I485" s="28" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J485" s="28" t="inlineStr">
@@ -43039,21 +43433,21 @@
         <v>458</v>
       </c>
       <c r="C486" s="31" t="n">
-        <v>541</v>
+        <v>141</v>
       </c>
       <c r="D486" s="32" t="inlineStr">
         <is>
-          <t>34461</t>
+          <t>31739</t>
         </is>
       </c>
       <c r="E486" s="30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F486" s="33" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G486" s="30" t="inlineStr">
@@ -43063,12 +43457,12 @@
       </c>
       <c r="H486" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I486" s="30" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J486" s="30" t="inlineStr">
@@ -43082,21 +43476,21 @@
         <v>459</v>
       </c>
       <c r="C487" s="18" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D487" s="19" t="inlineStr">
         <is>
-          <t>31734</t>
+          <t>30359</t>
         </is>
       </c>
       <c r="E487" s="28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F487" s="29" t="inlineStr">
         <is>
-          <t>43.0 kg</t>
+          <t>44.0 kg</t>
         </is>
       </c>
       <c r="G487" s="28" t="inlineStr">
@@ -43106,12 +43500,12 @@
       </c>
       <c r="H487" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I487" s="28" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J487" s="28" t="inlineStr">
@@ -43125,21 +43519,21 @@
         <v>460</v>
       </c>
       <c r="C488" s="31" t="n">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="D488" s="32" t="inlineStr">
         <is>
-          <t>30445</t>
+          <t>31633</t>
         </is>
       </c>
       <c r="E488" s="30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F488" s="33" t="inlineStr">
         <is>
-          <t>42.0 kg</t>
+          <t>33.0 kg</t>
         </is>
       </c>
       <c r="G488" s="30" t="inlineStr">
@@ -43149,12 +43543,12 @@
       </c>
       <c r="H488" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I488" s="30" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J488" s="30" t="inlineStr">
@@ -43167,22 +43561,24 @@
       <c r="B489" s="28" t="n">
         <v>461</v>
       </c>
-      <c r="C489" s="18" t="n">
-        <v>442</v>
+      <c r="C489" s="18" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
       </c>
       <c r="D489" s="19" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>34233</t>
         </is>
       </c>
       <c r="E489" s="28" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F489" s="29" t="inlineStr">
         <is>
-          <t>42.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G489" s="28" t="inlineStr">
@@ -43197,7 +43593,7 @@
       </c>
       <c r="I489" s="28" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J489" s="28" t="inlineStr">
@@ -43211,21 +43607,21 @@
         <v>462</v>
       </c>
       <c r="C490" s="31" t="n">
-        <v>429</v>
+        <v>541</v>
       </c>
       <c r="D490" s="32" t="inlineStr">
         <is>
-          <t>30317</t>
+          <t>34461</t>
         </is>
       </c>
       <c r="E490" s="30" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F490" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>33.0 kg</t>
         </is>
       </c>
       <c r="G490" s="30" t="inlineStr">
@@ -43240,7 +43636,7 @@
       </c>
       <c r="I490" s="30" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J490" s="30" t="inlineStr">
@@ -43254,16 +43650,16 @@
         <v>463</v>
       </c>
       <c r="C491" s="18" t="n">
-        <v>532</v>
+        <v>173</v>
       </c>
       <c r="D491" s="19" t="inlineStr">
         <is>
-          <t>34232</t>
+          <t>31734</t>
         </is>
       </c>
       <c r="E491" s="28" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F491" s="29" t="inlineStr">
@@ -43273,17 +43669,17 @@
       </c>
       <c r="G491" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H491" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I491" s="28" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J491" s="28" t="inlineStr">
@@ -43297,36 +43693,36 @@
         <v>464</v>
       </c>
       <c r="C492" s="31" t="n">
-        <v>571</v>
+        <v>409</v>
       </c>
       <c r="D492" s="32" t="inlineStr">
         <is>
-          <t>34462</t>
+          <t>30445</t>
         </is>
       </c>
       <c r="E492" s="30" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F492" s="33" t="inlineStr">
         <is>
-          <t>47.0 kg</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G492" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H492" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I492" s="30" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J492" s="30" t="inlineStr">
@@ -43340,36 +43736,36 @@
         <v>465</v>
       </c>
       <c r="C493" s="18" t="n">
-        <v>273</v>
+        <v>442</v>
       </c>
       <c r="D493" s="19" t="inlineStr">
         <is>
-          <t>30141</t>
+          <t>30748</t>
         </is>
       </c>
       <c r="E493" s="28" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F493" s="29" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G493" s="28" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H493" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I493" s="28" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J493" s="28" t="inlineStr">
@@ -43383,36 +43779,36 @@
         <v>466</v>
       </c>
       <c r="C494" s="31" t="n">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="D494" s="32" t="inlineStr">
         <is>
-          <t>30660</t>
+          <t>30317</t>
         </is>
       </c>
       <c r="E494" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F494" s="33" t="inlineStr">
         <is>
-          <t>44.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G494" s="30" t="inlineStr">
         <is>
-          <t>BLOK 14</t>
+          <t>BLOK 13</t>
         </is>
       </c>
       <c r="H494" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I494" s="30" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J494" s="30" t="inlineStr">
@@ -43426,21 +43822,21 @@
         <v>467</v>
       </c>
       <c r="C495" s="18" t="n">
-        <v>441</v>
+        <v>796</v>
       </c>
       <c r="D495" s="19" t="inlineStr">
         <is>
-          <t>30752</t>
+          <t>123367</t>
         </is>
       </c>
       <c r="E495" s="28" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F495" s="29" t="inlineStr">
         <is>
-          <t>40.0 kg</t>
+          <t>40 kg</t>
         </is>
       </c>
       <c r="G495" s="28" t="inlineStr">
@@ -43450,12 +43846,12 @@
       </c>
       <c r="H495" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I495" s="28" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J495" s="28" t="inlineStr">
@@ -43469,21 +43865,21 @@
         <v>468</v>
       </c>
       <c r="C496" s="31" t="n">
-        <v>181</v>
+        <v>792</v>
       </c>
       <c r="D496" s="32" t="inlineStr">
         <is>
-          <t>32278</t>
+          <t>123422</t>
         </is>
       </c>
       <c r="E496" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F496" s="33" t="inlineStr">
         <is>
-          <t>33 kg</t>
+          <t>46 kg</t>
         </is>
       </c>
       <c r="G496" s="30" t="inlineStr">
@@ -43493,12 +43889,12 @@
       </c>
       <c r="H496" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I496" s="30" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J496" s="30" t="inlineStr">
@@ -43512,21 +43908,21 @@
         <v>469</v>
       </c>
       <c r="C497" s="18" t="n">
-        <v>482</v>
+        <v>797</v>
       </c>
       <c r="D497" s="19" t="inlineStr">
         <is>
-          <t>33815</t>
+          <t>123368</t>
         </is>
       </c>
       <c r="E497" s="28" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F497" s="29" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>50 kg</t>
         </is>
       </c>
       <c r="G497" s="28" t="inlineStr">
@@ -43536,12 +43932,12 @@
       </c>
       <c r="H497" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I497" s="28" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J497" s="28" t="inlineStr">
@@ -43555,21 +43951,21 @@
         <v>470</v>
       </c>
       <c r="C498" s="31" t="n">
-        <v>13</v>
+        <v>807</v>
       </c>
       <c r="D498" s="32" t="inlineStr">
         <is>
-          <t>943644</t>
+          <t>123364</t>
         </is>
       </c>
       <c r="E498" s="30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F498" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>49 kg</t>
         </is>
       </c>
       <c r="G498" s="30" t="inlineStr">
@@ -43579,12 +43975,12 @@
       </c>
       <c r="H498" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I498" s="30" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J498" s="30" t="inlineStr">
@@ -43598,21 +43994,21 @@
         <v>471</v>
       </c>
       <c r="C499" s="18" t="n">
-        <v>219</v>
+        <v>798</v>
       </c>
       <c r="D499" s="19" t="inlineStr">
         <is>
-          <t>33419</t>
+          <t>123591</t>
         </is>
       </c>
       <c r="E499" s="28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F499" s="29" t="inlineStr">
         <is>
-          <t>46.0 kg</t>
+          <t>32 kg</t>
         </is>
       </c>
       <c r="G499" s="28" t="inlineStr">
@@ -43622,12 +44018,12 @@
       </c>
       <c r="H499" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I499" s="28" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J499" s="28" t="inlineStr">
@@ -43641,11 +44037,11 @@
         <v>472</v>
       </c>
       <c r="C500" s="31" t="n">
-        <v>232</v>
+        <v>801</v>
       </c>
       <c r="D500" s="32" t="inlineStr">
         <is>
-          <t>31730</t>
+          <t>123366</t>
         </is>
       </c>
       <c r="E500" s="30" t="inlineStr">
@@ -43655,7 +44051,7 @@
       </c>
       <c r="F500" s="33" t="inlineStr">
         <is>
-          <t>42.0 kg</t>
+          <t>32 kg</t>
         </is>
       </c>
       <c r="G500" s="30" t="inlineStr">
@@ -43665,12 +44061,12 @@
       </c>
       <c r="H500" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I500" s="30" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J500" s="30" t="inlineStr">
@@ -43684,21 +44080,21 @@
         <v>473</v>
       </c>
       <c r="C501" s="18" t="n">
-        <v>454</v>
+        <v>791</v>
       </c>
       <c r="D501" s="19" t="inlineStr">
         <is>
-          <t>30755</t>
+          <t>123423</t>
         </is>
       </c>
       <c r="E501" s="28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F501" s="29" t="inlineStr">
         <is>
-          <t>38.0 kg</t>
+          <t>44 kg</t>
         </is>
       </c>
       <c r="G501" s="28" t="inlineStr">
@@ -43708,12 +44104,12 @@
       </c>
       <c r="H501" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I501" s="28" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J501" s="28" t="inlineStr">
@@ -43727,21 +44123,21 @@
         <v>474</v>
       </c>
       <c r="C502" s="31" t="n">
-        <v>457</v>
+        <v>795</v>
       </c>
       <c r="D502" s="32" t="inlineStr">
         <is>
-          <t>30757</t>
+          <t>39351</t>
         </is>
       </c>
       <c r="E502" s="30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F502" s="33" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>30 kg</t>
         </is>
       </c>
       <c r="G502" s="30" t="inlineStr">
@@ -43751,12 +44147,12 @@
       </c>
       <c r="H502" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I502" s="30" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J502" s="30" t="inlineStr">
@@ -43770,21 +44166,21 @@
         <v>475</v>
       </c>
       <c r="C503" s="18" t="n">
-        <v>526</v>
+        <v>790</v>
       </c>
       <c r="D503" s="19" t="inlineStr">
         <is>
-          <t>34238</t>
+          <t>123420</t>
         </is>
       </c>
       <c r="E503" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F503" s="29" t="inlineStr">
         <is>
-          <t>42.0 kg</t>
+          <t>37 kg</t>
         </is>
       </c>
       <c r="G503" s="28" t="inlineStr">
@@ -43794,12 +44190,12 @@
       </c>
       <c r="H503" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I503" s="28" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J503" s="28" t="inlineStr">
@@ -43813,21 +44209,21 @@
         <v>476</v>
       </c>
       <c r="C504" s="31" t="n">
-        <v>308</v>
+        <v>802</v>
       </c>
       <c r="D504" s="32" t="inlineStr">
         <is>
-          <t>942822</t>
+          <t>123365</t>
         </is>
       </c>
       <c r="E504" s="30" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F504" s="33" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
+          <t>36 kg</t>
         </is>
       </c>
       <c r="G504" s="30" t="inlineStr">
@@ -43837,12 +44233,12 @@
       </c>
       <c r="H504" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I504" s="30" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J504" s="30" t="inlineStr">
@@ -43856,21 +44252,21 @@
         <v>477</v>
       </c>
       <c r="C505" s="18" t="n">
-        <v>49</v>
+        <v>800</v>
       </c>
       <c r="D505" s="19" t="inlineStr">
         <is>
-          <t>30758</t>
+          <t>39350</t>
         </is>
       </c>
       <c r="E505" s="28" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F505" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>33 kg</t>
         </is>
       </c>
       <c r="G505" s="28" t="inlineStr">
@@ -43880,12 +44276,12 @@
       </c>
       <c r="H505" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I505" s="28" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J505" s="28" t="inlineStr">
@@ -43899,21 +44295,21 @@
         <v>478</v>
       </c>
       <c r="C506" s="31" t="n">
-        <v>411</v>
+        <v>760</v>
       </c>
       <c r="D506" s="32" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>123594</t>
         </is>
       </c>
       <c r="E506" s="30" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F506" s="33" t="inlineStr">
         <is>
-          <t>29.0 kg</t>
+          <t>41 kg</t>
         </is>
       </c>
       <c r="G506" s="30" t="inlineStr">
@@ -43923,12 +44319,12 @@
       </c>
       <c r="H506" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I506" s="30" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J506" s="30" t="inlineStr">
@@ -43942,21 +44338,21 @@
         <v>479</v>
       </c>
       <c r="C507" s="18" t="n">
-        <v>319</v>
+        <v>532</v>
       </c>
       <c r="D507" s="19" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>34232</t>
         </is>
       </c>
       <c r="E507" s="28" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F507" s="29" t="inlineStr">
         <is>
-          <t>28.0 kg</t>
+          <t>43.0 kg</t>
         </is>
       </c>
       <c r="G507" s="28" t="inlineStr">
@@ -43966,12 +44362,12 @@
       </c>
       <c r="H507" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I507" s="28" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J507" s="28" t="inlineStr">
@@ -43985,21 +44381,21 @@
         <v>480</v>
       </c>
       <c r="C508" s="31" t="n">
-        <v>452</v>
+        <v>571</v>
       </c>
       <c r="D508" s="32" t="inlineStr">
         <is>
-          <t>30756</t>
+          <t>34462</t>
         </is>
       </c>
       <c r="E508" s="30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F508" s="33" t="inlineStr">
         <is>
-          <t>38.0 kg</t>
+          <t>47.0 kg</t>
         </is>
       </c>
       <c r="G508" s="30" t="inlineStr">
@@ -44009,12 +44405,12 @@
       </c>
       <c r="H508" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I508" s="30" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J508" s="30" t="inlineStr">
@@ -44028,21 +44424,21 @@
         <v>481</v>
       </c>
       <c r="C509" s="18" t="n">
-        <v>522</v>
+        <v>273</v>
       </c>
       <c r="D509" s="19" t="inlineStr">
         <is>
-          <t>33813</t>
+          <t>30141</t>
         </is>
       </c>
       <c r="E509" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F509" s="29" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>34.0 kg</t>
         </is>
       </c>
       <c r="G509" s="28" t="inlineStr">
@@ -44052,12 +44448,12 @@
       </c>
       <c r="H509" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I509" s="28" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J509" s="28" t="inlineStr">
@@ -44071,21 +44467,21 @@
         <v>482</v>
       </c>
       <c r="C510" s="31" t="n">
-        <v>543</v>
+        <v>449</v>
       </c>
       <c r="D510" s="32" t="inlineStr">
         <is>
-          <t>34249</t>
+          <t>30660</t>
         </is>
       </c>
       <c r="E510" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F510" s="33" t="inlineStr">
         <is>
-          <t>32.0 kg</t>
+          <t>44.0 kg</t>
         </is>
       </c>
       <c r="G510" s="30" t="inlineStr">
@@ -44095,12 +44491,12 @@
       </c>
       <c r="H510" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I510" s="30" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J510" s="30" t="inlineStr">
@@ -44114,21 +44510,21 @@
         <v>483</v>
       </c>
       <c r="C511" s="18" t="n">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D511" s="19" t="inlineStr">
         <is>
-          <t>30662</t>
+          <t>30752</t>
         </is>
       </c>
       <c r="E511" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F511" s="29" t="inlineStr">
         <is>
-          <t>46.0 kg</t>
+          <t>40.0 kg</t>
         </is>
       </c>
       <c r="G511" s="28" t="inlineStr">
@@ -44138,12 +44534,12 @@
       </c>
       <c r="H511" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I511" s="28" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J511" s="28" t="inlineStr">
@@ -44157,21 +44553,21 @@
         <v>484</v>
       </c>
       <c r="C512" s="31" t="n">
-        <v>256</v>
+        <v>181</v>
       </c>
       <c r="D512" s="32" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="E512" s="30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F512" s="33" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>33 kg</t>
         </is>
       </c>
       <c r="G512" s="30" t="inlineStr">
@@ -44181,12 +44577,12 @@
       </c>
       <c r="H512" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I512" s="30" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J512" s="30" t="inlineStr">
@@ -44200,21 +44596,21 @@
         <v>485</v>
       </c>
       <c r="C513" s="18" t="n">
-        <v>376</v>
+        <v>482</v>
       </c>
       <c r="D513" s="19" t="inlineStr">
         <is>
-          <t>31156</t>
+          <t>33815</t>
         </is>
       </c>
       <c r="E513" s="28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F513" s="29" t="inlineStr">
         <is>
-          <t>47.0 kg</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G513" s="28" t="inlineStr">
@@ -44224,12 +44620,12 @@
       </c>
       <c r="H513" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I513" s="28" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J513" s="28" t="inlineStr">
@@ -44243,21 +44639,21 @@
         <v>486</v>
       </c>
       <c r="C514" s="31" t="n">
-        <v>175</v>
+        <v>13</v>
       </c>
       <c r="D514" s="32" t="inlineStr">
         <is>
-          <t>32202</t>
+          <t>943644</t>
         </is>
       </c>
       <c r="E514" s="30" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F514" s="33" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G514" s="30" t="inlineStr">
@@ -44267,12 +44663,12 @@
       </c>
       <c r="H514" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I514" s="30" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J514" s="30" t="inlineStr">
@@ -44286,36 +44682,36 @@
         <v>487</v>
       </c>
       <c r="C515" s="18" t="n">
-        <v>525</v>
+        <v>219</v>
       </c>
       <c r="D515" s="19" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>33419</t>
         </is>
       </c>
       <c r="E515" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F515" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="G515" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H515" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I515" s="28" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J515" s="28" t="inlineStr">
@@ -44329,36 +44725,36 @@
         <v>488</v>
       </c>
       <c r="C516" s="31" t="n">
-        <v>537</v>
+        <v>232</v>
       </c>
       <c r="D516" s="32" t="inlineStr">
         <is>
-          <t>34702</t>
+          <t>31730</t>
         </is>
       </c>
       <c r="E516" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F516" s="33" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G516" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H516" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I516" s="30" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J516" s="30" t="inlineStr">
@@ -44372,36 +44768,36 @@
         <v>489</v>
       </c>
       <c r="C517" s="18" t="n">
-        <v>276</v>
+        <v>454</v>
       </c>
       <c r="D517" s="19" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>30755</t>
         </is>
       </c>
       <c r="E517" s="28" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F517" s="29" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>38.0 kg</t>
         </is>
       </c>
       <c r="G517" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H517" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I517" s="28" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J517" s="28" t="inlineStr">
@@ -44415,36 +44811,36 @@
         <v>490</v>
       </c>
       <c r="C518" s="31" t="n">
-        <v>564</v>
+        <v>457</v>
       </c>
       <c r="D518" s="32" t="inlineStr">
         <is>
-          <t>34532</t>
+          <t>30757</t>
         </is>
       </c>
       <c r="E518" s="30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F518" s="33" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>34.0 kg</t>
         </is>
       </c>
       <c r="G518" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H518" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I518" s="30" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J518" s="30" t="inlineStr">
@@ -44458,36 +44854,36 @@
         <v>491</v>
       </c>
       <c r="C519" s="18" t="n">
-        <v>149</v>
+        <v>526</v>
       </c>
       <c r="D519" s="19" t="inlineStr">
         <is>
-          <t>31729</t>
+          <t>34238</t>
         </is>
       </c>
       <c r="E519" s="28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F519" s="29" t="inlineStr">
         <is>
-          <t>45.0 kg</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G519" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H519" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I519" s="28" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J519" s="28" t="inlineStr">
@@ -44501,36 +44897,36 @@
         <v>492</v>
       </c>
       <c r="C520" s="31" t="n">
-        <v>443</v>
+        <v>308</v>
       </c>
       <c r="D520" s="32" t="inlineStr">
         <is>
-          <t>30750</t>
+          <t>942822</t>
         </is>
       </c>
       <c r="E520" s="30" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F520" s="33" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>39.0 kg</t>
         </is>
       </c>
       <c r="G520" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H520" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I520" s="30" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J520" s="30" t="inlineStr">
@@ -44544,36 +44940,36 @@
         <v>493</v>
       </c>
       <c r="C521" s="18" t="n">
-        <v>521</v>
+        <v>49</v>
       </c>
       <c r="D521" s="19" t="inlineStr">
         <is>
-          <t>33812</t>
+          <t>30758</t>
         </is>
       </c>
       <c r="E521" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F521" s="29" t="inlineStr">
         <is>
-          <t>47.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G521" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H521" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I521" s="28" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J521" s="28" t="inlineStr">
@@ -44587,36 +44983,36 @@
         <v>494</v>
       </c>
       <c r="C522" s="31" t="n">
-        <v>536</v>
+        <v>411</v>
       </c>
       <c r="D522" s="32" t="inlineStr">
         <is>
-          <t>34701</t>
+          <t>30451</t>
         </is>
       </c>
       <c r="E522" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F522" s="33" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>29.0 kg</t>
         </is>
       </c>
       <c r="G522" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H522" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I522" s="30" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J522" s="30" t="inlineStr">
@@ -44630,36 +45026,36 @@
         <v>495</v>
       </c>
       <c r="C523" s="18" t="n">
-        <v>575</v>
+        <v>319</v>
       </c>
       <c r="D523" s="19" t="inlineStr">
         <is>
-          <t>34463</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="E523" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F523" s="29" t="inlineStr">
         <is>
-          <t>38.0 kg</t>
+          <t>28.0 kg</t>
         </is>
       </c>
       <c r="G523" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H523" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I523" s="28" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J523" s="28" t="inlineStr">
@@ -44673,36 +45069,36 @@
         <v>496</v>
       </c>
       <c r="C524" s="31" t="n">
-        <v>223</v>
+        <v>452</v>
       </c>
       <c r="D524" s="32" t="inlineStr">
         <is>
-          <t>33837</t>
+          <t>30756</t>
         </is>
       </c>
       <c r="E524" s="30" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F524" s="33" t="inlineStr">
         <is>
-          <t>44.0 kg</t>
+          <t>38.0 kg</t>
         </is>
       </c>
       <c r="G524" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H524" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I524" s="30" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J524" s="30" t="inlineStr">
@@ -44716,36 +45112,36 @@
         <v>497</v>
       </c>
       <c r="C525" s="18" t="n">
-        <v>220</v>
+        <v>522</v>
       </c>
       <c r="D525" s="19" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="E525" s="28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F525" s="29" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G525" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H525" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I525" s="28" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 1</t>
         </is>
       </c>
       <c r="J525" s="28" t="inlineStr">
@@ -44759,36 +45155,36 @@
         <v>498</v>
       </c>
       <c r="C526" s="31" t="n">
-        <v>435</v>
+        <v>543</v>
       </c>
       <c r="D526" s="32" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>34249</t>
         </is>
       </c>
       <c r="E526" s="30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F526" s="33" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>32.0 kg</t>
         </is>
       </c>
       <c r="G526" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H526" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I526" s="30" t="inlineStr">
         <is>
-          <t>Saf 6</t>
+          <t>Saf 2</t>
         </is>
       </c>
       <c r="J526" s="30" t="inlineStr">
@@ -44802,36 +45198,36 @@
         <v>499</v>
       </c>
       <c r="C527" s="18" t="n">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="D527" s="19" t="inlineStr">
         <is>
-          <t>34329</t>
+          <t>30662</t>
         </is>
       </c>
       <c r="E527" s="28" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F527" s="29" t="inlineStr">
         <is>
-          <t>35.0 kg</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="G527" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H527" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I527" s="28" t="inlineStr">
         <is>
-          <t>Saf 1</t>
+          <t>Saf 3</t>
         </is>
       </c>
       <c r="J527" s="28" t="inlineStr">
@@ -44845,36 +45241,36 @@
         <v>500</v>
       </c>
       <c r="C528" s="31" t="n">
-        <v>566</v>
+        <v>256</v>
       </c>
       <c r="D528" s="32" t="inlineStr">
         <is>
-          <t>34341</t>
+          <t>31295</t>
         </is>
       </c>
       <c r="E528" s="30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F528" s="33" t="inlineStr">
         <is>
-          <t>41.0 kg</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G528" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H528" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I528" s="30" t="inlineStr">
         <is>
-          <t>Saf 2</t>
+          <t>Saf 4</t>
         </is>
       </c>
       <c r="J528" s="30" t="inlineStr">
@@ -44888,36 +45284,36 @@
         <v>501</v>
       </c>
       <c r="C529" s="18" t="n">
-        <v>559</v>
+        <v>376</v>
       </c>
       <c r="D529" s="19" t="inlineStr">
         <is>
-          <t>34344</t>
+          <t>31156</t>
         </is>
       </c>
       <c r="E529" s="28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F529" s="29" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>47.0 kg</t>
         </is>
       </c>
       <c r="G529" s="28" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H529" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I529" s="28" t="inlineStr">
         <is>
-          <t>Saf 3</t>
+          <t>Saf 5</t>
         </is>
       </c>
       <c r="J529" s="28" t="inlineStr">
@@ -44931,36 +45327,36 @@
         <v>502</v>
       </c>
       <c r="C530" s="31" t="n">
-        <v>572</v>
+        <v>175</v>
       </c>
       <c r="D530" s="32" t="inlineStr">
         <is>
-          <t>33462</t>
+          <t>32202</t>
         </is>
       </c>
       <c r="E530" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F530" s="33" t="inlineStr">
         <is>
-          <t>38.0 kg</t>
+          <t>34.0 kg</t>
         </is>
       </c>
       <c r="G530" s="30" t="inlineStr">
         <is>
-          <t>BLOK 15</t>
+          <t>BLOK 14</t>
         </is>
       </c>
       <c r="H530" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I530" s="30" t="inlineStr">
         <is>
-          <t>Saf 4</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J530" s="30" t="inlineStr">
@@ -44974,21 +45370,21 @@
         <v>503</v>
       </c>
       <c r="C531" s="18" t="n">
-        <v>356</v>
+        <v>793</v>
       </c>
       <c r="D531" s="19" t="inlineStr">
         <is>
-          <t>30330</t>
+          <t>123421</t>
         </is>
       </c>
       <c r="E531" s="28" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F531" s="29" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>35 kg</t>
         </is>
       </c>
       <c r="G531" s="28" t="inlineStr">
@@ -44998,12 +45394,12 @@
       </c>
       <c r="H531" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="I531" s="28" t="inlineStr">
         <is>
-          <t>Saf 5</t>
+          <t>Saf 6</t>
         </is>
       </c>
       <c r="J531" s="28" t="inlineStr">
@@ -45017,21 +45413,21 @@
         <v>504</v>
       </c>
       <c r="C532" s="31" t="n">
-        <v>285</v>
+        <v>794</v>
       </c>
       <c r="D532" s="32" t="inlineStr">
         <is>
-          <t>33421</t>
+          <t>39352</t>
         </is>
       </c>
       <c r="E532" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F532" s="33" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
+          <t>50 kg</t>
         </is>
       </c>
       <c r="G532" s="30" t="inlineStr">
@@ -45041,7 +45437,7 @@
       </c>
       <c r="H532" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="I532" s="30" t="inlineStr">
@@ -45059,14 +45455,12 @@
       <c r="B533" s="28" t="n">
         <v>505</v>
       </c>
-      <c r="C533" s="18" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+      <c r="C533" s="18" t="n">
+        <v>525</v>
       </c>
       <c r="D533" s="19" t="inlineStr">
         <is>
-          <t>943646</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="E533" s="28" t="inlineStr">
@@ -45076,7 +45470,7 @@
       </c>
       <c r="F533" s="29" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G533" s="28" t="inlineStr">
@@ -45086,7 +45480,7 @@
       </c>
       <c r="H533" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I533" s="28" t="inlineStr">
@@ -45105,21 +45499,21 @@
         <v>506</v>
       </c>
       <c r="C534" s="31" t="n">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="D534" s="32" t="inlineStr">
         <is>
-          <t>33834</t>
+          <t>34702</t>
         </is>
       </c>
       <c r="E534" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F534" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G534" s="30" t="inlineStr">
@@ -45129,7 +45523,7 @@
       </c>
       <c r="H534" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I534" s="30" t="inlineStr">
@@ -45148,21 +45542,21 @@
         <v>507</v>
       </c>
       <c r="C535" s="18" t="n">
-        <v>179</v>
+        <v>276</v>
       </c>
       <c r="D535" s="19" t="inlineStr">
         <is>
-          <t>942823</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="E535" s="28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F535" s="29" t="inlineStr">
         <is>
-          <t>43.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G535" s="28" t="inlineStr">
@@ -45172,7 +45566,7 @@
       </c>
       <c r="H535" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I535" s="28" t="inlineStr">
@@ -45191,21 +45585,21 @@
         <v>508</v>
       </c>
       <c r="C536" s="31" t="n">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="D536" s="32" t="inlineStr">
         <is>
-          <t>33836</t>
+          <t>34532</t>
         </is>
       </c>
       <c r="E536" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F536" s="33" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G536" s="30" t="inlineStr">
@@ -45215,7 +45609,7 @@
       </c>
       <c r="H536" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I536" s="30" t="inlineStr">
@@ -45234,11 +45628,11 @@
         <v>509</v>
       </c>
       <c r="C537" s="18" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D537" s="19" t="inlineStr">
         <is>
-          <t>31733</t>
+          <t>31729</t>
         </is>
       </c>
       <c r="E537" s="28" t="inlineStr">
@@ -45248,7 +45642,7 @@
       </c>
       <c r="F537" s="29" t="inlineStr">
         <is>
-          <t>41.0 kg</t>
+          <t>45.0 kg</t>
         </is>
       </c>
       <c r="G537" s="28" t="inlineStr">
@@ -45258,7 +45652,7 @@
       </c>
       <c r="H537" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I537" s="28" t="inlineStr">
@@ -45277,21 +45671,21 @@
         <v>510</v>
       </c>
       <c r="C538" s="31" t="n">
-        <v>343</v>
+        <v>443</v>
       </c>
       <c r="D538" s="32" t="inlineStr">
         <is>
-          <t>943613</t>
+          <t>30750</t>
         </is>
       </c>
       <c r="E538" s="30" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F538" s="33" t="inlineStr">
         <is>
-          <t>45.0 kg</t>
+          <t>34.0 kg</t>
         </is>
       </c>
       <c r="G538" s="30" t="inlineStr">
@@ -45301,7 +45695,7 @@
       </c>
       <c r="H538" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I538" s="30" t="inlineStr">
@@ -45320,31 +45714,31 @@
         <v>511</v>
       </c>
       <c r="C539" s="18" t="n">
-        <v>113</v>
+        <v>521</v>
       </c>
       <c r="D539" s="19" t="inlineStr">
         <is>
-          <t>943645</t>
+          <t>33812</t>
         </is>
       </c>
       <c r="E539" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F539" s="29" t="inlineStr">
         <is>
-          <t>46.0 kg</t>
+          <t>47.0 kg</t>
         </is>
       </c>
       <c r="G539" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H539" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I539" s="28" t="inlineStr">
@@ -45363,31 +45757,31 @@
         <v>512</v>
       </c>
       <c r="C540" s="31" t="n">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="D540" s="32" t="inlineStr">
         <is>
-          <t>33835</t>
+          <t>34701</t>
         </is>
       </c>
       <c r="E540" s="30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F540" s="33" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>33.0 kg</t>
         </is>
       </c>
       <c r="G540" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H540" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I540" s="30" t="inlineStr">
@@ -45406,11 +45800,11 @@
         <v>513</v>
       </c>
       <c r="C541" s="18" t="n">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="D541" s="19" t="inlineStr">
         <is>
-          <t>33461</t>
+          <t>34463</t>
         </is>
       </c>
       <c r="E541" s="28" t="inlineStr">
@@ -45420,17 +45814,17 @@
       </c>
       <c r="F541" s="29" t="inlineStr">
         <is>
-          <t>42.0 kg</t>
+          <t>38.0 kg</t>
         </is>
       </c>
       <c r="G541" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H541" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I541" s="28" t="inlineStr">
@@ -45449,31 +45843,31 @@
         <v>514</v>
       </c>
       <c r="C542" s="31" t="n">
-        <v>558</v>
+        <v>223</v>
       </c>
       <c r="D542" s="32" t="inlineStr">
         <is>
-          <t>34459</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="E542" s="30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F542" s="33" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>44.0 kg</t>
         </is>
       </c>
       <c r="G542" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H542" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I542" s="30" t="inlineStr">
@@ -45492,31 +45886,31 @@
         <v>515</v>
       </c>
       <c r="C543" s="18" t="n">
-        <v>549</v>
+        <v>220</v>
       </c>
       <c r="D543" s="19" t="inlineStr">
         <is>
-          <t>34340</t>
+          <t>31731</t>
         </is>
       </c>
       <c r="E543" s="28" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F543" s="29" t="inlineStr">
         <is>
-          <t>50.0 kg</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G543" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H543" s="28" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I543" s="28" t="inlineStr">
@@ -45535,31 +45929,31 @@
         <v>516</v>
       </c>
       <c r="C544" s="31" t="n">
-        <v>307</v>
+        <v>435</v>
       </c>
       <c r="D544" s="32" t="inlineStr">
         <is>
-          <t>942824</t>
+          <t>32120</t>
         </is>
       </c>
       <c r="E544" s="30" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F544" s="33" t="inlineStr">
         <is>
-          <t>47.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G544" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H544" s="30" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="I544" s="30" t="inlineStr">
@@ -45578,11 +45972,11 @@
         <v>517</v>
       </c>
       <c r="C545" s="18" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D545" s="19" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="E545" s="28" t="inlineStr">
@@ -45592,17 +45986,17 @@
       </c>
       <c r="F545" s="29" t="inlineStr">
         <is>
-          <t>32.0 kg</t>
+          <t>35.0 kg</t>
         </is>
       </c>
       <c r="G545" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H545" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I545" s="28" t="inlineStr">
@@ -45621,31 +46015,31 @@
         <v>518</v>
       </c>
       <c r="C546" s="31" t="n">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="D546" s="32" t="inlineStr">
         <is>
-          <t>33832</t>
+          <t>34341</t>
         </is>
       </c>
       <c r="E546" s="30" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F546" s="33" t="inlineStr">
         <is>
-          <t>49.0 kg</t>
+          <t>41.0 kg</t>
         </is>
       </c>
       <c r="G546" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H546" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I546" s="30" t="inlineStr">
@@ -45664,31 +46058,31 @@
         <v>519</v>
       </c>
       <c r="C547" s="18" t="n">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="D547" s="19" t="inlineStr">
         <is>
-          <t>34703</t>
+          <t>34344</t>
         </is>
       </c>
       <c r="E547" s="28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F547" s="29" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>36.0 kg</t>
         </is>
       </c>
       <c r="G547" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H547" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I547" s="28" t="inlineStr">
@@ -45707,31 +46101,31 @@
         <v>520</v>
       </c>
       <c r="C548" s="31" t="n">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="D548" s="32" t="inlineStr">
         <is>
-          <t>34246</t>
+          <t>33462</t>
         </is>
       </c>
       <c r="E548" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F548" s="33" t="inlineStr">
         <is>
-          <t>33.0 kg</t>
+          <t>38.0 kg</t>
         </is>
       </c>
       <c r="G548" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H548" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I548" s="30" t="inlineStr">
@@ -45750,31 +46144,31 @@
         <v>521</v>
       </c>
       <c r="C549" s="18" t="n">
-        <v>544</v>
+        <v>356</v>
       </c>
       <c r="D549" s="19" t="inlineStr">
         <is>
-          <t>34460</t>
+          <t>30330</t>
         </is>
       </c>
       <c r="E549" s="28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F549" s="29" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>33.0 kg</t>
         </is>
       </c>
       <c r="G549" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H549" s="28" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I549" s="28" t="inlineStr">
@@ -45793,31 +46187,31 @@
         <v>522</v>
       </c>
       <c r="C550" s="31" t="n">
-        <v>561</v>
+        <v>285</v>
       </c>
       <c r="D550" s="32" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="E550" s="30" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F550" s="33" t="inlineStr">
         <is>
-          <t>40.0 kg</t>
+          <t>39.0 kg</t>
         </is>
       </c>
       <c r="G550" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H550" s="30" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="I550" s="30" t="inlineStr">
@@ -45835,32 +46229,34 @@
       <c r="B551" s="28" t="n">
         <v>523</v>
       </c>
-      <c r="C551" s="18" t="n">
-        <v>523</v>
+      <c r="C551" s="18" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
       </c>
       <c r="D551" s="19" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>943646</t>
         </is>
       </c>
       <c r="E551" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F551" s="29" t="inlineStr">
         <is>
-          <t>45.0 kg</t>
+          <t>37.0 kg</t>
         </is>
       </c>
       <c r="G551" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H551" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I551" s="28" t="inlineStr">
@@ -45879,31 +46275,31 @@
         <v>524</v>
       </c>
       <c r="C552" s="31" t="n">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="D552" s="32" t="inlineStr">
         <is>
-          <t>34247</t>
+          <t>33834</t>
         </is>
       </c>
       <c r="E552" s="30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F552" s="33" t="inlineStr">
         <is>
-          <t>49.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G552" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H552" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I552" s="30" t="inlineStr">
@@ -45922,31 +46318,31 @@
         <v>525</v>
       </c>
       <c r="C553" s="18" t="n">
-        <v>547</v>
+        <v>179</v>
       </c>
       <c r="D553" s="19" t="inlineStr">
         <is>
-          <t>34531</t>
+          <t>942823</t>
         </is>
       </c>
       <c r="E553" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F553" s="29" t="inlineStr">
         <is>
-          <t>37.0 kg</t>
+          <t>43.0 kg</t>
         </is>
       </c>
       <c r="G553" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H553" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I553" s="28" t="inlineStr">
@@ -45965,31 +46361,31 @@
         <v>526</v>
       </c>
       <c r="C554" s="31" t="n">
-        <v>554</v>
+        <v>574</v>
       </c>
       <c r="D554" s="32" t="inlineStr">
         <is>
-          <t>33833</t>
+          <t>33836</t>
         </is>
       </c>
       <c r="E554" s="30" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F554" s="33" t="inlineStr">
         <is>
-          <t>36.0 kg</t>
+          <t>33.0 kg</t>
         </is>
       </c>
       <c r="G554" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H554" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I554" s="30" t="inlineStr">
@@ -46008,16 +46404,16 @@
         <v>527</v>
       </c>
       <c r="C555" s="18" t="n">
-        <v>540</v>
+        <v>150</v>
       </c>
       <c r="D555" s="19" t="inlineStr">
         <is>
-          <t>34248</t>
+          <t>31733</t>
         </is>
       </c>
       <c r="E555" s="28" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F555" s="29" t="inlineStr">
@@ -46027,12 +46423,12 @@
       </c>
       <c r="G555" s="28" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H555" s="28" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I555" s="28" t="inlineStr">
@@ -46051,31 +46447,31 @@
         <v>528</v>
       </c>
       <c r="C556" s="31" t="n">
-        <v>538</v>
+        <v>343</v>
       </c>
       <c r="D556" s="32" t="inlineStr">
         <is>
-          <t>34458</t>
+          <t>943613</t>
         </is>
       </c>
       <c r="E556" s="30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F556" s="33" t="inlineStr">
         <is>
-          <t>40.0 kg</t>
+          <t>45.0 kg</t>
         </is>
       </c>
       <c r="G556" s="30" t="inlineStr">
         <is>
-          <t>BLOK 16</t>
+          <t>BLOK 15</t>
         </is>
       </c>
       <c r="H556" s="30" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="I556" s="30" t="inlineStr">
@@ -46094,21 +46490,21 @@
         <v>529</v>
       </c>
       <c r="C557" s="18" t="n">
-        <v>524</v>
+        <v>113</v>
       </c>
       <c r="D557" s="19" t="inlineStr">
         <is>
-          <t>33445</t>
+          <t>943645</t>
         </is>
       </c>
       <c r="E557" s="28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F557" s="29" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>46.0 kg</t>
         </is>
       </c>
       <c r="G557" s="28" t="inlineStr">
@@ -46118,7 +46514,7 @@
       </c>
       <c r="H557" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I557" s="28" t="inlineStr">
@@ -46137,11 +46533,11 @@
         <v>530</v>
       </c>
       <c r="C558" s="31" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D558" s="32" t="inlineStr">
         <is>
-          <t>33838</t>
+          <t>33835</t>
         </is>
       </c>
       <c r="E558" s="30" t="inlineStr">
@@ -46151,7 +46547,7 @@
       </c>
       <c r="F558" s="33" t="inlineStr">
         <is>
-          <t>46.0 kg</t>
+          <t>50.0 kg</t>
         </is>
       </c>
       <c r="G558" s="30" t="inlineStr">
@@ -46161,7 +46557,7 @@
       </c>
       <c r="H558" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I558" s="30" t="inlineStr">
@@ -46180,11 +46576,11 @@
         <v>531</v>
       </c>
       <c r="C559" s="18" t="n">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="D559" s="19" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>33461</t>
         </is>
       </c>
       <c r="E559" s="28" t="inlineStr">
@@ -46194,7 +46590,7 @@
       </c>
       <c r="F559" s="29" t="inlineStr">
         <is>
-          <t>34.0 kg</t>
+          <t>42.0 kg</t>
         </is>
       </c>
       <c r="G559" s="28" t="inlineStr">
@@ -46204,7 +46600,7 @@
       </c>
       <c r="H559" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I559" s="28" t="inlineStr">
@@ -46223,21 +46619,21 @@
         <v>532</v>
       </c>
       <c r="C560" s="31" t="n">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="D560" s="32" t="inlineStr">
         <is>
-          <t>34704</t>
+          <t>34459</t>
         </is>
       </c>
       <c r="E560" s="30" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F560" s="33" t="inlineStr">
         <is>
-          <t>40.0 kg</t>
+          <t>33.0 kg</t>
         </is>
       </c>
       <c r="G560" s="30" t="inlineStr">
@@ -46247,7 +46643,7 @@
       </c>
       <c r="H560" s="30" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I560" s="30" t="inlineStr">
@@ -46266,16 +46662,16 @@
         <v>533</v>
       </c>
       <c r="C561" s="18" t="n">
-        <v>64</v>
+        <v>549</v>
       </c>
       <c r="D561" s="19" t="inlineStr">
         <is>
-          <t>942825</t>
+          <t>34340</t>
         </is>
       </c>
       <c r="E561" s="28" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F561" s="29" t="inlineStr">
@@ -46290,7 +46686,7 @@
       </c>
       <c r="H561" s="28" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="I561" s="28" t="inlineStr">
@@ -46309,46 +46705,820 @@
         <v>534</v>
       </c>
       <c r="C562" s="31" t="n">
+        <v>307</v>
+      </c>
+      <c r="D562" s="32" t="inlineStr">
+        <is>
+          <t>942824</t>
+        </is>
+      </c>
+      <c r="E562" s="30" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F562" s="33" t="inlineStr">
+        <is>
+          <t>47.0 kg</t>
+        </is>
+      </c>
+      <c r="G562" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H562" s="30" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="I562" s="30" t="inlineStr">
+        <is>
+          <t>Saf 6</t>
+        </is>
+      </c>
+      <c r="J562" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="563" ht="20" customHeight="1">
+      <c r="B563" s="28" t="n">
+        <v>535</v>
+      </c>
+      <c r="C563" s="18" t="n">
+        <v>480</v>
+      </c>
+      <c r="D563" s="19" t="inlineStr">
+        <is>
+          <t>34330</t>
+        </is>
+      </c>
+      <c r="E563" s="28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F563" s="29" t="inlineStr">
+        <is>
+          <t>32.0 kg</t>
+        </is>
+      </c>
+      <c r="G563" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H563" s="28" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="I563" s="28" t="inlineStr">
+        <is>
+          <t>Saf 1</t>
+        </is>
+      </c>
+      <c r="J563" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="564" ht="20" customHeight="1">
+      <c r="B564" s="30" t="n">
+        <v>536</v>
+      </c>
+      <c r="C564" s="31" t="n">
+        <v>548</v>
+      </c>
+      <c r="D564" s="32" t="inlineStr">
+        <is>
+          <t>33832</t>
+        </is>
+      </c>
+      <c r="E564" s="30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F564" s="33" t="inlineStr">
+        <is>
+          <t>49.0 kg</t>
+        </is>
+      </c>
+      <c r="G564" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H564" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="I564" s="30" t="inlineStr">
+        <is>
+          <t>Saf 2</t>
+        </is>
+      </c>
+      <c r="J564" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="565" ht="20" customHeight="1">
+      <c r="B565" s="28" t="n">
+        <v>537</v>
+      </c>
+      <c r="C565" s="18" t="n">
+        <v>542</v>
+      </c>
+      <c r="D565" s="19" t="inlineStr">
+        <is>
+          <t>34703</t>
+        </is>
+      </c>
+      <c r="E565" s="28" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F565" s="29" t="inlineStr">
+        <is>
+          <t>34.0 kg</t>
+        </is>
+      </c>
+      <c r="G565" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H565" s="28" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="I565" s="28" t="inlineStr">
+        <is>
+          <t>Saf 3</t>
+        </is>
+      </c>
+      <c r="J565" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="20" customHeight="1">
+      <c r="B566" s="30" t="n">
+        <v>538</v>
+      </c>
+      <c r="C566" s="31" t="n">
+        <v>557</v>
+      </c>
+      <c r="D566" s="32" t="inlineStr">
+        <is>
+          <t>34246</t>
+        </is>
+      </c>
+      <c r="E566" s="30" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F566" s="33" t="inlineStr">
+        <is>
+          <t>33.0 kg</t>
+        </is>
+      </c>
+      <c r="G566" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H566" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="I566" s="30" t="inlineStr">
+        <is>
+          <t>Saf 4</t>
+        </is>
+      </c>
+      <c r="J566" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="20" customHeight="1">
+      <c r="B567" s="28" t="n">
+        <v>539</v>
+      </c>
+      <c r="C567" s="18" t="n">
+        <v>544</v>
+      </c>
+      <c r="D567" s="19" t="inlineStr">
+        <is>
+          <t>34460</t>
+        </is>
+      </c>
+      <c r="E567" s="28" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F567" s="29" t="inlineStr">
+        <is>
+          <t>30.0 kg</t>
+        </is>
+      </c>
+      <c r="G567" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H567" s="28" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="I567" s="28" t="inlineStr">
+        <is>
+          <t>Saf 5</t>
+        </is>
+      </c>
+      <c r="J567" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="20" customHeight="1">
+      <c r="B568" s="30" t="n">
+        <v>540</v>
+      </c>
+      <c r="C568" s="31" t="n">
+        <v>561</v>
+      </c>
+      <c r="D568" s="32" t="inlineStr">
+        <is>
+          <t>34343</t>
+        </is>
+      </c>
+      <c r="E568" s="30" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F568" s="33" t="inlineStr">
+        <is>
+          <t>40.0 kg</t>
+        </is>
+      </c>
+      <c r="G568" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H568" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="I568" s="30" t="inlineStr">
+        <is>
+          <t>Saf 6</t>
+        </is>
+      </c>
+      <c r="J568" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="569" ht="20" customHeight="1">
+      <c r="B569" s="28" t="n">
+        <v>541</v>
+      </c>
+      <c r="C569" s="18" t="n">
+        <v>523</v>
+      </c>
+      <c r="D569" s="19" t="inlineStr">
+        <is>
+          <t>33814</t>
+        </is>
+      </c>
+      <c r="E569" s="28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F569" s="29" t="inlineStr">
+        <is>
+          <t>45.0 kg</t>
+        </is>
+      </c>
+      <c r="G569" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H569" s="28" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="I569" s="28" t="inlineStr">
+        <is>
+          <t>Saf 1</t>
+        </is>
+      </c>
+      <c r="J569" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="570" ht="20" customHeight="1">
+      <c r="B570" s="30" t="n">
+        <v>542</v>
+      </c>
+      <c r="C570" s="31" t="n">
+        <v>539</v>
+      </c>
+      <c r="D570" s="32" t="inlineStr">
+        <is>
+          <t>34247</t>
+        </is>
+      </c>
+      <c r="E570" s="30" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F570" s="33" t="inlineStr">
+        <is>
+          <t>49.0 kg</t>
+        </is>
+      </c>
+      <c r="G570" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H570" s="30" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="I570" s="30" t="inlineStr">
+        <is>
+          <t>Saf 2</t>
+        </is>
+      </c>
+      <c r="J570" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="571" ht="20" customHeight="1">
+      <c r="B571" s="28" t="n">
+        <v>543</v>
+      </c>
+      <c r="C571" s="18" t="n">
+        <v>547</v>
+      </c>
+      <c r="D571" s="19" t="inlineStr">
+        <is>
+          <t>34531</t>
+        </is>
+      </c>
+      <c r="E571" s="28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F571" s="29" t="inlineStr">
+        <is>
+          <t>37.0 kg</t>
+        </is>
+      </c>
+      <c r="G571" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H571" s="28" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="I571" s="28" t="inlineStr">
+        <is>
+          <t>Saf 3</t>
+        </is>
+      </c>
+      <c r="J571" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="572" ht="20" customHeight="1">
+      <c r="B572" s="30" t="n">
+        <v>544</v>
+      </c>
+      <c r="C572" s="31" t="n">
+        <v>554</v>
+      </c>
+      <c r="D572" s="32" t="inlineStr">
+        <is>
+          <t>33833</t>
+        </is>
+      </c>
+      <c r="E572" s="30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F572" s="33" t="inlineStr">
+        <is>
+          <t>36.0 kg</t>
+        </is>
+      </c>
+      <c r="G572" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H572" s="30" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="I572" s="30" t="inlineStr">
+        <is>
+          <t>Saf 4</t>
+        </is>
+      </c>
+      <c r="J572" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="573" ht="20" customHeight="1">
+      <c r="B573" s="28" t="n">
+        <v>545</v>
+      </c>
+      <c r="C573" s="18" t="n">
+        <v>540</v>
+      </c>
+      <c r="D573" s="19" t="inlineStr">
+        <is>
+          <t>34248</t>
+        </is>
+      </c>
+      <c r="E573" s="28" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F573" s="29" t="inlineStr">
+        <is>
+          <t>41.0 kg</t>
+        </is>
+      </c>
+      <c r="G573" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H573" s="28" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="I573" s="28" t="inlineStr">
+        <is>
+          <t>Saf 5</t>
+        </is>
+      </c>
+      <c r="J573" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="574" ht="20" customHeight="1">
+      <c r="B574" s="30" t="n">
+        <v>546</v>
+      </c>
+      <c r="C574" s="31" t="n">
+        <v>538</v>
+      </c>
+      <c r="D574" s="32" t="inlineStr">
+        <is>
+          <t>34458</t>
+        </is>
+      </c>
+      <c r="E574" s="30" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F574" s="33" t="inlineStr">
+        <is>
+          <t>40.0 kg</t>
+        </is>
+      </c>
+      <c r="G574" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H574" s="30" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="I574" s="30" t="inlineStr">
+        <is>
+          <t>Saf 6</t>
+        </is>
+      </c>
+      <c r="J574" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="575" ht="20" customHeight="1">
+      <c r="B575" s="28" t="n">
+        <v>547</v>
+      </c>
+      <c r="C575" s="18" t="n">
+        <v>524</v>
+      </c>
+      <c r="D575" s="19" t="inlineStr">
+        <is>
+          <t>33445</t>
+        </is>
+      </c>
+      <c r="E575" s="28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F575" s="29" t="inlineStr">
+        <is>
+          <t>30.0 kg</t>
+        </is>
+      </c>
+      <c r="G575" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H575" s="28" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="I575" s="28" t="inlineStr">
+        <is>
+          <t>Saf 1</t>
+        </is>
+      </c>
+      <c r="J575" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="576" ht="20" customHeight="1">
+      <c r="B576" s="30" t="n">
+        <v>548</v>
+      </c>
+      <c r="C576" s="31" t="n">
+        <v>551</v>
+      </c>
+      <c r="D576" s="32" t="inlineStr">
+        <is>
+          <t>33838</t>
+        </is>
+      </c>
+      <c r="E576" s="30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F576" s="33" t="inlineStr">
+        <is>
+          <t>46.0 kg</t>
+        </is>
+      </c>
+      <c r="G576" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H576" s="30" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="I576" s="30" t="inlineStr">
+        <is>
+          <t>Saf 2</t>
+        </is>
+      </c>
+      <c r="J576" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="577" ht="20" customHeight="1">
+      <c r="B577" s="28" t="n">
+        <v>549</v>
+      </c>
+      <c r="C577" s="18" t="n">
+        <v>546</v>
+      </c>
+      <c r="D577" s="19" t="inlineStr">
+        <is>
+          <t>33831</t>
+        </is>
+      </c>
+      <c r="E577" s="28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F577" s="29" t="inlineStr">
+        <is>
+          <t>34.0 kg</t>
+        </is>
+      </c>
+      <c r="G577" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H577" s="28" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="I577" s="28" t="inlineStr">
+        <is>
+          <t>Saf 3</t>
+        </is>
+      </c>
+      <c r="J577" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="578" ht="20" customHeight="1">
+      <c r="B578" s="30" t="n">
+        <v>550</v>
+      </c>
+      <c r="C578" s="31" t="n">
+        <v>573</v>
+      </c>
+      <c r="D578" s="32" t="inlineStr">
+        <is>
+          <t>34704</t>
+        </is>
+      </c>
+      <c r="E578" s="30" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F578" s="33" t="inlineStr">
+        <is>
+          <t>40.0 kg</t>
+        </is>
+      </c>
+      <c r="G578" s="30" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H578" s="30" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="I578" s="30" t="inlineStr">
+        <is>
+          <t>Saf 4</t>
+        </is>
+      </c>
+      <c r="J578" s="30" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="20" customHeight="1">
+      <c r="B579" s="28" t="n">
+        <v>551</v>
+      </c>
+      <c r="C579" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="D579" s="19" t="inlineStr">
+        <is>
+          <t>942825</t>
+        </is>
+      </c>
+      <c r="E579" s="28" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F579" s="29" t="inlineStr">
+        <is>
+          <t>50.0 kg</t>
+        </is>
+      </c>
+      <c r="G579" s="28" t="inlineStr">
+        <is>
+          <t>BLOK 16</t>
+        </is>
+      </c>
+      <c r="H579" s="28" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="I579" s="28" t="inlineStr">
+        <is>
+          <t>Saf 5</t>
+        </is>
+      </c>
+      <c r="J579" s="28" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="580" ht="20" customHeight="1">
+      <c r="B580" s="30" t="n">
+        <v>552</v>
+      </c>
+      <c r="C580" s="31" t="n">
         <v>560</v>
       </c>
-      <c r="D562" s="32" t="inlineStr">
+      <c r="D580" s="32" t="inlineStr">
         <is>
           <t>34464</t>
         </is>
       </c>
-      <c r="E562" s="30" t="inlineStr">
+      <c r="E580" s="30" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="F562" s="33" t="inlineStr">
+      <c r="F580" s="33" t="inlineStr">
         <is>
           <t>31.0 kg</t>
         </is>
       </c>
-      <c r="G562" s="30" t="inlineStr">
+      <c r="G580" s="30" t="inlineStr">
         <is>
           <t>BLOK 16</t>
         </is>
       </c>
-      <c r="H562" s="30" t="inlineStr">
+      <c r="H580" s="30" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="I562" s="30" t="inlineStr">
+      <c r="I580" s="30" t="inlineStr">
         <is>
           <t>Saf 6</t>
         </is>
       </c>
-      <c r="J562" s="30" t="inlineStr">
+      <c r="J580" s="30" t="inlineStr">
         <is>
           <t>SELESAI</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B28:J562"/>
+  <autoFilter ref="B28:J580"/>
   <mergeCells count="1">
     <mergeCell ref="B24:D24"/>
   </mergeCells>

--- a/c.xlsx
+++ b/c.xlsx
@@ -2110,8 +2110,10 @@
       <c r="I23" s="10" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="12" t="inlineStr"/>
-      <c r="L23" s="10" t="n">
-        <v>961</v>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>930/961</t>
+        </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
@@ -2120,11 +2122,13 @@
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
-        </is>
-      </c>
-      <c r="O23" s="10" t="n">
-        <v>962</v>
+          <t>39.0 kg/39.0 kg</t>
+        </is>
+      </c>
+      <c r="O23" s="10" t="inlineStr">
+        <is>
+          <t>931/962</t>
+        </is>
       </c>
       <c r="P23" s="11" t="inlineStr">
         <is>
@@ -2133,7 +2137,7 @@
       </c>
       <c r="Q23" s="12" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>30.0 kg/30.0 kg</t>
         </is>
       </c>
       <c r="R23" s="10" t="n">
@@ -3177,8 +3181,10 @@
       <c r="U36" s="10" t="inlineStr"/>
       <c r="V36" s="11" t="inlineStr"/>
       <c r="W36" s="12" t="inlineStr"/>
-      <c r="X36" s="10" t="n">
-        <v>964</v>
+      <c r="X36" s="10" t="inlineStr">
+        <is>
+          <t>964/287</t>
+        </is>
       </c>
       <c r="Y36" s="11" t="inlineStr">
         <is>
@@ -3190,8 +3196,10 @@
           <t>47.0 kg</t>
         </is>
       </c>
-      <c r="AA36" s="10" t="n">
-        <v>963</v>
+      <c r="AA36" s="10" t="inlineStr">
+        <is>
+          <t>963/242</t>
+        </is>
       </c>
       <c r="AB36" s="11" t="inlineStr">
         <is>
@@ -14236,11 +14244,15 @@
       <c r="C19" s="14" t="inlineStr"/>
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr"/>
-      <c r="F19" s="14" t="n">
-        <v>961</v>
-      </c>
-      <c r="G19" s="14" t="n">
-        <v>962</v>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>930/961</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>931/962</t>
+        </is>
       </c>
       <c r="H19" s="14" t="n">
         <v>960</v>
@@ -14545,11 +14557,15 @@
       <c r="G30" s="14" t="inlineStr"/>
       <c r="H30" s="14" t="inlineStr"/>
       <c r="I30" s="14" t="inlineStr"/>
-      <c r="J30" s="14" t="n">
-        <v>964</v>
-      </c>
-      <c r="K30" s="14" t="n">
-        <v>963</v>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>964/287</t>
+        </is>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>963/242</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -18735,8 +18751,10 @@
       <c r="G14" s="17" t="inlineStr"/>
       <c r="H14" s="18" t="inlineStr"/>
       <c r="I14" s="12" t="inlineStr"/>
-      <c r="J14" s="17" t="n">
-        <v>961</v>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>930/961</t>
+        </is>
       </c>
       <c r="K14" s="18" t="inlineStr">
         <is>
@@ -18745,11 +18763,13 @@
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="n">
-        <v>962</v>
+          <t>39.0 kg/39.0 kg</t>
+        </is>
+      </c>
+      <c r="M14" s="17" t="inlineStr">
+        <is>
+          <t>931/962</t>
+        </is>
       </c>
       <c r="N14" s="18" t="inlineStr">
         <is>
@@ -18758,7 +18778,7 @@
       </c>
       <c r="O14" s="12" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>30.0 kg/30.0 kg</t>
         </is>
       </c>
       <c r="P14" s="17" t="n">
@@ -19522,8 +19542,10 @@
       <c r="S22" s="17" t="inlineStr"/>
       <c r="T22" s="18" t="inlineStr"/>
       <c r="U22" s="12" t="inlineStr"/>
-      <c r="V22" s="17" t="n">
-        <v>964</v>
+      <c r="V22" s="17" t="inlineStr">
+        <is>
+          <t>964/287</t>
+        </is>
       </c>
       <c r="W22" s="18" t="inlineStr">
         <is>
@@ -19535,8 +19557,10 @@
           <t>47.0 kg</t>
         </is>
       </c>
-      <c r="Y22" s="17" t="n">
-        <v>963</v>
+      <c r="Y22" s="17" t="inlineStr">
+        <is>
+          <t>963/242</t>
+        </is>
       </c>
       <c r="Z22" s="18" t="inlineStr">
         <is>
@@ -27469,7 +27493,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>2298</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -27499,7 +27523,7 @@
         <v>21</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>2133</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -30774,8 +30798,10 @@
       <c r="B94" s="30" t="n">
         <v>66</v>
       </c>
-      <c r="C94" s="31" t="n">
-        <v>961</v>
+      <c r="C94" s="31" t="inlineStr">
+        <is>
+          <t>930/961</t>
+        </is>
       </c>
       <c r="D94" s="32" t="inlineStr">
         <is>
@@ -30784,12 +30810,12 @@
       </c>
       <c r="E94" s="30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70/68</t>
         </is>
       </c>
       <c r="F94" s="33" t="inlineStr">
         <is>
-          <t>39.0 kg</t>
+          <t>39.0 kg/39.0 kg</t>
         </is>
       </c>
       <c r="G94" s="30" t="inlineStr">
@@ -30817,8 +30843,10 @@
       <c r="B95" s="28" t="n">
         <v>67</v>
       </c>
-      <c r="C95" s="17" t="n">
-        <v>962</v>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>931/962</t>
+        </is>
       </c>
       <c r="D95" s="18" t="inlineStr">
         <is>
@@ -30827,12 +30855,12 @@
       </c>
       <c r="E95" s="28" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70/68</t>
         </is>
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>30.0 kg</t>
+          <t>30.0 kg/30.0 kg</t>
         </is>
       </c>
       <c r="G95" s="28" t="inlineStr">
@@ -33096,8 +33124,10 @@
       <c r="B148" s="30" t="n">
         <v>120</v>
       </c>
-      <c r="C148" s="31" t="n">
-        <v>964</v>
+      <c r="C148" s="31" t="inlineStr">
+        <is>
+          <t>964/287</t>
+        </is>
       </c>
       <c r="D148" s="32" t="inlineStr">
         <is>
@@ -33139,8 +33169,10 @@
       <c r="B149" s="28" t="n">
         <v>121</v>
       </c>
-      <c r="C149" s="17" t="n">
-        <v>963</v>
+      <c r="C149" s="17" t="inlineStr">
+        <is>
+          <t>963/242</t>
+        </is>
       </c>
       <c r="D149" s="18" t="inlineStr">
         <is>

--- a/c.xlsx
+++ b/c.xlsx
@@ -2110,10 +2110,8 @@
       <c r="I23" s="10" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr"/>
       <c r="K23" s="12" t="inlineStr"/>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>930/961</t>
-        </is>
+      <c r="L23" s="10" t="n">
+        <v>961</v>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
@@ -2122,13 +2120,11 @@
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>39.0 kg/39.0 kg</t>
-        </is>
-      </c>
-      <c r="O23" s="10" t="inlineStr">
-        <is>
-          <t>931/962</t>
-        </is>
+          <t>39.0 kg</t>
+        </is>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>962</v>
       </c>
       <c r="P23" s="11" t="inlineStr">
         <is>
@@ -2137,7 +2133,7 @@
       </c>
       <c r="Q23" s="12" t="inlineStr">
         <is>
-          <t>30.0 kg/30.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="R23" s="10" t="n">
@@ -3181,10 +3177,8 @@
       <c r="U36" s="10" t="inlineStr"/>
       <c r="V36" s="11" t="inlineStr"/>
       <c r="W36" s="12" t="inlineStr"/>
-      <c r="X36" s="10" t="inlineStr">
-        <is>
-          <t>964/287</t>
-        </is>
+      <c r="X36" s="10" t="n">
+        <v>964</v>
       </c>
       <c r="Y36" s="11" t="inlineStr">
         <is>
@@ -3196,10 +3190,8 @@
           <t>47.0 kg</t>
         </is>
       </c>
-      <c r="AA36" s="10" t="inlineStr">
-        <is>
-          <t>963/242</t>
-        </is>
+      <c r="AA36" s="10" t="n">
+        <v>963</v>
       </c>
       <c r="AB36" s="11" t="inlineStr">
         <is>
@@ -14244,15 +14236,11 @@
       <c r="C19" s="14" t="inlineStr"/>
       <c r="D19" s="14" t="inlineStr"/>
       <c r="E19" s="14" t="inlineStr"/>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>930/961</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>931/962</t>
-        </is>
+      <c r="F19" s="14" t="n">
+        <v>961</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>962</v>
       </c>
       <c r="H19" s="14" t="n">
         <v>960</v>
@@ -14557,15 +14545,11 @@
       <c r="G30" s="14" t="inlineStr"/>
       <c r="H30" s="14" t="inlineStr"/>
       <c r="I30" s="14" t="inlineStr"/>
-      <c r="J30" s="14" t="inlineStr">
-        <is>
-          <t>964/287</t>
-        </is>
-      </c>
-      <c r="K30" s="14" t="inlineStr">
-        <is>
-          <t>963/242</t>
-        </is>
+      <c r="J30" s="14" t="n">
+        <v>964</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>963</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -18751,10 +18735,8 @@
       <c r="G14" s="17" t="inlineStr"/>
       <c r="H14" s="18" t="inlineStr"/>
       <c r="I14" s="12" t="inlineStr"/>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>930/961</t>
-        </is>
+      <c r="J14" s="17" t="n">
+        <v>961</v>
       </c>
       <c r="K14" s="18" t="inlineStr">
         <is>
@@ -18763,13 +18745,11 @@
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>39.0 kg/39.0 kg</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="inlineStr">
-        <is>
-          <t>931/962</t>
-        </is>
+          <t>39.0 kg</t>
+        </is>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>962</v>
       </c>
       <c r="N14" s="18" t="inlineStr">
         <is>
@@ -18778,7 +18758,7 @@
       </c>
       <c r="O14" s="12" t="inlineStr">
         <is>
-          <t>30.0 kg/30.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="P14" s="17" t="n">
@@ -19542,10 +19522,8 @@
       <c r="S22" s="17" t="inlineStr"/>
       <c r="T22" s="18" t="inlineStr"/>
       <c r="U22" s="12" t="inlineStr"/>
-      <c r="V22" s="17" t="inlineStr">
-        <is>
-          <t>964/287</t>
-        </is>
+      <c r="V22" s="17" t="n">
+        <v>964</v>
       </c>
       <c r="W22" s="18" t="inlineStr">
         <is>
@@ -19557,10 +19535,8 @@
           <t>47.0 kg</t>
         </is>
       </c>
-      <c r="Y22" s="17" t="inlineStr">
-        <is>
-          <t>963/242</t>
-        </is>
+      <c r="Y22" s="17" t="n">
+        <v>963</v>
       </c>
       <c r="Z22" s="18" t="inlineStr">
         <is>
@@ -27493,7 +27469,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>2229</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -27523,7 +27499,7 @@
         <v>21</v>
       </c>
       <c r="I10" s="23" t="n">
-        <v>2037</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -30798,10 +30774,8 @@
       <c r="B94" s="30" t="n">
         <v>66</v>
       </c>
-      <c r="C94" s="31" t="inlineStr">
-        <is>
-          <t>930/961</t>
-        </is>
+      <c r="C94" s="31" t="n">
+        <v>961</v>
       </c>
       <c r="D94" s="32" t="inlineStr">
         <is>
@@ -30810,12 +30784,12 @@
       </c>
       <c r="E94" s="30" t="inlineStr">
         <is>
-          <t>70/68</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F94" s="33" t="inlineStr">
         <is>
-          <t>39.0 kg/39.0 kg</t>
+          <t>39.0 kg</t>
         </is>
       </c>
       <c r="G94" s="30" t="inlineStr">
@@ -30843,10 +30817,8 @@
       <c r="B95" s="28" t="n">
         <v>67</v>
       </c>
-      <c r="C95" s="17" t="inlineStr">
-        <is>
-          <t>931/962</t>
-        </is>
+      <c r="C95" s="17" t="n">
+        <v>962</v>
       </c>
       <c r="D95" s="18" t="inlineStr">
         <is>
@@ -30855,12 +30827,12 @@
       </c>
       <c r="E95" s="28" t="inlineStr">
         <is>
-          <t>70/68</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>30.0 kg/30.0 kg</t>
+          <t>30.0 kg</t>
         </is>
       </c>
       <c r="G95" s="28" t="inlineStr">
@@ -33124,10 +33096,8 @@
       <c r="B148" s="30" t="n">
         <v>120</v>
       </c>
-      <c r="C148" s="31" t="inlineStr">
-        <is>
-          <t>964/287</t>
-        </is>
+      <c r="C148" s="31" t="n">
+        <v>964</v>
       </c>
       <c r="D148" s="32" t="inlineStr">
         <is>
@@ -33169,10 +33139,8 @@
       <c r="B149" s="28" t="n">
         <v>121</v>
       </c>
-      <c r="C149" s="17" t="inlineStr">
-        <is>
-          <t>963/242</t>
-        </is>
+      <c r="C149" s="17" t="n">
+        <v>963</v>
       </c>
       <c r="D149" s="18" t="inlineStr">
         <is>
